--- a/data/CANONICAL Bouquet Recipe Master Sheet.xlsx
+++ b/data/CANONICAL Bouquet Recipe Master Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sharon/Documents/Sweet Piedmont/Offerings/Software and Code/bouquet-blueprint-app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14282A8B-0353-FD47-B8DA-3635326775E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3070DFDE-9FCF-4747-B5F0-C2F68FD84ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11100" yWindow="920" windowWidth="16140" windowHeight="21280" firstSheet="1" activeTab="1" xr2:uid="{835A2F5B-2282-E345-9D43-16C3FBECA701}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="34240" windowHeight="21260" firstSheet="1" activeTab="1" xr2:uid="{835A2F5B-2282-E345-9D43-16C3FBECA701}"/>
   </bookViews>
   <sheets>
     <sheet name="IMPT INFO" sheetId="30" r:id="rId1"/>
@@ -543,7 +543,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5337" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5349" uniqueCount="947">
   <si>
     <t>CANONICAL PRICING WORKBOOK</t>
   </si>
@@ -3399,6 +3399,24 @@
   </si>
   <si>
     <t>Standard Deviation</t>
+  </si>
+  <si>
+    <t>Geranium foliage</t>
+  </si>
+  <si>
+    <t>Poppy - Icelandic (S)</t>
+  </si>
+  <si>
+    <t>Poppy - Icelandic (M)</t>
+  </si>
+  <si>
+    <t>Poppy - Icelandic (L)</t>
+  </si>
+  <si>
+    <t>Raspberry foliage</t>
+  </si>
+  <si>
+    <t>Spirea branch</t>
   </si>
 </sst>
 </file>
@@ -11650,10 +11668,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{63FB889B-362F-FA4D-9D4D-A49BD91E0CC2}" name="Table31615" displayName="Table31615" ref="A1:K293" totalsRowShown="0" headerRowDxfId="143" dataDxfId="142" tableBorderDxfId="141" headerRowCellStyle="Currency" dataCellStyle="Currency">
-  <autoFilter ref="A1:K293" xr:uid="{63FB889B-362F-FA4D-9D4D-A49BD91E0CC2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K293">
-    <sortCondition ref="C1:C293"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{63FB889B-362F-FA4D-9D4D-A49BD91E0CC2}" name="Table31615" displayName="Table31615" ref="A1:K297" totalsRowShown="0" headerRowDxfId="143" dataDxfId="142" tableBorderDxfId="141" headerRowCellStyle="Currency" dataCellStyle="Currency">
+  <autoFilter ref="A1:K297" xr:uid="{63FB889B-362F-FA4D-9D4D-A49BD91E0CC2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K297">
+    <sortCondition ref="C1:C297"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{CD3DACDE-DD55-C44F-80CC-C1C7B474F6D3}" name="Season"/>
@@ -33847,7 +33865,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D3CD6E7-2CCA-C441-90A4-7482336BBF20}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:T293"/>
+  <dimension ref="A1:T297"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -34189,28 +34207,28 @@
         <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" s="79">
         <f>E9*(1+$T$1)</f>
-        <v>2.8537500000000002</v>
+        <v>2.9475000000000002</v>
       </c>
       <c r="E9" s="79">
         <f>AVERAGE(G9:Q9)</f>
-        <v>1.9025000000000001</v>
+        <v>1.9650000000000001</v>
       </c>
       <c r="F9" s="79">
         <f>STDEV(G9:Q9)</f>
-        <v>0.7949999999999996</v>
+        <v>0.60737138556240855</v>
       </c>
       <c r="G9" s="79">
-        <v>0.75</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H9" s="79">
-        <v>2.4</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="I9" s="79"/>
       <c r="J9" s="140"/>
@@ -34226,40 +34244,40 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="322" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="D10" s="79">
         <f>E10*(1+$T$1)</f>
-        <v>2.4299999999999997</v>
+        <v>2.8537500000000002</v>
       </c>
       <c r="E10" s="79">
         <f>AVERAGE(G10:Q10)</f>
-        <v>1.6199999999999999</v>
+        <v>1.9025000000000001</v>
       </c>
       <c r="F10" s="79">
         <f>STDEV(G10:Q10)</f>
-        <v>0.63895748424027965</v>
+        <v>0.7949999999999996</v>
       </c>
       <c r="G10" s="79">
-        <v>1.1000000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H10" s="79">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="I10" s="79"/>
       <c r="J10" s="140"/>
       <c r="K10" s="141"/>
       <c r="L10" s="155">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O10" s="155">
-        <v>1.68</v>
+        <v>2.46</v>
       </c>
       <c r="S10" s="112"/>
       <c r="T10" s="159"/>
@@ -34269,166 +34287,176 @@
         <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>923</v>
-      </c>
-      <c r="D11" s="79" t="e">
-        <f>E11*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>58</v>
+      </c>
+      <c r="D11" s="79">
+        <f>E11*(1+$T$1)</f>
+        <v>2.8537500000000002</v>
       </c>
       <c r="E11" s="79">
         <f>AVERAGE(G11:Q11)</f>
-        <v>1.5</v>
-      </c>
-      <c r="F11" s="79" t="e">
+        <v>1.9025000000000001</v>
+      </c>
+      <c r="F11" s="79">
         <f>STDEV(G11:Q11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
+        <v>0.7949999999999996</v>
+      </c>
+      <c r="G11" s="79">
+        <v>0.75</v>
+      </c>
+      <c r="H11" s="79">
+        <v>2.4</v>
+      </c>
       <c r="I11" s="79"/>
       <c r="J11" s="140"/>
       <c r="K11" s="141"/>
+      <c r="L11" s="155">
+        <v>2</v>
+      </c>
       <c r="O11" s="155">
-        <v>1.5</v>
+        <v>2.46</v>
       </c>
       <c r="S11" s="112"/>
       <c r="T11" s="159"/>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="322" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>899</v>
-      </c>
-      <c r="D12" s="79" t="e">
-        <f>E12*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>43</v>
+      </c>
+      <c r="D12" s="79">
+        <f>E12*(1+$T$1)</f>
+        <v>2.4299999999999997</v>
       </c>
       <c r="E12" s="79">
         <f>AVERAGE(G12:Q12)</f>
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="F12" s="79" t="e">
+        <v>1.6199999999999999</v>
+      </c>
+      <c r="F12" s="79">
         <f>STDEV(G12:Q12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
+        <v>0.63895748424027965</v>
+      </c>
+      <c r="G12" s="79">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H12" s="79">
+        <v>1.2</v>
+      </c>
       <c r="I12" s="79"/>
       <c r="J12" s="140"/>
       <c r="K12" s="141"/>
+      <c r="L12" s="155">
+        <v>2.5</v>
+      </c>
       <c r="O12" s="155">
-        <v>2.0099999999999998</v>
+        <v>1.68</v>
       </c>
       <c r="S12" s="112"/>
       <c r="T12" s="159"/>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="322" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" s="79">
-        <f>E13*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>923</v>
+      </c>
+      <c r="D13" s="79" t="e">
+        <f>E13*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E13" s="79">
         <f>AVERAGE(G13:Q13)</f>
-        <v>1.1000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="F13" s="79" t="e">
         <f>STDEV(G13:Q13)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G13" s="140"/>
-      <c r="H13" s="140"/>
-      <c r="I13" s="79">
-        <v>1.1000000000000001</v>
-      </c>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
       <c r="J13" s="140"/>
       <c r="K13" s="141"/>
+      <c r="O13" s="155">
+        <v>1.5</v>
+      </c>
       <c r="S13" s="112"/>
       <c r="T13" s="159"/>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="322" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="79">
-        <f>E14*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>899</v>
+      </c>
+      <c r="D14" s="79" t="e">
+        <f>E14*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E14" s="79">
         <f>AVERAGE(G14:Q14)</f>
-        <v>1.1000000000000001</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="F14" s="79" t="e">
         <f>STDEV(G14:Q14)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G14" s="140"/>
-      <c r="H14" s="140"/>
-      <c r="I14" s="79">
-        <v>1.1000000000000001</v>
-      </c>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
       <c r="J14" s="140"/>
       <c r="K14" s="141"/>
+      <c r="O14" s="155">
+        <v>2.0099999999999998</v>
+      </c>
       <c r="S14" s="112"/>
       <c r="T14" s="159"/>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="322" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s">
         <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="D15" s="79">
         <f>E15*(1+$T$1)</f>
-        <v>1.7250000000000001</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="E15" s="79">
         <f>AVERAGE(G15:Q15)</f>
-        <v>1.1500000000000001</v>
-      </c>
-      <c r="F15" s="79">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F15" s="79" t="e">
         <f>STDEV(G15:Q15)</f>
-        <v>8.660254037844381E-2</v>
-      </c>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G15" s="140"/>
+      <c r="H15" s="140"/>
+      <c r="I15" s="79">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I15" s="79"/>
       <c r="J15" s="140"/>
       <c r="K15" s="141"/>
-      <c r="N15" s="155">
-        <v>1.25</v>
-      </c>
-      <c r="P15" s="155">
-        <v>1.1000000000000001</v>
-      </c>
       <c r="S15" s="112"/>
       <c r="T15" s="159"/>
     </row>
@@ -34437,65 +34465,67 @@
         <v>142</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>900</v>
-      </c>
-      <c r="D16" s="79" t="e">
-        <f>E16*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>135</v>
+      </c>
+      <c r="D16" s="79">
+        <f>E16*(1+$T$1)</f>
+        <v>1.6500000000000001</v>
       </c>
       <c r="E16" s="79">
         <f>AVERAGE(G16:Q16)</f>
-        <v>3.75</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F16" s="79" t="e">
         <f>STDEV(G16:Q16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="140"/>
+      <c r="I16" s="79">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="J16" s="140"/>
       <c r="K16" s="141"/>
-      <c r="O16" s="155">
-        <v>3.75</v>
-      </c>
       <c r="S16" s="112"/>
       <c r="T16" s="159"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" t="s">
-        <v>142</v>
+      <c r="A17" s="322" t="s">
+        <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="D17" s="79">
         <f>E17*(1+$T$1)</f>
-        <v>2.5875000000000004</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="E17" s="79">
         <f>AVERAGE(G17:Q17)</f>
-        <v>1.7250000000000001</v>
+        <v>1.1500000000000001</v>
       </c>
       <c r="F17" s="79">
         <f>STDEV(G17:Q17)</f>
-        <v>0.31819805153394543</v>
-      </c>
-      <c r="G17" s="140"/>
-      <c r="H17" s="140"/>
-      <c r="I17" s="79">
-        <v>1.5</v>
-      </c>
+        <v>8.660254037844381E-2</v>
+      </c>
+      <c r="G17" s="79"/>
+      <c r="H17" s="79">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I17" s="79"/>
       <c r="J17" s="140"/>
       <c r="K17" s="141"/>
-      <c r="O17" s="155">
-        <v>1.95</v>
+      <c r="N17" s="155">
+        <v>1.25</v>
+      </c>
+      <c r="P17" s="155">
+        <v>1.1000000000000001</v>
       </c>
       <c r="S17" s="112"/>
       <c r="T17" s="159"/>
@@ -34508,29 +34538,32 @@
         <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="79">
         <f>E18*(1+$T$1)</f>
-        <v>2.52</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="E18" s="79">
         <f>AVERAGE(G18:Q18)</f>
-        <v>1.68</v>
+        <v>1.1500000000000001</v>
       </c>
       <c r="F18" s="79">
         <f>STDEV(G18:Q18)</f>
-        <v>1.3152186130069783</v>
-      </c>
-      <c r="G18" s="79">
-        <v>0.75</v>
-      </c>
-      <c r="H18" s="79"/>
+        <v>8.660254037844381E-2</v>
+      </c>
+      <c r="G18" s="79"/>
+      <c r="H18" s="79">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="I18" s="79"/>
       <c r="J18" s="140"/>
       <c r="K18" s="141"/>
-      <c r="O18" s="155">
-        <v>2.61</v>
+      <c r="N18" s="155">
+        <v>1.25</v>
+      </c>
+      <c r="P18" s="155">
+        <v>1.1000000000000001</v>
       </c>
       <c r="S18" s="112"/>
       <c r="T18" s="159"/>
@@ -34540,339 +34573,339 @@
         <v>142</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" s="79">
-        <f>E19*(1+$T$1)</f>
-        <v>2.5</v>
+        <v>900</v>
+      </c>
+      <c r="D19" s="79" t="e">
+        <f>E19*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E19" s="79">
         <f>AVERAGE(G19:Q19)</f>
-        <v>1.6666666666666667</v>
-      </c>
-      <c r="F19" s="79">
+        <v>3.75</v>
+      </c>
+      <c r="F19" s="79" t="e">
         <f>STDEV(G19:Q19)</f>
-        <v>0.23094010767585105</v>
-      </c>
-      <c r="G19" s="79">
-        <v>1.4</v>
-      </c>
-      <c r="H19" s="79">
-        <v>1.8</v>
-      </c>
-      <c r="I19" s="79">
-        <v>1.8</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G19" s="79"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="79"/>
       <c r="J19" s="140"/>
       <c r="K19" s="141"/>
+      <c r="O19" s="155">
+        <v>3.75</v>
+      </c>
       <c r="S19" s="112"/>
       <c r="T19" s="159"/>
     </row>
     <row r="20" spans="1:20">
-      <c r="A20" s="322" t="s">
-        <v>55</v>
+      <c r="A20" t="s">
+        <v>142</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="D20" s="79">
         <f>E20*(1+$T$1)</f>
-        <v>2.125</v>
+        <v>2.5875000000000004</v>
       </c>
       <c r="E20" s="79">
         <f>AVERAGE(G20:Q20)</f>
-        <v>1.4166666666666667</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="F20" s="79">
         <f>STDEV(G20:Q20)</f>
-        <v>0.38188130791298686</v>
-      </c>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79">
-        <v>1</v>
-      </c>
-      <c r="I20" s="79"/>
+        <v>0.31819805153394543</v>
+      </c>
+      <c r="G20" s="140"/>
+      <c r="H20" s="140"/>
+      <c r="I20" s="79">
+        <v>1.5</v>
+      </c>
       <c r="J20" s="140"/>
       <c r="K20" s="141"/>
-      <c r="N20" s="155">
-        <v>1.5</v>
-      </c>
       <c r="O20" s="155">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="S20" s="112"/>
       <c r="T20" s="159"/>
     </row>
     <row r="21" spans="1:20">
       <c r="A21" s="322" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>935</v>
+        <v>60</v>
       </c>
       <c r="D21" s="79">
         <f>E21*(1+$T$1)</f>
-        <v>3.75</v>
-      </c>
-      <c r="E21" s="140">
+        <v>2.3049999999999997</v>
+      </c>
+      <c r="E21" s="79">
         <f>AVERAGE(G21:Q21)</f>
-        <v>2.5</v>
-      </c>
-      <c r="F21" s="140">
+        <v>1.5366666666666664</v>
+      </c>
+      <c r="F21" s="79">
         <f>STDEV(G21:Q21)</f>
-        <v>0.5</v>
-      </c>
-      <c r="G21" s="140"/>
-      <c r="H21" s="140">
-        <v>3</v>
-      </c>
+        <v>0.96256601505212824</v>
+      </c>
+      <c r="G21" s="79">
+        <v>0.75</v>
+      </c>
+      <c r="H21" s="79"/>
       <c r="I21" s="79">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="J21" s="140"/>
       <c r="K21" s="141"/>
-      <c r="L21" s="155">
-        <v>2.5</v>
+      <c r="O21" s="155">
+        <v>2.61</v>
       </c>
       <c r="S21" s="112"/>
       <c r="T21" s="159"/>
     </row>
     <row r="22" spans="1:20">
       <c r="A22" s="322" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>902</v>
-      </c>
-      <c r="D22" s="79" t="e">
-        <f>E22*(1+$O$1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E22" s="140">
+        <v>98</v>
+      </c>
+      <c r="D22" s="79">
+        <f>E22*(1+$T$1)</f>
+        <v>2.5</v>
+      </c>
+      <c r="E22" s="79">
         <f>AVERAGE(G22:Q22)</f>
-        <v>1.5</v>
-      </c>
-      <c r="F22" s="140" t="e">
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="F22" s="79">
         <f>STDEV(G22:Q22)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G22" s="140"/>
-      <c r="H22" s="140"/>
-      <c r="I22" s="79"/>
+        <v>0.23094010767585105</v>
+      </c>
+      <c r="G22" s="79">
+        <v>1.4</v>
+      </c>
+      <c r="H22" s="79">
+        <v>1.8</v>
+      </c>
+      <c r="I22" s="79">
+        <v>1.8</v>
+      </c>
       <c r="J22" s="140"/>
       <c r="K22" s="141"/>
-      <c r="O22" s="155">
-        <v>1.5</v>
-      </c>
       <c r="S22" s="112"/>
       <c r="T22" s="159"/>
     </row>
     <row r="23" spans="1:20">
       <c r="A23" s="322" t="s">
-        <v>892</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>933</v>
-      </c>
-      <c r="D23" s="79" t="e">
-        <f>E23*(1+$O$1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E23" s="140">
+        <v>61</v>
+      </c>
+      <c r="D23" s="79">
+        <f>E23*(1+$T$1)</f>
+        <v>2.125</v>
+      </c>
+      <c r="E23" s="79">
         <f>AVERAGE(G23:Q23)</f>
-        <v>0.8640000000000001</v>
-      </c>
-      <c r="F23" s="140">
+        <v>1.4166666666666667</v>
+      </c>
+      <c r="F23" s="79">
         <f>STDEV(G23:Q23)</f>
-        <v>0.2353295561547675</v>
-      </c>
-      <c r="G23" s="140"/>
-      <c r="H23" s="140">
-        <v>0.89</v>
+        <v>0.38188130791298686</v>
+      </c>
+      <c r="G23" s="79"/>
+      <c r="H23" s="79">
+        <v>1</v>
       </c>
       <c r="I23" s="79"/>
-      <c r="J23" s="140">
-        <v>0.63</v>
-      </c>
+      <c r="J23" s="140"/>
       <c r="K23" s="141"/>
-      <c r="L23" s="155">
-        <v>0.95</v>
-      </c>
       <c r="N23" s="155">
-        <v>1.2</v>
-      </c>
-      <c r="P23" s="155">
-        <v>0.65</v>
+        <v>1.5</v>
+      </c>
+      <c r="O23" s="155">
+        <v>1.75</v>
       </c>
       <c r="S23" s="112"/>
       <c r="T23" s="159"/>
     </row>
     <row r="24" spans="1:20">
       <c r="A24" s="322" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="322" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="322" t="s">
-        <v>62</v>
+        <v>30</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>935</v>
       </c>
       <c r="D24" s="79">
         <f>E24*(1+$T$1)</f>
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="E24" s="79">
+        <v>3.75</v>
+      </c>
+      <c r="E24" s="140">
         <f>AVERAGE(G24:Q24)</f>
-        <v>1.6733333333333331</v>
-      </c>
-      <c r="F24" s="79">
+        <v>2.5</v>
+      </c>
+      <c r="F24" s="140">
         <f>STDEV(G24:Q24)</f>
-        <v>0.41064989143226871</v>
-      </c>
-      <c r="G24" s="79">
-        <v>1.25</v>
-      </c>
-      <c r="H24" s="79">
-        <v>1.7</v>
-      </c>
-      <c r="I24" s="79"/>
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="140"/>
+      <c r="H24" s="140">
+        <v>3</v>
+      </c>
+      <c r="I24" s="79">
+        <v>2</v>
+      </c>
       <c r="J24" s="140"/>
       <c r="K24" s="141"/>
-      <c r="O24" s="155">
-        <v>2.0699999999999998</v>
+      <c r="L24" s="155">
+        <v>2.5</v>
       </c>
       <c r="S24" s="112"/>
       <c r="T24" s="159"/>
     </row>
     <row r="25" spans="1:20">
       <c r="A25" s="322" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D25" s="79" t="e">
         <f>E25*(1+$O$1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E25" s="79" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E25" s="140">
         <f>AVERAGE(G25:Q25)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F25" s="79" t="e">
+        <v>1.5</v>
+      </c>
+      <c r="F25" s="140" t="e">
         <f>STDEV(G25:Q25)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="140"/>
       <c r="I25" s="79"/>
       <c r="J25" s="140"/>
       <c r="K25" s="141"/>
+      <c r="O25" s="155">
+        <v>1.5</v>
+      </c>
       <c r="S25" s="112"/>
       <c r="T25" s="159"/>
     </row>
     <row r="26" spans="1:20">
       <c r="A26" s="322" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>904</v>
+        <v>933</v>
       </c>
       <c r="D26" s="79" t="e">
         <f>E26*(1+$O$1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E26" s="79">
+      <c r="E26" s="140">
         <f>AVERAGE(G26:Q26)</f>
-        <v>2.35</v>
-      </c>
-      <c r="F26" s="79">
+        <v>0.8640000000000001</v>
+      </c>
+      <c r="F26" s="140">
         <f>STDEV(G26:Q26)</f>
-        <v>1.2020815280171309</v>
-      </c>
-      <c r="G26" s="79"/>
-      <c r="H26" s="79"/>
+        <v>0.2353295561547675</v>
+      </c>
+      <c r="G26" s="140"/>
+      <c r="H26" s="140">
+        <v>0.89</v>
+      </c>
       <c r="I26" s="79"/>
-      <c r="J26" s="140"/>
+      <c r="J26" s="140">
+        <v>0.63</v>
+      </c>
       <c r="K26" s="141"/>
       <c r="L26" s="155">
-        <v>3.2</v>
-      </c>
-      <c r="O26" s="155">
-        <v>1.5</v>
+        <v>0.95</v>
+      </c>
+      <c r="N26" s="155">
+        <v>1.2</v>
+      </c>
+      <c r="P26" s="155">
+        <v>0.65</v>
       </c>
       <c r="S26" s="112"/>
       <c r="T26" s="159"/>
     </row>
     <row r="27" spans="1:20">
       <c r="A27" s="322" t="s">
-        <v>142</v>
-      </c>
-      <c r="B27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" t="s">
-        <v>905</v>
+        <v>55</v>
+      </c>
+      <c r="B27" s="322" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="322" t="s">
+        <v>62</v>
       </c>
       <c r="D27" s="79">
         <f>E27*(1+$T$1)</f>
-        <v>2.3250000000000002</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="E27" s="79">
         <f>AVERAGE(G27:Q27)</f>
-        <v>1.55</v>
+        <v>1.6733333333333331</v>
       </c>
       <c r="F27" s="79">
         <f>STDEV(G27:Q27)</f>
-        <v>0.17320508075688779</v>
+        <v>0.41064989143226871</v>
       </c>
       <c r="G27" s="79">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="H27" s="79">
-        <v>1.8</v>
-      </c>
-      <c r="I27" s="79">
-        <v>1.5</v>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="I27" s="79"/>
       <c r="J27" s="140"/>
       <c r="K27" s="141"/>
       <c r="O27" s="155">
-        <v>1.5</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="S27" s="112"/>
       <c r="T27" s="159"/>
     </row>
     <row r="28" spans="1:20">
       <c r="A28" s="322" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="D28" s="79" t="e">
         <f>E28*(1+$O$1)</f>
@@ -34880,7 +34913,7 @@
       </c>
       <c r="E28" s="79">
         <f>AVERAGE(G28:Q28)</f>
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="F28" s="79" t="e">
         <f>STDEV(G28:Q28)</f>
@@ -34888,24 +34921,23 @@
       </c>
       <c r="G28" s="79"/>
       <c r="H28" s="79"/>
-      <c r="I28" s="79"/>
+      <c r="I28" s="79">
+        <v>1.75</v>
+      </c>
       <c r="J28" s="140"/>
       <c r="K28" s="141"/>
-      <c r="O28" s="155">
-        <v>1.86</v>
-      </c>
       <c r="S28" s="112"/>
       <c r="T28" s="159"/>
     </row>
     <row r="29" spans="1:20">
       <c r="A29" s="322" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="D29" s="79" t="e">
         <f>E29*(1+$O$1)</f>
@@ -34913,24 +34945,26 @@
       </c>
       <c r="E29" s="79">
         <f>AVERAGE(G29:Q29)</f>
-        <v>2.6666666666666665</v>
+        <v>1.9750000000000001</v>
       </c>
       <c r="F29" s="79">
         <f>STDEV(G29:Q29)</f>
-        <v>1.3316656236958793</v>
-      </c>
-      <c r="G29" s="79"/>
+        <v>0.83416625041614656</v>
+      </c>
+      <c r="G29" s="79">
+        <v>1.4</v>
+      </c>
       <c r="H29" s="79">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I29" s="79"/>
       <c r="J29" s="140"/>
       <c r="K29" s="141"/>
       <c r="L29" s="155">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="O29" s="155">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="S29" s="112"/>
       <c r="T29" s="159"/>
@@ -34940,46 +34974,49 @@
         <v>142</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>906</v>
-      </c>
-      <c r="D30" s="79" t="e">
-        <f>E30*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>905</v>
+      </c>
+      <c r="D30" s="79">
+        <f>E30*(1+$T$1)</f>
+        <v>2.3250000000000002</v>
       </c>
       <c r="E30" s="79">
         <f>AVERAGE(G30:Q30)</f>
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="F30" s="79">
         <f>STDEV(G30:Q30)</f>
-        <v>0.63639610306789296</v>
-      </c>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="79"/>
+        <v>0.17320508075688779</v>
+      </c>
+      <c r="G30" s="79">
+        <v>1.4</v>
+      </c>
+      <c r="H30" s="79">
+        <v>1.8</v>
+      </c>
+      <c r="I30" s="79">
+        <v>1.5</v>
+      </c>
       <c r="J30" s="140"/>
       <c r="K30" s="141"/>
-      <c r="N30" s="155">
-        <v>1.2</v>
-      </c>
       <c r="O30" s="155">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="S30" s="112"/>
       <c r="T30" s="159"/>
     </row>
     <row r="31" spans="1:20">
       <c r="A31" s="322" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C31" t="s">
-        <v>934</v>
+        <v>907</v>
       </c>
       <c r="D31" s="79" t="e">
         <f>E31*(1+$O$1)</f>
@@ -34987,268 +35024,272 @@
       </c>
       <c r="E31" s="79">
         <f>AVERAGE(G31:Q31)</f>
-        <v>1.55</v>
-      </c>
-      <c r="F31" s="79">
+        <v>1.86</v>
+      </c>
+      <c r="F31" s="79" t="e">
         <f>STDEV(G31:Q31)</f>
-        <v>0.77781745930520196</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G31" s="79"/>
       <c r="H31" s="79"/>
       <c r="I31" s="79"/>
       <c r="J31" s="140"/>
       <c r="K31" s="141"/>
-      <c r="N31" s="155">
-        <v>1</v>
-      </c>
       <c r="O31" s="155">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="S31" s="112"/>
       <c r="T31" s="159"/>
     </row>
     <row r="32" spans="1:20">
       <c r="A32" s="322" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" s="79">
-        <f>E32*(1+$T$1)</f>
-        <v>2.4900000000000002</v>
+        <v>908</v>
+      </c>
+      <c r="D32" s="79" t="e">
+        <f>E32*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E32" s="79">
         <f>AVERAGE(G32:Q32)</f>
-        <v>1.6600000000000001</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="F32" s="79">
         <f>STDEV(G32:Q32)</f>
-        <v>0.19697715603592203</v>
-      </c>
-      <c r="G32" s="79">
-        <v>1.6</v>
-      </c>
-      <c r="H32" s="79"/>
+        <v>1.3316656236958793</v>
+      </c>
+      <c r="G32" s="79"/>
+      <c r="H32" s="79">
+        <v>2</v>
+      </c>
       <c r="I32" s="79"/>
       <c r="J32" s="140"/>
       <c r="K32" s="141"/>
       <c r="L32" s="155">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O32" s="155">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="S32" s="112"/>
       <c r="T32" s="159"/>
     </row>
     <row r="33" spans="1:20">
-      <c r="A33" t="s">
-        <v>892</v>
+      <c r="A33" s="322" t="s">
+        <v>142</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
-      </c>
-      <c r="D33" s="79">
-        <f>E33*(1+$T$1)</f>
-        <v>1.9500000000000002</v>
+        <v>906</v>
+      </c>
+      <c r="D33" s="79" t="e">
+        <f>E33*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E33" s="79">
         <f>AVERAGE(G33:Q33)</f>
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="F33" s="79">
         <f>STDEV(G33:Q33)</f>
-        <v>0.28284271247461834</v>
-      </c>
-      <c r="G33" s="140"/>
-      <c r="H33" s="140"/>
-      <c r="I33" s="79">
-        <v>1.1000000000000001</v>
-      </c>
+        <v>0.63639610306789296</v>
+      </c>
+      <c r="G33" s="79"/>
+      <c r="H33" s="79"/>
+      <c r="I33" s="79"/>
       <c r="J33" s="140"/>
       <c r="K33" s="141"/>
+      <c r="N33" s="155">
+        <v>1.2</v>
+      </c>
       <c r="O33" s="155">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="S33" s="112"/>
       <c r="T33" s="159"/>
     </row>
     <row r="34" spans="1:20">
       <c r="A34" s="322" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="B34" t="s">
         <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" s="79">
-        <f>E34*(1+$T$1)</f>
-        <v>2.37</v>
+        <v>934</v>
+      </c>
+      <c r="D34" s="79" t="e">
+        <f>E34*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E34" s="79">
         <f>AVERAGE(G34:Q34)</f>
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="F34" s="79">
         <f>STDEV(G34:Q34)</f>
-        <v>0.3204684071792413</v>
+        <v>0.77781745930520196</v>
       </c>
       <c r="G34" s="79"/>
-      <c r="H34" s="79">
-        <v>1.6</v>
-      </c>
-      <c r="I34" s="79">
-        <v>1.25</v>
-      </c>
+      <c r="H34" s="79"/>
+      <c r="I34" s="79"/>
       <c r="J34" s="140"/>
       <c r="K34" s="141"/>
+      <c r="N34" s="155">
+        <v>1</v>
+      </c>
       <c r="O34" s="155">
-        <v>1.89</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="S34" s="112"/>
+      <c r="T34" s="159"/>
     </row>
     <row r="35" spans="1:20">
       <c r="A35" s="322" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="D35" s="79">
         <f>E35*(1+$T$1)</f>
-        <v>2.3549999999999995</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="E35" s="79">
         <f>AVERAGE(G35:Q35)</f>
-        <v>1.5699999999999998</v>
+        <v>1.6600000000000001</v>
       </c>
       <c r="F35" s="79">
         <f>STDEV(G35:Q35)</f>
-        <v>0.45254833995939103</v>
-      </c>
-      <c r="G35" s="79"/>
+        <v>0.19697715603592203</v>
+      </c>
+      <c r="G35" s="79">
+        <v>1.6</v>
+      </c>
       <c r="H35" s="79"/>
-      <c r="I35" s="79">
-        <v>1.25</v>
-      </c>
+      <c r="I35" s="79"/>
       <c r="J35" s="140"/>
       <c r="K35" s="141"/>
+      <c r="L35" s="155">
+        <v>1.5</v>
+      </c>
       <c r="O35" s="155">
-        <v>1.89</v>
-      </c>
+        <v>1.88</v>
+      </c>
+      <c r="S35" s="112"/>
+      <c r="T35" s="159"/>
     </row>
     <row r="36" spans="1:20">
-      <c r="A36" s="322" t="s">
-        <v>142</v>
+      <c r="A36" t="s">
+        <v>892</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>364</v>
-      </c>
-      <c r="D36" s="79" t="e">
-        <f>E36*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>119</v>
+      </c>
+      <c r="D36" s="79">
+        <f>E36*(1+$T$1)</f>
+        <v>1.9500000000000002</v>
       </c>
       <c r="E36" s="79">
         <f>AVERAGE(G36:Q36)</f>
-        <v>1.5</v>
-      </c>
-      <c r="F36" s="79" t="e">
+        <v>1.3</v>
+      </c>
+      <c r="F36" s="79">
         <f>STDEV(G36:Q36)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G36" s="79"/>
-      <c r="H36" s="79"/>
-      <c r="I36" s="79"/>
+        <v>0.28284271247461834</v>
+      </c>
+      <c r="G36" s="140"/>
+      <c r="H36" s="140"/>
+      <c r="I36" s="79">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="J36" s="140"/>
       <c r="K36" s="141"/>
       <c r="O36" s="155">
         <v>1.5</v>
       </c>
+      <c r="S36" s="112"/>
+      <c r="T36" s="159"/>
     </row>
     <row r="37" spans="1:20">
-      <c r="A37" t="s">
-        <v>142</v>
+      <c r="A37" s="322" t="s">
+        <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D37" s="79">
         <f>E37*(1+$T$1)</f>
-        <v>6.15</v>
+        <v>2.37</v>
       </c>
       <c r="E37" s="79">
         <f>AVERAGE(G37:Q37)</f>
-        <v>4.1000000000000005</v>
+        <v>1.58</v>
       </c>
       <c r="F37" s="79">
         <f>STDEV(G37:Q37)</f>
-        <v>0.36055512754639901</v>
+        <v>0.3204684071792413</v>
       </c>
       <c r="G37" s="79"/>
       <c r="H37" s="79">
-        <v>3.8</v>
-      </c>
-      <c r="I37" s="79"/>
+        <v>1.6</v>
+      </c>
+      <c r="I37" s="79">
+        <v>1.25</v>
+      </c>
       <c r="J37" s="140"/>
       <c r="K37" s="141"/>
-      <c r="L37" s="155">
-        <v>4</v>
-      </c>
       <c r="O37" s="155">
-        <v>4.5</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="38" spans="1:20">
       <c r="A38" s="322" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="D38" s="79">
         <f>E38*(1+$T$1)</f>
-        <v>4.51</v>
+        <v>2.3549999999999995</v>
       </c>
       <c r="E38" s="79">
         <f>AVERAGE(G38:Q38)</f>
-        <v>3.0066666666666664</v>
+        <v>1.5699999999999998</v>
       </c>
       <c r="F38" s="79">
         <f>STDEV(G38:Q38)</f>
-        <v>0.59002824791134789</v>
-      </c>
-      <c r="G38" s="79">
-        <v>3</v>
-      </c>
+        <v>0.45254833995939103</v>
+      </c>
+      <c r="G38" s="79"/>
       <c r="H38" s="79"/>
-      <c r="I38" s="79"/>
+      <c r="I38" s="79">
+        <v>1.25</v>
+      </c>
       <c r="J38" s="140"/>
       <c r="K38" s="141"/>
-      <c r="L38" s="155">
-        <v>2.42</v>
-      </c>
       <c r="O38" s="155">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -35259,164 +35300,167 @@
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
-      </c>
-      <c r="D39" s="79">
-        <f>E39*(1+$T$1)</f>
-        <v>4.2750000000000004</v>
+        <v>364</v>
+      </c>
+      <c r="D39" s="79" t="e">
+        <f>E39*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E39" s="79">
         <f>AVERAGE(G39:Q39)</f>
-        <v>2.85</v>
-      </c>
-      <c r="F39" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="F39" s="79" t="e">
         <f>STDEV(G39:Q39)</f>
-        <v>1.0606601717798212</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G39" s="79"/>
       <c r="H39" s="79"/>
-      <c r="I39" s="79">
-        <v>2.1</v>
-      </c>
+      <c r="I39" s="79"/>
       <c r="J39" s="140"/>
       <c r="K39" s="141"/>
       <c r="O39" s="155">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="40" spans="1:20">
-      <c r="A40" s="322" t="s">
-        <v>892</v>
+      <c r="A40" t="s">
+        <v>142</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="D40" s="79">
         <f>E40*(1+$T$1)</f>
-        <v>2</v>
+        <v>6.15</v>
       </c>
       <c r="E40" s="79">
         <f>AVERAGE(G40:Q40)</f>
-        <v>1.3333333333333333</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="F40" s="79">
         <f>STDEV(G40:Q40)</f>
-        <v>0.15275252316519469</v>
-      </c>
-      <c r="G40" s="79">
-        <v>1.3</v>
-      </c>
+        <v>0.36055512754639901</v>
+      </c>
+      <c r="G40" s="79"/>
       <c r="H40" s="79">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="I40" s="79"/>
       <c r="J40" s="140"/>
       <c r="K40" s="141"/>
-      <c r="N40" s="155">
-        <v>1.5</v>
+      <c r="L40" s="155">
+        <v>4</v>
+      </c>
+      <c r="O40" s="155">
+        <v>4.5</v>
       </c>
     </row>
     <row r="41" spans="1:20">
       <c r="A41" s="322" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D41" s="79">
         <f>E41*(1+$T$1)</f>
-        <v>2</v>
+        <v>4.51</v>
       </c>
       <c r="E41" s="79">
         <f>AVERAGE(G41:Q41)</f>
-        <v>1.3333333333333333</v>
+        <v>3.0066666666666664</v>
       </c>
       <c r="F41" s="79">
         <f>STDEV(G41:Q41)</f>
-        <v>0.15275252316519469</v>
+        <v>0.59002824791134789</v>
       </c>
       <c r="G41" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="H41" s="79">
-        <v>1.2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H41" s="79"/>
       <c r="I41" s="79"/>
       <c r="J41" s="140"/>
       <c r="K41" s="141"/>
-      <c r="N41" s="155">
-        <v>1.5</v>
+      <c r="L41" s="155">
+        <v>2.42</v>
+      </c>
+      <c r="O41" s="155">
+        <v>3.6</v>
       </c>
     </row>
     <row r="42" spans="1:20">
       <c r="A42" s="322" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="D42" s="79">
         <f>E42*(1+$T$1)</f>
-        <v>1.75</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="E42" s="79">
         <f>AVERAGE(G42:Q42)</f>
-        <v>1.1666666666666667</v>
+        <v>3.3</v>
       </c>
       <c r="F42" s="79">
         <f>STDEV(G42:Q42)</f>
-        <v>0.15275252316519497</v>
+        <v>0.42426406871192857</v>
       </c>
       <c r="G42" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="H42" s="79">
-        <v>1.2</v>
-      </c>
-      <c r="I42" s="79">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H42" s="79"/>
+      <c r="I42" s="79"/>
       <c r="J42" s="140"/>
       <c r="K42" s="141"/>
+      <c r="O42" s="155">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="43" spans="1:20">
       <c r="A43" s="322" t="s">
         <v>892</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>909</v>
-      </c>
-      <c r="D43" s="79" t="e">
-        <f>E43*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>92</v>
+      </c>
+      <c r="D43" s="79">
+        <f>E43*(1+$T$1)</f>
+        <v>2</v>
       </c>
       <c r="E43" s="79">
         <f>AVERAGE(G43:Q43)</f>
-        <v>1.68</v>
-      </c>
-      <c r="F43" s="79" t="e">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="F43" s="79">
         <f>STDEV(G43:Q43)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G43" s="79"/>
-      <c r="H43" s="79"/>
+        <v>0.15275252316519469</v>
+      </c>
+      <c r="G43" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="H43" s="79">
+        <v>1.2</v>
+      </c>
       <c r="I43" s="79"/>
       <c r="J43" s="140"/>
       <c r="K43" s="141"/>
-      <c r="O43" s="155">
-        <v>1.68</v>
+      <c r="N43" s="155">
+        <v>1.5</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -35424,381 +35468,379 @@
         <v>892</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="D44" s="79">
         <f>E44*(1+$T$1)</f>
-        <v>2.8875000000000002</v>
+        <v>2</v>
       </c>
       <c r="E44" s="79">
         <f>AVERAGE(G44:Q44)</f>
-        <v>1.925</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="F44" s="79">
         <f>STDEV(G44:Q44)</f>
-        <v>0.38568121551353746</v>
+        <v>0.15275252316519469</v>
       </c>
       <c r="G44" s="79">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H44" s="79">
-        <v>1.95</v>
+        <v>1.2</v>
       </c>
       <c r="I44" s="79"/>
-      <c r="J44" s="140">
-        <v>2.25</v>
-      </c>
+      <c r="J44" s="140"/>
       <c r="K44" s="141"/>
-      <c r="L44" s="155">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="O44" s="155">
-        <v>2.25</v>
-      </c>
-      <c r="P44" s="155">
+      <c r="N44" s="155">
         <v>1.5</v>
       </c>
     </row>
     <row r="45" spans="1:20">
-      <c r="A45" s="156" t="s">
-        <v>55</v>
+      <c r="A45" s="322" t="s">
+        <v>892</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C45" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="D45" s="79">
         <f>E45*(1+$T$1)</f>
-        <v>1.8000000000000003</v>
+        <v>1.75</v>
       </c>
       <c r="E45" s="79">
         <f>AVERAGE(G45:Q45)</f>
-        <v>1.2000000000000002</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="F45" s="79">
         <f>STDEV(G45:Q45)</f>
-        <v>0.14142135623730948</v>
+        <v>0.15275252316519497</v>
       </c>
       <c r="G45" s="79">
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="H45" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="I45" s="157"/>
+        <v>1.2</v>
+      </c>
+      <c r="I45" s="79">
+        <v>1</v>
+      </c>
       <c r="J45" s="140"/>
       <c r="K45" s="141"/>
     </row>
     <row r="46" spans="1:20">
-      <c r="A46" s="156" t="s">
-        <v>30</v>
+      <c r="A46" s="322" t="s">
+        <v>892</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C46" t="s">
-        <v>38</v>
-      </c>
-      <c r="D46" s="79">
-        <f>E46*(1+$T$1)</f>
-        <v>1.875</v>
+        <v>909</v>
+      </c>
+      <c r="D46" s="79" t="e">
+        <f>E46*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E46" s="79">
         <f>AVERAGE(G46:Q46)</f>
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="F46" s="79" t="e">
         <f>STDEV(G46:Q46)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G46" s="140"/>
-      <c r="H46" s="140"/>
-      <c r="I46" s="157">
-        <v>1.25</v>
-      </c>
+      <c r="G46" s="79"/>
+      <c r="H46" s="79"/>
+      <c r="I46" s="79"/>
       <c r="J46" s="140"/>
       <c r="K46" s="141"/>
+      <c r="O46" s="155">
+        <v>1.68</v>
+      </c>
     </row>
     <row r="47" spans="1:20">
-      <c r="A47" s="156" t="s">
-        <v>142</v>
+      <c r="A47" s="322" t="s">
+        <v>892</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C47" t="s">
-        <v>936</v>
-      </c>
-      <c r="D47" s="79" t="e">
-        <f>E47*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>120</v>
+      </c>
+      <c r="D47" s="79">
+        <f>E47*(1+$T$1)</f>
+        <v>2.8875000000000002</v>
       </c>
       <c r="E47" s="79">
         <f>AVERAGE(G47:Q47)</f>
-        <v>1.4460000000000002</v>
+        <v>1.925</v>
       </c>
       <c r="F47" s="79">
         <f>STDEV(G47:Q47)</f>
-        <v>0.25510782034269269</v>
-      </c>
-      <c r="G47" s="140"/>
-      <c r="H47" s="140">
-        <v>1.3</v>
-      </c>
-      <c r="I47" s="157"/>
+        <v>0.38568121551353746</v>
+      </c>
+      <c r="G47" s="79">
+        <v>1.4</v>
+      </c>
+      <c r="H47" s="79">
+        <v>1.95</v>
+      </c>
+      <c r="I47" s="79"/>
       <c r="J47" s="140">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="K47" s="141"/>
-      <c r="N47" s="155">
-        <v>1.7</v>
+      <c r="L47" s="155">
+        <v>2.2000000000000002</v>
       </c>
       <c r="O47" s="155">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="P47" s="155">
-        <v>1.1000000000000001</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="48" spans="1:20">
       <c r="A48" s="156" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C48" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="D48" s="79">
         <f>E48*(1+$T$1)</f>
-        <v>1.5</v>
+        <v>1.8000000000000003</v>
       </c>
       <c r="E48" s="79">
         <f>AVERAGE(G48:Q48)</f>
-        <v>1</v>
-      </c>
-      <c r="F48" s="79" t="e">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="F48" s="79">
         <f>STDEV(G48:Q48)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G48" s="79"/>
-      <c r="H48" s="79"/>
-      <c r="I48" s="157">
-        <v>1</v>
-      </c>
+        <v>0.14142135623730948</v>
+      </c>
+      <c r="G48" s="79">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H48" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="I48" s="157"/>
       <c r="J48" s="140"/>
       <c r="K48" s="141"/>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="156" t="s">
-        <v>894</v>
+        <v>30</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C49" t="s">
-        <v>901</v>
-      </c>
-      <c r="D49" s="79" t="e">
-        <f>E49*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>38</v>
+      </c>
+      <c r="D49" s="79">
+        <f>E49*(1+$T$1)</f>
+        <v>1.875</v>
       </c>
       <c r="E49" s="79">
         <f>AVERAGE(G49:Q49)</f>
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="F49" s="79" t="e">
         <f>STDEV(G49:Q49)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G49" s="79"/>
-      <c r="H49" s="79"/>
-      <c r="I49" s="157"/>
+      <c r="G49" s="140"/>
+      <c r="H49" s="140"/>
+      <c r="I49" s="157">
+        <v>1.25</v>
+      </c>
       <c r="J49" s="140"/>
       <c r="K49" s="141"/>
-      <c r="O49" s="155">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="156" t="s">
         <v>142</v>
       </c>
       <c r="B50" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C50" t="s">
-        <v>136</v>
-      </c>
-      <c r="D50" s="79">
-        <f>E50*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>936</v>
+      </c>
+      <c r="D50" s="79" t="e">
+        <f>E50*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E50" s="79">
         <f>AVERAGE(G50:Q50)</f>
-        <v>1.5</v>
+        <v>1.4460000000000002</v>
       </c>
       <c r="F50" s="79">
         <f>STDEV(G50:Q50)</f>
-        <v>0.21602468994692911</v>
-      </c>
-      <c r="G50" s="79">
-        <f>14/10</f>
-        <v>1.4</v>
-      </c>
-      <c r="H50" s="79"/>
+        <v>0.25510782034269269</v>
+      </c>
+      <c r="G50" s="140"/>
+      <c r="H50" s="140">
+        <v>1.3</v>
+      </c>
       <c r="I50" s="157"/>
-      <c r="J50" s="140"/>
+      <c r="J50" s="140">
+        <v>1.45</v>
+      </c>
       <c r="K50" s="141"/>
       <c r="N50" s="155">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="O50" s="155">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="P50" s="155">
-        <v>1.5</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="156" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="D51" s="79">
         <f>E51*(1+$T$1)</f>
-        <v>2.2874999999999996</v>
+        <v>1.5</v>
       </c>
       <c r="E51" s="79">
         <f>AVERAGE(G51:Q51)</f>
-        <v>1.5249999999999999</v>
-      </c>
-      <c r="F51" s="79">
+        <v>1</v>
+      </c>
+      <c r="F51" s="79" t="e">
         <f>STDEV(G51:Q51)</f>
-        <v>0.60104076400856621</v>
-      </c>
-      <c r="G51" s="79">
-        <v>1.1000000000000001</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G51" s="79"/>
       <c r="H51" s="79"/>
-      <c r="I51" s="157"/>
+      <c r="I51" s="157">
+        <v>1</v>
+      </c>
       <c r="J51" s="140"/>
       <c r="K51" s="141"/>
-      <c r="O51" s="155">
-        <v>1.95</v>
-      </c>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="156" t="s">
-        <v>142</v>
+        <v>894</v>
       </c>
       <c r="B52" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C52" t="s">
-        <v>107</v>
-      </c>
-      <c r="D52" s="79">
-        <f>E52*(1+$T$1)</f>
-        <v>1.9500000000000002</v>
+        <v>901</v>
+      </c>
+      <c r="D52" s="79" t="e">
+        <f>E52*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E52" s="79">
         <f>AVERAGE(G52:Q52)</f>
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="F52" s="79" t="e">
         <f>STDEV(G52:Q52)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G52" s="79">
-        <v>1.3</v>
-      </c>
+      <c r="G52" s="79"/>
       <c r="H52" s="79"/>
       <c r="I52" s="157"/>
       <c r="J52" s="140"/>
       <c r="K52" s="141"/>
+      <c r="O52" s="155">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="156" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B53" t="s">
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="D53" s="79">
         <f>E53*(1+$T$1)</f>
-        <v>2.0249999999999999</v>
+        <v>2.25</v>
       </c>
       <c r="E53" s="79">
         <f>AVERAGE(G53:Q53)</f>
-        <v>1.3499999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="F53" s="79">
         <f>STDEV(G53:Q53)</f>
-        <v>0.68738635424337613</v>
+        <v>0.21602468994692911</v>
       </c>
       <c r="G53" s="79">
-        <v>1.5</v>
+        <f>14/10</f>
+        <v>1.4</v>
       </c>
       <c r="H53" s="79"/>
       <c r="I53" s="157"/>
       <c r="J53" s="140"/>
       <c r="K53" s="141"/>
+      <c r="N53" s="155">
+        <v>1.3</v>
+      </c>
       <c r="O53" s="155">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="P53" s="155">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="156" t="s">
-        <v>892</v>
+        <v>30</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C54" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="D54" s="79">
         <f>E54*(1+$T$1)</f>
-        <v>1.9899999999999998</v>
+        <v>2.2874999999999996</v>
       </c>
       <c r="E54" s="79">
         <f>AVERAGE(G54:Q54)</f>
-        <v>1.3266666666666664</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="F54" s="79">
         <f>STDEV(G54:Q54)</f>
-        <v>0.31005375877956043</v>
-      </c>
-      <c r="G54" s="79"/>
+        <v>0.60104076400856621</v>
+      </c>
+      <c r="G54" s="79">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="H54" s="79"/>
-      <c r="I54" s="157">
-        <v>1.2</v>
-      </c>
+      <c r="I54" s="157"/>
       <c r="J54" s="140"/>
       <c r="K54" s="141"/>
-      <c r="N54" s="155">
-        <v>1.1000000000000001</v>
-      </c>
       <c r="O54" s="155">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -35806,256 +35848,263 @@
         <v>142</v>
       </c>
       <c r="B55" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C55" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D55" s="79">
         <f>E55*(1+$T$1)</f>
-        <v>2.0250000000000004</v>
+        <v>1.9500000000000002</v>
       </c>
       <c r="E55" s="79">
         <f>AVERAGE(G55:Q55)</f>
-        <v>1.35</v>
-      </c>
-      <c r="F55" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="F55" s="79" t="e">
         <f>STDEV(G55:Q55)</f>
-        <v>0.21213203435596303</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G55" s="79">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H55" s="79"/>
       <c r="I55" s="157"/>
       <c r="J55" s="140"/>
       <c r="K55" s="141"/>
-      <c r="O55" s="155">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="156" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C56" t="s">
-        <v>910</v>
-      </c>
-      <c r="D56" s="79" t="e">
-        <f>E56*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>64</v>
+      </c>
+      <c r="D56" s="79">
+        <f>E56*(1+$T$1)</f>
+        <v>2.0249999999999999</v>
       </c>
       <c r="E56" s="79">
         <f>AVERAGE(G56:Q56)</f>
-        <v>1.89</v>
-      </c>
-      <c r="F56" s="79" t="e">
+        <v>1.3499999999999999</v>
+      </c>
+      <c r="F56" s="79">
         <f>STDEV(G56:Q56)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G56" s="79"/>
+        <v>0.68738635424337613</v>
+      </c>
+      <c r="G56" s="79">
+        <v>1.5</v>
+      </c>
       <c r="H56" s="79"/>
       <c r="I56" s="157"/>
       <c r="J56" s="140"/>
       <c r="K56" s="141"/>
       <c r="O56" s="155">
-        <v>1.89</v>
+        <v>1.95</v>
+      </c>
+      <c r="P56" s="155">
+        <v>0.6</v>
       </c>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="156" t="s">
-        <v>21</v>
+        <v>892</v>
       </c>
       <c r="B57" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="D57" s="79">
         <f>E57*(1+$T$1)</f>
-        <v>5.3625000000000007</v>
+        <v>1.9899999999999998</v>
       </c>
       <c r="E57" s="79">
         <f>AVERAGE(G57:Q57)</f>
-        <v>3.5750000000000002</v>
+        <v>1.3266666666666664</v>
       </c>
       <c r="F57" s="79">
         <f>STDEV(G57:Q57)</f>
-        <v>1.5202795795510775</v>
-      </c>
-      <c r="G57" s="140"/>
-      <c r="H57" s="140"/>
+        <v>0.31005375877956043</v>
+      </c>
+      <c r="G57" s="79"/>
+      <c r="H57" s="79"/>
       <c r="I57" s="157">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J57" s="140"/>
       <c r="K57" s="141"/>
+      <c r="N57" s="155">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="O57" s="155">
-        <v>4.6500000000000004</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B58" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C58" t="s">
-        <v>916</v>
+        <v>127</v>
       </c>
       <c r="D58" s="79">
         <f>E58*(1+$T$1)</f>
-        <v>6.0950000000000006</v>
+        <v>2.0250000000000004</v>
       </c>
       <c r="E58" s="79">
         <f>AVERAGE(G58:Q58)</f>
-        <v>4.0633333333333335</v>
+        <v>1.35</v>
       </c>
       <c r="F58" s="79">
         <f>STDEV(G58:Q58)</f>
-        <v>2.0895055236426936</v>
-      </c>
-      <c r="G58" s="79"/>
-      <c r="H58" s="79">
-        <v>1.79</v>
-      </c>
+        <v>0.21213203435596303</v>
+      </c>
+      <c r="G58" s="79">
+        <v>1.2</v>
+      </c>
+      <c r="H58" s="79"/>
       <c r="I58" s="157"/>
       <c r="J58" s="140"/>
       <c r="K58" s="141"/>
       <c r="O58" s="155">
-        <v>4.5</v>
-      </c>
-      <c r="P58" s="155">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C59" t="s">
-        <v>917</v>
-      </c>
-      <c r="D59" s="79">
-        <f>E59*(1+$T$1)</f>
-        <v>2.6850000000000001</v>
+        <v>910</v>
+      </c>
+      <c r="D59" s="79" t="e">
+        <f>E59*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E59" s="79">
         <f>AVERAGE(G59:Q59)</f>
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="F59" s="79" t="e">
         <f>STDEV(G59:Q59)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G59" s="79"/>
-      <c r="H59" s="79">
-        <v>1.79</v>
-      </c>
+      <c r="H59" s="79"/>
       <c r="I59" s="157"/>
       <c r="J59" s="140"/>
       <c r="K59" s="141"/>
+      <c r="O59" s="155">
+        <v>1.89</v>
+      </c>
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="156" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C60" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="D60" s="79">
         <f>E60*(1+$T$1)</f>
-        <v>2.0999999999999996</v>
+        <v>5.3625000000000007</v>
       </c>
       <c r="E60" s="79">
         <f>AVERAGE(G60:Q60)</f>
-        <v>1.4</v>
+        <v>3.5750000000000002</v>
       </c>
       <c r="F60" s="79">
         <f>STDEV(G60:Q60)</f>
-        <v>0.14142135623730948</v>
-      </c>
-      <c r="G60" s="79">
-        <v>1.5</v>
-      </c>
-      <c r="H60" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="I60" s="157"/>
+        <v>1.5202795795510775</v>
+      </c>
+      <c r="G60" s="140"/>
+      <c r="H60" s="140"/>
+      <c r="I60" s="157">
+        <v>2.5</v>
+      </c>
       <c r="J60" s="140"/>
       <c r="K60" s="141"/>
+      <c r="O60" s="155">
+        <v>4.6500000000000004</v>
+      </c>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="156" t="s">
-        <v>55</v>
+        <v>892</v>
       </c>
       <c r="B61" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C61" t="s">
-        <v>65</v>
+        <v>916</v>
       </c>
       <c r="D61" s="79">
         <f>E61*(1+$T$1)</f>
-        <v>2.0474999999999999</v>
+        <v>6.0950000000000006</v>
       </c>
       <c r="E61" s="79">
         <f>AVERAGE(G61:Q61)</f>
-        <v>1.365</v>
+        <v>4.0633333333333335</v>
       </c>
       <c r="F61" s="79">
         <f>STDEV(G61:Q61)</f>
-        <v>0.3323401871576776</v>
-      </c>
-      <c r="G61" s="79">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="H61" s="79"/>
+        <v>2.0895055236426936</v>
+      </c>
+      <c r="G61" s="79"/>
+      <c r="H61" s="79">
+        <v>1.79</v>
+      </c>
       <c r="I61" s="157"/>
       <c r="J61" s="140"/>
       <c r="K61" s="141"/>
       <c r="O61" s="155">
-        <v>1.6</v>
+        <v>4.5</v>
+      </c>
+      <c r="P61" s="155">
+        <v>5.9</v>
       </c>
     </row>
     <row r="62" spans="1:16">
       <c r="A62" s="156" t="s">
-        <v>55</v>
+        <v>892</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C62" t="s">
-        <v>66</v>
+        <v>917</v>
       </c>
       <c r="D62" s="79">
         <f>E62*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>2.6850000000000001</v>
       </c>
       <c r="E62" s="79">
         <f>AVERAGE(G62:Q62)</f>
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="F62" s="79" t="e">
         <f>STDEV(G62:Q62)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G62" s="140"/>
-      <c r="H62" s="140"/>
-      <c r="I62" s="157">
-        <v>1.5</v>
-      </c>
+      <c r="G62" s="79"/>
+      <c r="H62" s="79">
+        <v>1.79</v>
+      </c>
+      <c r="I62" s="157"/>
       <c r="J62" s="140"/>
       <c r="K62" s="141"/>
     </row>
@@ -36064,244 +36113,238 @@
         <v>142</v>
       </c>
       <c r="B63" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C63" t="s">
-        <v>108</v>
+        <v>941</v>
       </c>
       <c r="D63" s="79">
         <f>E63*(1+$T$1)</f>
-        <v>1.7999999999999998</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="E63" s="79">
         <f>AVERAGE(G63:Q63)</f>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="F63" s="79">
         <f>STDEV(G63:Q63)</f>
-        <v>0.36055512754639879</v>
+        <v>0.14142135623730948</v>
       </c>
       <c r="G63" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="H63" s="79">
         <v>1.3</v>
-      </c>
-      <c r="H63" s="79">
-        <v>0.8</v>
       </c>
       <c r="I63" s="157"/>
       <c r="J63" s="140"/>
       <c r="K63" s="141"/>
-      <c r="L63" s="155">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="156" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C64" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="D64" s="79">
         <f>E64*(1+$T$1)</f>
-        <v>1.7999999999999998</v>
+        <v>2.0474999999999999</v>
       </c>
       <c r="E64" s="79">
         <f>AVERAGE(G64:Q64)</f>
-        <v>1.2</v>
-      </c>
-      <c r="F64" s="79" t="e">
+        <v>1.365</v>
+      </c>
+      <c r="F64" s="79">
         <f>STDEV(G64:Q64)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G64" s="79"/>
+        <v>0.3323401871576776</v>
+      </c>
+      <c r="G64" s="79">
+        <v>1.1299999999999999</v>
+      </c>
       <c r="H64" s="79"/>
-      <c r="I64" s="157">
-        <v>1.2</v>
-      </c>
+      <c r="I64" s="157"/>
       <c r="J64" s="140"/>
       <c r="K64" s="141"/>
+      <c r="O64" s="155">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="156" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B65" t="s">
         <v>33</v>
       </c>
       <c r="C65" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D65" s="79">
         <f>E65*(1+$T$1)</f>
-        <v>4.0537499999999991</v>
+        <v>2.25</v>
       </c>
       <c r="E65" s="79">
         <f>AVERAGE(G65:Q65)</f>
-        <v>2.7024999999999997</v>
-      </c>
-      <c r="F65" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="F65" s="79" t="e">
         <f>STDEV(G65:Q65)</f>
-        <v>0.8266549058303202</v>
-      </c>
-      <c r="G65" s="79"/>
-      <c r="H65" s="79">
-        <v>3.6</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G65" s="140"/>
+      <c r="H65" s="140"/>
       <c r="I65" s="157">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J65" s="140"/>
       <c r="K65" s="141"/>
-      <c r="L65" s="155">
-        <v>2</v>
-      </c>
-      <c r="O65" s="155">
-        <v>3.21</v>
-      </c>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="156" t="s">
-        <v>894</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C66" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="D66" s="79">
         <f>E66*(1+$T$1)</f>
-        <v>1.9500000000000002</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="E66" s="79">
         <f>AVERAGE(G66:Q66)</f>
-        <v>1.3</v>
-      </c>
-      <c r="F66" s="79" t="e">
+        <v>1.2</v>
+      </c>
+      <c r="F66" s="79">
         <f>STDEV(G66:Q66)</f>
-        <v>#DIV/0!</v>
+        <v>0.36055512754639879</v>
       </c>
       <c r="G66" s="79">
         <v>1.3</v>
       </c>
-      <c r="H66" s="79"/>
+      <c r="H66" s="79">
+        <v>0.8</v>
+      </c>
       <c r="I66" s="157"/>
       <c r="J66" s="140"/>
       <c r="K66" s="141"/>
+      <c r="L66" s="155">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="156" t="s">
         <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C67" t="s">
-        <v>912</v>
-      </c>
-      <c r="D67" s="79" t="e">
-        <f>E67*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>99</v>
+      </c>
+      <c r="D67" s="79">
+        <f>E67*(1+$T$1)</f>
+        <v>1.7999999999999998</v>
       </c>
       <c r="E67" s="79">
         <f>AVERAGE(G67:Q67)</f>
-        <v>2.7850000000000001</v>
-      </c>
-      <c r="F67" s="79">
+        <v>1.2</v>
+      </c>
+      <c r="F67" s="79" t="e">
         <f>STDEV(G67:Q67)</f>
-        <v>2.0718510242453894</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G67" s="79"/>
-      <c r="H67" s="79">
-        <v>3.49</v>
-      </c>
-      <c r="I67" s="157"/>
+      <c r="H67" s="79"/>
+      <c r="I67" s="157">
+        <v>1.2</v>
+      </c>
       <c r="J67" s="140"/>
       <c r="K67" s="141"/>
-      <c r="L67" s="155">
-        <v>1</v>
-      </c>
-      <c r="N67" s="155">
-        <v>1.25</v>
-      </c>
-      <c r="O67" s="155">
-        <v>5.4</v>
-      </c>
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="156" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="B68" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C68" t="s">
-        <v>911</v>
-      </c>
-      <c r="D68" s="79" t="e">
-        <f>E68*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>35</v>
+      </c>
+      <c r="D68" s="79">
+        <f>E68*(1+$T$1)</f>
+        <v>4.0537499999999991</v>
       </c>
       <c r="E68" s="79">
         <f>AVERAGE(G68:Q68)</f>
-        <v>1.89</v>
-      </c>
-      <c r="F68" s="79" t="e">
+        <v>2.7024999999999997</v>
+      </c>
+      <c r="F68" s="79">
         <f>STDEV(G68:Q68)</f>
-        <v>#DIV/0!</v>
+        <v>0.8266549058303202</v>
       </c>
       <c r="G68" s="79"/>
-      <c r="H68" s="79"/>
-      <c r="I68" s="157"/>
+      <c r="H68" s="79">
+        <v>3.6</v>
+      </c>
+      <c r="I68" s="157">
+        <v>2</v>
+      </c>
       <c r="J68" s="140"/>
       <c r="K68" s="141"/>
+      <c r="L68" s="155">
+        <v>2</v>
+      </c>
       <c r="O68" s="155">
-        <v>1.89</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="156" t="s">
-        <v>142</v>
+        <v>894</v>
       </c>
       <c r="B69" t="s">
         <v>51</v>
       </c>
       <c r="C69" t="s">
-        <v>924</v>
-      </c>
-      <c r="D69" s="79" t="e">
-        <f>E69*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>137</v>
+      </c>
+      <c r="D69" s="79">
+        <f>E69*(1+$T$1)</f>
+        <v>1.9500000000000002</v>
       </c>
       <c r="E69" s="79">
         <f>AVERAGE(G69:Q69)</f>
-        <v>2.0699999999999998</v>
+        <v>1.3</v>
       </c>
       <c r="F69" s="79" t="e">
         <f>STDEV(G69:Q69)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G69" s="79"/>
+      <c r="G69" s="79">
+        <v>1.3</v>
+      </c>
       <c r="H69" s="79"/>
       <c r="I69" s="157"/>
       <c r="J69" s="140"/>
       <c r="K69" s="141"/>
-      <c r="O69" s="155">
-        <v>2.0699999999999998</v>
-      </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="156" t="s">
         <v>142</v>
       </c>
       <c r="B70" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C70" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
       <c r="D70" s="79" t="e">
         <f>E70*(1+$O$1)</f>
@@ -36309,24 +36352,27 @@
       </c>
       <c r="E70" s="79">
         <f>AVERAGE(G70:Q70)</f>
-        <v>1.2166666666666666</v>
+        <v>2.7850000000000001</v>
       </c>
       <c r="F70" s="79">
         <f>STDEV(G70:Q70)</f>
-        <v>0.17559422921421339</v>
+        <v>2.0718510242453894</v>
       </c>
       <c r="G70" s="79"/>
-      <c r="H70" s="79"/>
+      <c r="H70" s="79">
+        <v>3.49</v>
+      </c>
       <c r="I70" s="157"/>
-      <c r="J70" s="140">
-        <v>1.4</v>
-      </c>
+      <c r="J70" s="140"/>
       <c r="K70" s="141"/>
+      <c r="L70" s="155">
+        <v>1</v>
+      </c>
       <c r="N70" s="155">
-        <v>1.2</v>
-      </c>
-      <c r="P70" s="155">
-        <v>1.05</v>
+        <v>1.25</v>
+      </c>
+      <c r="O70" s="155">
+        <v>5.4</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -36337,153 +36383,155 @@
         <v>49</v>
       </c>
       <c r="C71" t="s">
-        <v>128</v>
-      </c>
-      <c r="D71" s="79">
-        <f>E71*(1+$T$1)</f>
-        <v>1.875</v>
+        <v>911</v>
+      </c>
+      <c r="D71" s="79" t="e">
+        <f>E71*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E71" s="79">
         <f>AVERAGE(G71:Q71)</f>
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="F71" s="79" t="e">
         <f>STDEV(G71:Q71)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G71" s="140"/>
-      <c r="H71" s="140"/>
-      <c r="I71" s="157">
-        <v>1.25</v>
-      </c>
+      <c r="G71" s="79"/>
+      <c r="H71" s="79"/>
+      <c r="I71" s="157"/>
       <c r="J71" s="140"/>
       <c r="K71" s="141"/>
+      <c r="O71" s="155">
+        <v>1.89</v>
+      </c>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="156" t="s">
         <v>142</v>
       </c>
       <c r="B72" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C72" t="s">
-        <v>100</v>
-      </c>
-      <c r="D72" s="79">
-        <f>E72*(1+$T$1)</f>
-        <v>4.0649999999999995</v>
+        <v>924</v>
+      </c>
+      <c r="D72" s="79" t="e">
+        <f>E72*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E72" s="79">
         <f>AVERAGE(G72:Q72)</f>
-        <v>2.71</v>
+        <v>1.7849999999999999</v>
       </c>
       <c r="F72" s="79">
         <f>STDEV(G72:Q72)</f>
-        <v>0.74542413621853099</v>
-      </c>
-      <c r="G72" s="79">
-        <v>2.5</v>
-      </c>
-      <c r="H72" s="79">
-        <v>3.5</v>
-      </c>
+        <v>0.40305086527633177</v>
+      </c>
+      <c r="G72" s="79"/>
+      <c r="H72" s="79"/>
       <c r="I72" s="157">
-        <v>2.5</v>
-      </c>
-      <c r="J72" s="140">
-        <v>2.5</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="J72" s="140"/>
       <c r="K72" s="141"/>
-      <c r="L72" s="155">
-        <v>3</v>
-      </c>
-      <c r="N72" s="155">
-        <v>1.18</v>
-      </c>
       <c r="O72" s="155">
-        <v>3</v>
-      </c>
-      <c r="P72" s="155">
-        <v>3.5</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="156" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="B73" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C73" t="s">
-        <v>44</v>
-      </c>
-      <c r="D73" s="79">
-        <f>E73*(1+$T$1)</f>
-        <v>1.875</v>
+        <v>930</v>
+      </c>
+      <c r="D73" s="79" t="e">
+        <f>E73*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E73" s="79">
         <f>AVERAGE(G73:Q73)</f>
-        <v>1.25</v>
-      </c>
-      <c r="F73" s="79" t="e">
+        <v>1.2874999999999999</v>
+      </c>
+      <c r="F73" s="79">
         <f>STDEV(G73:Q73)</f>
-        <v>#DIV/0!</v>
+        <v>0.20155644370746537</v>
       </c>
       <c r="G73" s="79"/>
       <c r="H73" s="79"/>
       <c r="I73" s="157">
-        <v>1.25</v>
-      </c>
-      <c r="J73" s="140"/>
+        <v>1.5</v>
+      </c>
+      <c r="J73" s="140">
+        <v>1.4</v>
+      </c>
       <c r="K73" s="141"/>
+      <c r="N73" s="155">
+        <v>1.2</v>
+      </c>
+      <c r="P73" s="155">
+        <v>1.05</v>
+      </c>
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="156" t="s">
         <v>142</v>
       </c>
       <c r="B74" t="s">
-        <v>33</v>
-      </c>
-      <c r="C74" s="66" t="s">
-        <v>101</v>
-      </c>
-      <c r="D74" s="79">
-        <f>E74*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>49</v>
+      </c>
+      <c r="C74" t="s">
+        <v>930</v>
+      </c>
+      <c r="D74" s="79" t="e">
+        <f>E74*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E74" s="79">
         <f>AVERAGE(G74:Q74)</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F74" s="79" t="e">
+        <v>1.2874999999999999</v>
+      </c>
+      <c r="F74" s="79">
         <f>STDEV(G74:Q74)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G74" s="140"/>
-      <c r="H74" s="140"/>
+        <v>0.20155644370746537</v>
+      </c>
+      <c r="G74" s="79"/>
+      <c r="H74" s="79"/>
       <c r="I74" s="157">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J74" s="140"/>
+        <v>1.5</v>
+      </c>
+      <c r="J74" s="140">
+        <v>1.4</v>
+      </c>
       <c r="K74" s="141"/>
+      <c r="N74" s="155">
+        <v>1.2</v>
+      </c>
+      <c r="P74" s="155">
+        <v>1.05</v>
+      </c>
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="156" t="s">
         <v>142</v>
       </c>
       <c r="B75" t="s">
-        <v>41</v>
-      </c>
-      <c r="C75" s="66" t="s">
-        <v>101</v>
+        <v>49</v>
+      </c>
+      <c r="C75" t="s">
+        <v>128</v>
       </c>
       <c r="D75" s="79">
         <f>E75*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>1.875</v>
       </c>
       <c r="E75" s="79">
         <f>AVERAGE(G75:Q75)</f>
-        <v>1.1000000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="F75" s="79" t="e">
         <f>STDEV(G75:Q75)</f>
@@ -36492,7 +36540,7 @@
       <c r="G75" s="140"/>
       <c r="H75" s="140"/>
       <c r="I75" s="157">
-        <v>1.1000000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="J75" s="140"/>
       <c r="K75" s="141"/>
@@ -36502,442 +36550,452 @@
         <v>142</v>
       </c>
       <c r="B76" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C76" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="D76" s="79">
         <f>E76*(1+$T$1)</f>
-        <v>1.875</v>
+        <v>4.0649999999999995</v>
       </c>
       <c r="E76" s="79">
         <f>AVERAGE(G76:Q76)</f>
-        <v>1.25</v>
+        <v>2.71</v>
       </c>
       <c r="F76" s="79">
         <f>STDEV(G76:Q76)</f>
-        <v>0.35355339059327379</v>
-      </c>
-      <c r="G76" s="79"/>
-      <c r="H76" s="79"/>
+        <v>0.74542413621853099</v>
+      </c>
+      <c r="G76" s="79">
+        <v>2.5</v>
+      </c>
+      <c r="H76" s="79">
+        <v>3.5</v>
+      </c>
       <c r="I76" s="157">
-        <v>1</v>
-      </c>
-      <c r="J76" s="140"/>
+        <v>2.5</v>
+      </c>
+      <c r="J76" s="140">
+        <v>2.5</v>
+      </c>
       <c r="K76" s="141"/>
+      <c r="L76" s="155">
+        <v>3</v>
+      </c>
+      <c r="N76" s="155">
+        <v>1.18</v>
+      </c>
       <c r="O76" s="155">
-        <v>1.5</v>
+        <v>3</v>
+      </c>
+      <c r="P76" s="155">
+        <v>3.5</v>
       </c>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="156" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B77" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C77" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D77" s="79">
         <f>E77*(1+$T$1)</f>
-        <v>2.69</v>
+        <v>1.875</v>
       </c>
       <c r="E77" s="79">
         <f>AVERAGE(G77:Q77)</f>
-        <v>1.7933333333333332</v>
-      </c>
-      <c r="F77" s="79">
+        <v>1.25</v>
+      </c>
+      <c r="F77" s="79" t="e">
         <f>STDEV(G77:Q77)</f>
-        <v>0.35795716689756812</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G77" s="79"/>
-      <c r="H77" s="79">
-        <v>1.4</v>
-      </c>
-      <c r="I77" s="157"/>
+      <c r="H77" s="79"/>
+      <c r="I77" s="157">
+        <v>1.25</v>
+      </c>
       <c r="J77" s="140"/>
       <c r="K77" s="141"/>
-      <c r="O77" s="155">
-        <v>2.1</v>
-      </c>
-      <c r="P77" s="155">
-        <v>1.88</v>
-      </c>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="156" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B78" t="s">
         <v>33</v>
       </c>
-      <c r="C78" t="s">
-        <v>68</v>
+      <c r="C78" s="66" t="s">
+        <v>101</v>
       </c>
       <c r="D78" s="79">
         <f>E78*(1+$T$1)</f>
-        <v>4.59</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="E78" s="79">
         <f>AVERAGE(G78:Q78)</f>
-        <v>3.06</v>
-      </c>
-      <c r="F78" s="79">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F78" s="79" t="e">
         <f>STDEV(G78:Q78)</f>
-        <v>1.0053854982045451</v>
-      </c>
-      <c r="G78" s="79"/>
-      <c r="H78" s="79">
-        <v>4</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G78" s="140"/>
+      <c r="H78" s="140"/>
       <c r="I78" s="157">
-        <v>2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J78" s="140"/>
       <c r="K78" s="141"/>
-      <c r="O78" s="155">
-        <v>3.18</v>
-      </c>
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="156" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B79" t="s">
-        <v>49</v>
-      </c>
-      <c r="C79" t="s">
-        <v>68</v>
+        <v>41</v>
+      </c>
+      <c r="C79" s="66" t="s">
+        <v>101</v>
       </c>
       <c r="D79" s="79">
         <f>E79*(1+$T$1)</f>
-        <v>4.59</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="E79" s="79">
         <f>AVERAGE(G79:Q79)</f>
-        <v>3.06</v>
-      </c>
-      <c r="F79" s="79">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F79" s="79" t="e">
         <f>STDEV(G79:Q79)</f>
-        <v>1.0053854982045451</v>
-      </c>
-      <c r="G79" s="79"/>
-      <c r="H79" s="79">
-        <v>4</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G79" s="140"/>
+      <c r="H79" s="140"/>
       <c r="I79" s="157">
-        <v>2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J79" s="140"/>
       <c r="K79" s="141"/>
-      <c r="O79" s="155">
-        <v>3.18</v>
-      </c>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="156" t="s">
         <v>142</v>
       </c>
       <c r="B80" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C80" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="D80" s="79">
         <f>E80*(1+$T$1)</f>
-        <v>3.7232142857142856</v>
+        <v>1.875</v>
       </c>
       <c r="E80" s="79">
         <f>AVERAGE(G80:Q80)</f>
-        <v>2.4821428571428572</v>
+        <v>1.25</v>
       </c>
       <c r="F80" s="79">
         <f>STDEV(G80:Q80)</f>
-        <v>0.50347010125442637</v>
-      </c>
-      <c r="G80" s="79">
-        <f>17.25/10</f>
-        <v>1.7250000000000001</v>
-      </c>
-      <c r="H80" s="79">
-        <v>2.7</v>
-      </c>
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="G80" s="79"/>
+      <c r="H80" s="79"/>
       <c r="I80" s="157">
-        <v>2.5</v>
-      </c>
-      <c r="J80" s="140">
-        <v>2.6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J80" s="140"/>
       <c r="K80" s="141"/>
-      <c r="L80" s="155">
-        <v>2.8</v>
-      </c>
       <c r="O80" s="155">
-        <v>3.15</v>
-      </c>
-      <c r="P80" s="155">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16">
       <c r="A81" s="156" t="s">
-        <v>892</v>
+        <v>55</v>
       </c>
       <c r="B81" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="D81" s="79">
         <f>E81*(1+$T$1)</f>
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="E81" s="79">
         <f>AVERAGE(G81:Q81)</f>
-        <v>1.9000000000000001</v>
+        <v>1.7933333333333332</v>
       </c>
       <c r="F81" s="79">
         <f>STDEV(G81:Q81)</f>
-        <v>0.34999999999999942</v>
-      </c>
-      <c r="G81" s="79">
-        <v>1.55</v>
-      </c>
+        <v>0.35795716689756812</v>
+      </c>
+      <c r="G81" s="79"/>
       <c r="H81" s="79">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="I81" s="157"/>
       <c r="J81" s="140"/>
       <c r="K81" s="141"/>
       <c r="O81" s="155">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15">
+        <v>2.1</v>
+      </c>
+      <c r="P81" s="155">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16">
       <c r="A82" s="156" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B82" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C82" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D82" s="79">
         <f>E82*(1+$T$1)</f>
-        <v>2.4375</v>
+        <v>5.3849999999999998</v>
       </c>
       <c r="E82" s="79">
         <f>AVERAGE(G82:Q82)</f>
-        <v>1.625</v>
+        <v>3.59</v>
       </c>
       <c r="F82" s="79">
         <f>STDEV(G82:Q82)</f>
-        <v>0.17677669529663689</v>
+        <v>0.57982756057297036</v>
       </c>
       <c r="G82" s="79"/>
-      <c r="H82" s="79"/>
-      <c r="I82" s="157">
-        <v>1.5</v>
-      </c>
+      <c r="H82" s="79">
+        <v>4</v>
+      </c>
+      <c r="I82" s="157"/>
       <c r="J82" s="140"/>
       <c r="K82" s="141"/>
       <c r="O82" s="155">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16">
       <c r="A83" s="156" t="s">
-        <v>894</v>
+        <v>55</v>
       </c>
       <c r="B83" t="s">
         <v>49</v>
       </c>
       <c r="C83" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="D83" s="79">
         <f>E83*(1+$T$1)</f>
-        <v>2.0625</v>
+        <v>5.3849999999999998</v>
       </c>
       <c r="E83" s="79">
         <f>AVERAGE(G83:Q83)</f>
-        <v>1.375</v>
+        <v>3.59</v>
       </c>
       <c r="F83" s="79">
         <f>STDEV(G83:Q83)</f>
-        <v>0.17677669529663689</v>
-      </c>
-      <c r="G83" s="79">
-        <v>1.25</v>
-      </c>
-      <c r="H83" s="79"/>
+        <v>0.57982756057297036</v>
+      </c>
+      <c r="G83" s="79"/>
+      <c r="H83" s="79">
+        <v>4</v>
+      </c>
       <c r="I83" s="157"/>
       <c r="J83" s="140"/>
       <c r="K83" s="141"/>
       <c r="O83" s="155">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
       <c r="A84" s="156" t="s">
         <v>142</v>
       </c>
       <c r="B84" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C84" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="D84" s="79">
         <f>E84*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>3.7232142857142856</v>
       </c>
       <c r="E84" s="79">
         <f>AVERAGE(G84:Q84)</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F84" s="79" t="e">
+        <v>2.4821428571428572</v>
+      </c>
+      <c r="F84" s="79">
         <f>STDEV(G84:Q84)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G84" s="140"/>
-      <c r="H84" s="140"/>
+        <v>0.50347010125442637</v>
+      </c>
+      <c r="G84" s="79">
+        <f>17.25/10</f>
+        <v>1.7250000000000001</v>
+      </c>
+      <c r="H84" s="79">
+        <v>2.7</v>
+      </c>
       <c r="I84" s="157">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J84" s="140"/>
+        <v>2.5</v>
+      </c>
+      <c r="J84" s="140">
+        <v>2.6</v>
+      </c>
       <c r="K84" s="141"/>
-    </row>
-    <row r="85" spans="1:15">
+      <c r="L84" s="155">
+        <v>2.8</v>
+      </c>
+      <c r="O84" s="155">
+        <v>3.15</v>
+      </c>
+      <c r="P84" s="155">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16">
       <c r="A85" s="156" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B85" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C85" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D85" s="79">
         <f>E85*(1+$T$1)</f>
-        <v>1.5</v>
+        <v>2.85</v>
       </c>
       <c r="E85" s="79">
         <f>AVERAGE(G85:Q85)</f>
-        <v>1</v>
-      </c>
-      <c r="F85" s="79" t="e">
+        <v>1.9000000000000001</v>
+      </c>
+      <c r="F85" s="79">
         <f>STDEV(G85:Q85)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G85" s="140"/>
-      <c r="H85" s="140"/>
-      <c r="I85" s="157">
-        <v>1</v>
-      </c>
+        <v>0.34999999999999942</v>
+      </c>
+      <c r="G85" s="79">
+        <v>1.55</v>
+      </c>
+      <c r="H85" s="79">
+        <v>1.9</v>
+      </c>
+      <c r="I85" s="157"/>
       <c r="J85" s="140"/>
       <c r="K85" s="141"/>
-    </row>
-    <row r="86" spans="1:15">
+      <c r="O85" s="155">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16">
       <c r="A86" s="156" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B86" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C86" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="D86" s="79">
         <f>E86*(1+$T$1)</f>
-        <v>3.7874999999999996</v>
+        <v>2.4375</v>
       </c>
       <c r="E86" s="79">
         <f>AVERAGE(G86:Q86)</f>
-        <v>2.5249999999999999</v>
+        <v>1.625</v>
       </c>
       <c r="F86" s="79">
         <f>STDEV(G86:Q86)</f>
-        <v>1.7324116139070416</v>
-      </c>
-      <c r="G86" s="79">
-        <v>1.3</v>
-      </c>
+        <v>0.17677669529663689</v>
+      </c>
+      <c r="G86" s="79"/>
       <c r="H86" s="79"/>
-      <c r="I86" s="157"/>
+      <c r="I86" s="157">
+        <v>1.5</v>
+      </c>
       <c r="J86" s="140"/>
       <c r="K86" s="141"/>
       <c r="O86" s="155">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16">
       <c r="A87" s="156" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B87" t="s">
         <v>49</v>
       </c>
       <c r="C87" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D87" s="79">
         <f>E87*(1+$T$1)</f>
-        <v>3.75</v>
+        <v>2.0625</v>
       </c>
       <c r="E87" s="79">
         <f>AVERAGE(G87:Q87)</f>
-        <v>2.5</v>
-      </c>
-      <c r="F87" s="79" t="e">
+        <v>1.375</v>
+      </c>
+      <c r="F87" s="79">
         <f>STDEV(G87:Q87)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G87" s="79"/>
+        <v>0.17677669529663689</v>
+      </c>
+      <c r="G87" s="79">
+        <v>1.25</v>
+      </c>
       <c r="H87" s="79"/>
-      <c r="I87" s="157">
-        <v>2.5</v>
-      </c>
+      <c r="I87" s="157"/>
       <c r="J87" s="140"/>
       <c r="K87" s="141"/>
-    </row>
-    <row r="88" spans="1:15">
+      <c r="O87" s="155">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
       <c r="A88" s="156" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="B88" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C88" t="s">
-        <v>925</v>
-      </c>
-      <c r="D88" s="79" t="e">
-        <f>E88*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>130</v>
+      </c>
+      <c r="D88" s="79">
+        <f>E88*(1+$T$1)</f>
+        <v>1.6500000000000001</v>
       </c>
       <c r="E88" s="79">
         <f>AVERAGE(G88:Q88)</f>
-        <v>1.96</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F88" s="79" t="e">
         <f>STDEV(G88:Q88)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G88" s="79"/>
-      <c r="H88" s="79"/>
-      <c r="I88" s="157"/>
+      <c r="G88" s="140"/>
+      <c r="H88" s="140"/>
+      <c r="I88" s="157">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="J88" s="140"/>
       <c r="K88" s="141"/>
-      <c r="O88" s="155">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15">
+    </row>
+    <row r="89" spans="1:16">
       <c r="A89" s="156" t="s">
         <v>894</v>
       </c>
@@ -36945,15 +37003,15 @@
         <v>51</v>
       </c>
       <c r="C89" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D89" s="79">
         <f>E89*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="E89" s="79">
         <f>AVERAGE(G89:Q89)</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F89" s="79" t="e">
         <f>STDEV(G89:Q89)</f>
@@ -36962,265 +37020,239 @@
       <c r="G89" s="140"/>
       <c r="H89" s="140"/>
       <c r="I89" s="157">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J89" s="140"/>
       <c r="K89" s="141"/>
     </row>
-    <row r="90" spans="1:15">
+    <row r="90" spans="1:16">
       <c r="A90" s="156" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B90" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C90" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="D90" s="79">
         <f>E90*(1+$T$1)</f>
-        <v>2.65</v>
+        <v>3.2749999999999995</v>
       </c>
       <c r="E90" s="79">
         <f>AVERAGE(G90:Q90)</f>
-        <v>1.7666666666666666</v>
+        <v>2.1833333333333331</v>
       </c>
       <c r="F90" s="79">
         <f>STDEV(G90:Q90)</f>
-        <v>0.2516611478423586</v>
-      </c>
-      <c r="G90" s="79"/>
-      <c r="H90" s="79">
-        <v>1.8</v>
-      </c>
-      <c r="I90" s="157"/>
+        <v>1.3604533558095018</v>
+      </c>
+      <c r="G90" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="H90" s="79"/>
+      <c r="I90" s="157">
+        <v>1.5</v>
+      </c>
       <c r="J90" s="140"/>
       <c r="K90" s="141"/>
-      <c r="L90" s="155">
-        <v>2</v>
-      </c>
       <c r="O90" s="155">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
       <c r="A91" s="156" t="s">
-        <v>21</v>
+        <v>892</v>
       </c>
       <c r="B91" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C91" t="s">
-        <v>29</v>
+        <v>121</v>
       </c>
       <c r="D91" s="79">
         <f>E91*(1+$T$1)</f>
-        <v>1.855</v>
+        <v>3.75</v>
       </c>
       <c r="E91" s="79">
         <f>AVERAGE(G91:Q91)</f>
-        <v>1.2366666666666666</v>
-      </c>
-      <c r="F91" s="79">
+        <v>2.5</v>
+      </c>
+      <c r="F91" s="79" t="e">
         <f>STDEV(G91:Q91)</f>
-        <v>0.42193996413392026</v>
-      </c>
-      <c r="G91" s="79">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H91" s="79">
-        <v>0.9</v>
-      </c>
-      <c r="I91" s="157"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G91" s="79"/>
+      <c r="H91" s="79"/>
+      <c r="I91" s="157">
+        <v>2.5</v>
+      </c>
       <c r="J91" s="140"/>
       <c r="K91" s="141"/>
-      <c r="O91" s="155">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15">
+    </row>
+    <row r="92" spans="1:16">
       <c r="A92" s="156" t="s">
-        <v>894</v>
+        <v>30</v>
       </c>
       <c r="B92" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C92" t="s">
-        <v>117</v>
-      </c>
-      <c r="D92" s="79">
-        <f>E92*(1+$T$1)</f>
-        <v>1.6124999999999998</v>
+        <v>925</v>
+      </c>
+      <c r="D92" s="79" t="e">
+        <f>E92*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E92" s="79">
         <f>AVERAGE(G92:Q92)</f>
-        <v>1.075</v>
-      </c>
-      <c r="F92" s="79">
+        <v>1.96</v>
+      </c>
+      <c r="F92" s="79" t="e">
         <f>STDEV(G92:Q92)</f>
-        <v>0.24748737341529214</v>
-      </c>
-      <c r="G92" s="79">
-        <v>1.25</v>
-      </c>
-      <c r="H92" s="79">
-        <v>0.9</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G92" s="79"/>
+      <c r="H92" s="79"/>
       <c r="I92" s="157"/>
       <c r="J92" s="140"/>
       <c r="K92" s="141"/>
-    </row>
-    <row r="93" spans="1:15">
+      <c r="O92" s="155">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
       <c r="A93" s="156" t="s">
-        <v>55</v>
+        <v>894</v>
       </c>
       <c r="B93" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C93" t="s">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="D93" s="79">
         <f>E93*(1+$T$1)</f>
-        <v>6.0187500000000007</v>
+        <v>2.25</v>
       </c>
       <c r="E93" s="79">
         <f>AVERAGE(G93:Q93)</f>
-        <v>4.0125000000000002</v>
-      </c>
-      <c r="F93" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="F93" s="79" t="e">
         <f>STDEV(G93:Q93)</f>
-        <v>0.37052890125692844</v>
-      </c>
-      <c r="G93" s="79">
-        <v>4</v>
-      </c>
-      <c r="H93" s="79">
-        <v>3.95</v>
-      </c>
-      <c r="I93" s="157"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G93" s="140"/>
+      <c r="H93" s="140"/>
+      <c r="I93" s="157">
+        <v>1.5</v>
+      </c>
       <c r="J93" s="140"/>
       <c r="K93" s="141"/>
-      <c r="L93" s="155">
-        <v>4.5</v>
-      </c>
-      <c r="O93" s="155">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15">
+    </row>
+    <row r="94" spans="1:16">
       <c r="A94" s="156" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B94" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C94" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D94" s="79">
         <f>E94*(1+$T$1)</f>
-        <v>6.3937500000000007</v>
+        <v>2.65</v>
       </c>
       <c r="E94" s="79">
         <f>AVERAGE(G94:Q94)</f>
-        <v>4.2625000000000002</v>
+        <v>1.7666666666666666</v>
       </c>
       <c r="F94" s="79">
         <f>STDEV(G94:Q94)</f>
-        <v>0.58789880081524093</v>
-      </c>
-      <c r="G94" s="79">
-        <v>4</v>
-      </c>
+        <v>0.2516611478423586</v>
+      </c>
+      <c r="G94" s="79"/>
       <c r="H94" s="79">
-        <v>4.95</v>
+        <v>1.8</v>
       </c>
       <c r="I94" s="157"/>
       <c r="J94" s="140"/>
       <c r="K94" s="141"/>
       <c r="L94" s="155">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="O94" s="155">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
       <c r="A95" s="156" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="B95" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C95" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D95" s="79">
         <f>E95*(1+$T$1)</f>
-        <v>5.9287499999999991</v>
+        <v>1.855</v>
       </c>
       <c r="E95" s="79">
         <f>AVERAGE(G95:Q95)</f>
-        <v>3.9524999999999997</v>
+        <v>1.2366666666666666</v>
       </c>
       <c r="F95" s="79">
         <f>STDEV(G95:Q95)</f>
-        <v>0.46657439563982656</v>
+        <v>0.42193996413392026</v>
       </c>
       <c r="G95" s="79">
-        <v>4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H95" s="79">
-        <v>3.95</v>
+        <v>0.9</v>
       </c>
       <c r="I95" s="157"/>
       <c r="J95" s="140"/>
       <c r="K95" s="141"/>
-      <c r="L95" s="155">
-        <v>4.5</v>
-      </c>
       <c r="O95" s="155">
-        <v>3.36</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16">
       <c r="A96" s="156" t="s">
-        <v>55</v>
+        <v>894</v>
       </c>
       <c r="B96" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C96" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D96" s="79">
         <f>E96*(1+$T$1)</f>
-        <v>5.4224999999999994</v>
+        <v>1.6124999999999998</v>
       </c>
       <c r="E96" s="79">
         <f>AVERAGE(G96:Q96)</f>
-        <v>3.6149999999999998</v>
+        <v>1.075</v>
       </c>
       <c r="F96" s="79">
         <f>STDEV(G96:Q96)</f>
-        <v>0.63945289114992876</v>
+        <v>0.24748737341529214</v>
       </c>
       <c r="G96" s="79">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="H96" s="79">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="I96" s="157"/>
       <c r="J96" s="140"/>
       <c r="K96" s="141"/>
-      <c r="L96" s="155">
-        <v>4.5</v>
-      </c>
-      <c r="O96" s="155">
-        <v>3.36</v>
-      </c>
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="156" t="s">
@@ -37230,25 +37262,25 @@
         <v>22</v>
       </c>
       <c r="C97" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D97" s="79">
         <f>E97*(1+$T$1)</f>
-        <v>5.4412500000000001</v>
+        <v>6.0187500000000007</v>
       </c>
       <c r="E97" s="79">
         <f>AVERAGE(G97:Q97)</f>
-        <v>3.6274999999999999</v>
+        <v>4.0125000000000002</v>
       </c>
       <c r="F97" s="79">
         <f>STDEV(G97:Q97)</f>
-        <v>0.63955062348495895</v>
+        <v>0.37052890125692844</v>
       </c>
       <c r="G97" s="79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H97" s="79">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="I97" s="157"/>
       <c r="J97" s="140"/>
@@ -37257,177 +37289,190 @@
         <v>4.5</v>
       </c>
       <c r="O97" s="155">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="156" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B98" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C98" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="D98" s="79">
         <f>E98*(1+$T$1)</f>
-        <v>1.875</v>
+        <v>6.3937500000000007</v>
       </c>
       <c r="E98" s="79">
         <f>AVERAGE(G98:Q98)</f>
-        <v>1.25</v>
-      </c>
-      <c r="F98" s="79" t="e">
+        <v>4.2625000000000002</v>
+      </c>
+      <c r="F98" s="79">
         <f>STDEV(G98:Q98)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G98" s="140"/>
-      <c r="H98" s="140"/>
-      <c r="I98" s="157">
-        <v>1.25</v>
-      </c>
+        <v>0.58789880081524093</v>
+      </c>
+      <c r="G98" s="79">
+        <v>4</v>
+      </c>
+      <c r="H98" s="79">
+        <v>4.95</v>
+      </c>
+      <c r="I98" s="157"/>
       <c r="J98" s="140"/>
       <c r="K98" s="141"/>
+      <c r="L98" s="155">
+        <v>4.5</v>
+      </c>
+      <c r="O98" s="155">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="156" t="s">
-        <v>892</v>
+        <v>55</v>
       </c>
       <c r="B99" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C99" t="s">
-        <v>913</v>
-      </c>
-      <c r="D99" s="79" t="e">
-        <f>E99*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>72</v>
+      </c>
+      <c r="D99" s="79">
+        <f>E99*(1+$T$1)</f>
+        <v>5.9287499999999991</v>
       </c>
       <c r="E99" s="79">
         <f>AVERAGE(G99:Q99)</f>
-        <v>1.65</v>
+        <v>3.9524999999999997</v>
       </c>
       <c r="F99" s="79">
         <f>STDEV(G99:Q99)</f>
-        <v>0.21213203435596428</v>
-      </c>
-      <c r="G99" s="140"/>
-      <c r="H99" s="140"/>
+        <v>0.46657439563982656</v>
+      </c>
+      <c r="G99" s="79">
+        <v>4</v>
+      </c>
+      <c r="H99" s="79">
+        <v>3.95</v>
+      </c>
       <c r="I99" s="157"/>
       <c r="J99" s="140"/>
       <c r="K99" s="141"/>
-      <c r="N99" s="155">
-        <v>1.5</v>
+      <c r="L99" s="155">
+        <v>4.5</v>
       </c>
       <c r="O99" s="155">
-        <v>1.8</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="156" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B100" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C100" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D100" s="79">
         <f>E100*(1+$T$1)</f>
-        <v>2.8125</v>
+        <v>5.4224999999999994</v>
       </c>
       <c r="E100" s="79">
         <f>AVERAGE(G100:Q100)</f>
-        <v>1.875</v>
+        <v>3.6149999999999998</v>
       </c>
       <c r="F100" s="79">
         <f>STDEV(G100:Q100)</f>
-        <v>0.5303300858899106</v>
-      </c>
-      <c r="G100" s="79"/>
-      <c r="H100" s="79"/>
-      <c r="I100" s="157">
-        <f>15/10</f>
-        <v>1.5</v>
-      </c>
+        <v>0.63945289114992876</v>
+      </c>
+      <c r="G100" s="79">
+        <v>3</v>
+      </c>
+      <c r="H100" s="79">
+        <v>3.6</v>
+      </c>
+      <c r="I100" s="157"/>
       <c r="J100" s="140"/>
       <c r="K100" s="141"/>
+      <c r="L100" s="155">
+        <v>4.5</v>
+      </c>
       <c r="O100" s="155">
-        <v>2.25</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="156" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B101" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="D101" s="79">
         <f>E101*(1+$T$1)</f>
-        <v>2.2874999999999996</v>
+        <v>5.4412500000000001</v>
       </c>
       <c r="E101" s="79">
         <f>AVERAGE(G101:Q101)</f>
-        <v>1.5249999999999999</v>
+        <v>3.6274999999999999</v>
       </c>
       <c r="F101" s="79">
         <f>STDEV(G101:Q101)</f>
-        <v>0.60104076400856621</v>
-      </c>
-      <c r="G101" s="79"/>
-      <c r="H101" s="79"/>
-      <c r="I101" s="157">
-        <v>1.1000000000000001</v>
-      </c>
+        <v>0.63955062348495895</v>
+      </c>
+      <c r="G101" s="79">
+        <v>3</v>
+      </c>
+      <c r="H101" s="79">
+        <v>3.65</v>
+      </c>
+      <c r="I101" s="157"/>
       <c r="J101" s="140"/>
       <c r="K101" s="141"/>
+      <c r="L101" s="155">
+        <v>4.5</v>
+      </c>
       <c r="O101" s="155">
-        <v>1.95</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="156" t="s">
-        <v>892</v>
+        <v>21</v>
       </c>
       <c r="B102" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C102" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="D102" s="79">
         <f>E102*(1+$T$1)</f>
-        <v>2.1975000000000002</v>
+        <v>1.875</v>
       </c>
       <c r="E102" s="79">
         <f>AVERAGE(G102:Q102)</f>
-        <v>1.4650000000000001</v>
-      </c>
-      <c r="F102" s="79">
+        <v>1.25</v>
+      </c>
+      <c r="F102" s="79" t="e">
         <f>STDEV(G102:Q102)</f>
-        <v>0.29137604568666914</v>
-      </c>
-      <c r="G102" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="H102" s="79">
-        <v>1.2</v>
-      </c>
-      <c r="I102" s="157"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G102" s="140"/>
+      <c r="H102" s="140"/>
+      <c r="I102" s="157">
+        <v>1.25</v>
+      </c>
       <c r="J102" s="140"/>
       <c r="K102" s="141"/>
-      <c r="N102" s="155">
-        <v>1.5</v>
-      </c>
-      <c r="P102" s="155">
-        <v>1.86</v>
-      </c>
     </row>
     <row r="103" spans="1:16">
       <c r="A103" s="156" t="s">
@@ -37437,66 +37482,58 @@
         <v>33</v>
       </c>
       <c r="C103" t="s">
-        <v>80</v>
-      </c>
-      <c r="D103" s="79">
-        <f>E103*(1+$T$1)</f>
-        <v>2.1975000000000002</v>
+        <v>913</v>
+      </c>
+      <c r="D103" s="79" t="e">
+        <f>E103*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E103" s="79">
         <f>AVERAGE(G103:Q103)</f>
-        <v>1.4650000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="F103" s="79">
         <f>STDEV(G103:Q103)</f>
-        <v>0.29137604568666914</v>
-      </c>
-      <c r="G103" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="H103" s="79">
-        <v>1.2</v>
-      </c>
+        <v>0.21213203435596428</v>
+      </c>
+      <c r="G103" s="140"/>
+      <c r="H103" s="140"/>
       <c r="I103" s="157"/>
       <c r="J103" s="140"/>
       <c r="K103" s="141"/>
       <c r="N103" s="155">
         <v>1.5</v>
       </c>
-      <c r="P103" s="155">
-        <v>1.86</v>
+      <c r="O103" s="155">
+        <v>1.8</v>
       </c>
     </row>
     <row r="104" spans="1:16">
       <c r="A104" s="156" t="s">
-        <v>892</v>
+        <v>30</v>
       </c>
       <c r="B104" t="s">
         <v>41</v>
       </c>
       <c r="C104" t="s">
-        <v>112</v>
+        <v>942</v>
       </c>
       <c r="D104" s="79">
-        <f>E104*(1+$T$1)</f>
-        <v>1.75</v>
+        <f t="shared" ref="D104:D105" si="0">E104*(1+$T$1)</f>
+        <v>2.0999999999999996</v>
       </c>
       <c r="E104" s="79">
-        <f>AVERAGE(G104:Q104)</f>
-        <v>1.1666666666666667</v>
-      </c>
-      <c r="F104" s="79">
-        <f>STDEV(G104:Q104)</f>
-        <v>0.15275252316519497</v>
-      </c>
-      <c r="G104" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="H104" s="79">
-        <v>1.2</v>
-      </c>
+        <f t="shared" ref="E104:E105" si="1">AVERAGE(G104:Q104)</f>
+        <v>1.4</v>
+      </c>
+      <c r="F104" s="79" t="e">
+        <f t="shared" ref="F104:F105" si="2">STDEV(G104:Q104)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G104" s="79"/>
+      <c r="H104" s="79"/>
       <c r="I104" s="157">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J104" s="140"/>
       <c r="K104" s="141"/>
@@ -37506,34 +37543,32 @@
         <v>30</v>
       </c>
       <c r="B105" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C105" t="s">
-        <v>915</v>
-      </c>
-      <c r="D105" s="79" t="e">
-        <f>E105*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>943</v>
+      </c>
+      <c r="D105" s="79">
+        <f t="shared" si="0"/>
+        <v>2.8125</v>
       </c>
       <c r="E105" s="79">
-        <f>AVERAGE(G105:Q105)</f>
-        <v>3.0333333333333332</v>
+        <f t="shared" si="1"/>
+        <v>1.875</v>
       </c>
       <c r="F105" s="79">
-        <f>STDEV(G105:Q105)</f>
-        <v>0.83864970836061026</v>
+        <f t="shared" si="2"/>
+        <v>0.5303300858899106</v>
       </c>
       <c r="G105" s="79"/>
-      <c r="H105" s="79">
-        <v>4</v>
-      </c>
-      <c r="I105" s="157"/>
-      <c r="J105" s="140">
-        <v>2.6</v>
-      </c>
+      <c r="H105" s="79"/>
+      <c r="I105" s="157">
+        <v>1.5</v>
+      </c>
+      <c r="J105" s="140"/>
       <c r="K105" s="141"/>
       <c r="O105" s="155">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -37541,77 +37576,66 @@
         <v>30</v>
       </c>
       <c r="B106" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C106" t="s">
-        <v>914</v>
+        <v>944</v>
       </c>
       <c r="D106" s="79">
         <f>E106*(1+$T$1)</f>
-        <v>3.6574999999999998</v>
+        <v>2.8875000000000002</v>
       </c>
       <c r="E106" s="79">
         <f>AVERAGE(G106:Q106)</f>
-        <v>2.438333333333333</v>
+        <v>1.925</v>
       </c>
       <c r="F106" s="79">
         <f>STDEV(G106:Q106)</f>
-        <v>0.46023544699063185</v>
+        <v>0.45961940777125559</v>
       </c>
       <c r="G106" s="79"/>
-      <c r="H106" s="79">
-        <v>1.9</v>
-      </c>
-      <c r="I106" s="157"/>
-      <c r="J106" s="140">
-        <v>2.4</v>
-      </c>
+      <c r="H106" s="79"/>
+      <c r="I106" s="157">
+        <v>1.6</v>
+      </c>
+      <c r="J106" s="140"/>
       <c r="K106" s="141"/>
-      <c r="L106" s="155">
-        <v>2.8</v>
-      </c>
-      <c r="N106" s="155">
-        <v>3.15</v>
-      </c>
       <c r="O106" s="155">
         <v>2.25</v>
       </c>
-      <c r="P106" s="155">
-        <v>2.13</v>
-      </c>
     </row>
     <row r="107" spans="1:16">
       <c r="A107" s="156" t="s">
-        <v>892</v>
+        <v>21</v>
       </c>
       <c r="B107" t="s">
         <v>51</v>
       </c>
       <c r="C107" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="D107" s="79">
         <f>E107*(1+$T$1)</f>
-        <v>2.8125</v>
+        <v>2.2874999999999996</v>
       </c>
       <c r="E107" s="79">
         <f>AVERAGE(G107:Q107)</f>
-        <v>1.875</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="F107" s="79">
         <f>STDEV(G107:Q107)</f>
-        <v>0.5303300858899106</v>
-      </c>
-      <c r="G107" s="79">
-        <f>22.5/10</f>
-        <v>2.25</v>
-      </c>
+        <v>0.60104076400856621</v>
+      </c>
+      <c r="G107" s="79"/>
       <c r="H107" s="79"/>
       <c r="I107" s="157">
-        <v>1.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J107" s="140"/>
       <c r="K107" s="141"/>
+      <c r="O107" s="155">
+        <v>1.95</v>
+      </c>
     </row>
     <row r="108" spans="1:16">
       <c r="A108" s="156" t="s">
@@ -37621,156 +37645,185 @@
         <v>26</v>
       </c>
       <c r="C108" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D108" s="79">
         <f>E108*(1+$T$1)</f>
-        <v>2.1</v>
+        <v>2.1975000000000002</v>
       </c>
       <c r="E108" s="79">
         <f>AVERAGE(G108:Q108)</f>
-        <v>1.4000000000000001</v>
+        <v>1.4650000000000001</v>
       </c>
       <c r="F108" s="79">
         <f>STDEV(G108:Q108)</f>
-        <v>0.40000000000000019</v>
+        <v>0.29137604568666914</v>
       </c>
       <c r="G108" s="79">
-        <v>1.4</v>
-      </c>
-      <c r="H108" s="79"/>
-      <c r="I108" s="157">
-        <v>1</v>
-      </c>
+        <v>1.3</v>
+      </c>
+      <c r="H108" s="79">
+        <v>1.2</v>
+      </c>
+      <c r="I108" s="157"/>
       <c r="J108" s="140"/>
       <c r="K108" s="141"/>
-      <c r="O108" s="155">
-        <v>1.8</v>
+      <c r="N108" s="155">
+        <v>1.5</v>
+      </c>
+      <c r="P108" s="155">
+        <v>1.86</v>
       </c>
     </row>
     <row r="109" spans="1:16">
       <c r="A109" s="156" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B109" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C109" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="D109" s="79">
         <f>E109*(1+$T$1)</f>
-        <v>1.875</v>
+        <v>2.1975000000000002</v>
       </c>
       <c r="E109" s="79">
         <f>AVERAGE(G109:Q109)</f>
-        <v>1.25</v>
-      </c>
-      <c r="F109" s="79" t="e">
+        <v>1.4650000000000001</v>
+      </c>
+      <c r="F109" s="79">
         <f>STDEV(G109:Q109)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G109" s="79"/>
-      <c r="H109" s="79"/>
-      <c r="I109" s="157">
-        <v>1.25</v>
-      </c>
+        <v>0.29137604568666914</v>
+      </c>
+      <c r="G109" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="H109" s="79">
+        <v>1.2</v>
+      </c>
+      <c r="I109" s="157"/>
       <c r="J109" s="140"/>
       <c r="K109" s="141"/>
+      <c r="N109" s="155">
+        <v>1.5</v>
+      </c>
+      <c r="P109" s="155">
+        <v>1.86</v>
+      </c>
     </row>
     <row r="110" spans="1:16">
       <c r="A110" s="156" t="s">
-        <v>30</v>
+        <v>892</v>
       </c>
       <c r="B110" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C110" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="D110" s="79">
         <f>E110*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="E110" s="79">
         <f>AVERAGE(G110:Q110)</f>
-        <v>1.5</v>
-      </c>
-      <c r="F110" s="79" t="e">
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="F110" s="79">
         <f>STDEV(G110:Q110)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G110" s="79"/>
-      <c r="H110" s="79"/>
+        <v>0.15275252316519497</v>
+      </c>
+      <c r="G110" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="H110" s="79">
+        <v>1.2</v>
+      </c>
       <c r="I110" s="157">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J110" s="140"/>
       <c r="K110" s="141"/>
     </row>
     <row r="111" spans="1:16">
       <c r="A111" s="156" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B111" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C111" t="s">
-        <v>39</v>
-      </c>
-      <c r="D111" s="79">
-        <f>E111*(1+$T$1)</f>
-        <v>3</v>
+        <v>915</v>
+      </c>
+      <c r="D111" s="79" t="e">
+        <f>E111*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E111" s="79">
         <f>AVERAGE(G111:Q111)</f>
-        <v>2</v>
-      </c>
-      <c r="F111" s="79" t="e">
+        <v>3.0333333333333332</v>
+      </c>
+      <c r="F111" s="79">
         <f>STDEV(G111:Q111)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G111" s="79">
-        <v>2</v>
-      </c>
-      <c r="H111" s="79"/>
+        <v>0.83864970836061026</v>
+      </c>
+      <c r="G111" s="79"/>
+      <c r="H111" s="79">
+        <v>4</v>
+      </c>
       <c r="I111" s="157"/>
-      <c r="J111" s="140"/>
+      <c r="J111" s="140">
+        <v>2.6</v>
+      </c>
       <c r="K111" s="141"/>
+      <c r="O111" s="155">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="112" spans="1:16">
       <c r="A112" s="156" t="s">
-        <v>892</v>
+        <v>30</v>
       </c>
       <c r="B112" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C112" t="s">
-        <v>104</v>
+        <v>914</v>
       </c>
       <c r="D112" s="79">
         <f>E112*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>3.6574999999999998</v>
       </c>
       <c r="E112" s="79">
         <f>AVERAGE(G112:Q112)</f>
-        <v>1.5</v>
+        <v>2.438333333333333</v>
       </c>
       <c r="F112" s="79">
         <f>STDEV(G112:Q112)</f>
-        <v>0.17320508075688776</v>
-      </c>
-      <c r="G112" s="79">
-        <v>1.4</v>
-      </c>
+        <v>0.46023544699063185</v>
+      </c>
+      <c r="G112" s="79"/>
       <c r="H112" s="79">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="I112" s="157"/>
-      <c r="J112" s="140"/>
+      <c r="J112" s="140">
+        <v>2.4</v>
+      </c>
       <c r="K112" s="141"/>
       <c r="L112" s="155">
-        <v>1.4</v>
+        <v>2.8</v>
+      </c>
+      <c r="N112" s="155">
+        <v>3.15</v>
+      </c>
+      <c r="O112" s="155">
+        <v>2.25</v>
+      </c>
+      <c r="P112" s="155">
+        <v>2.13</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -37778,27 +37831,30 @@
         <v>892</v>
       </c>
       <c r="B113" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C113" t="s">
-        <v>78</v>
+        <v>945</v>
       </c>
       <c r="D113" s="79">
         <f>E113*(1+$T$1)</f>
-        <v>2.0999999999999996</v>
+        <v>2.8125</v>
       </c>
       <c r="E113" s="79">
         <f>AVERAGE(G113:Q113)</f>
-        <v>1.4</v>
-      </c>
-      <c r="F113" s="79" t="e">
+        <v>1.875</v>
+      </c>
+      <c r="F113" s="79">
         <f>STDEV(G113:Q113)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G113" s="79"/>
+        <v>0.5303300858899106</v>
+      </c>
+      <c r="G113" s="79">
+        <f>22.5/10</f>
+        <v>2.25</v>
+      </c>
       <c r="H113" s="79"/>
       <c r="I113" s="157">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J113" s="140"/>
       <c r="K113" s="141"/>
@@ -37811,29 +37867,31 @@
         <v>26</v>
       </c>
       <c r="C114" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D114" s="79">
         <f>E114*(1+$T$1)</f>
-        <v>2.2949999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="E114" s="79">
         <f>AVERAGE(G114:Q114)</f>
-        <v>1.53</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="F114" s="79">
         <f>STDEV(G114:Q114)</f>
-        <v>4.2426406871192889E-2</v>
-      </c>
-      <c r="G114" s="140"/>
-      <c r="H114" s="140"/>
+        <v>0.40000000000000019</v>
+      </c>
+      <c r="G114" s="79">
+        <v>1.4</v>
+      </c>
+      <c r="H114" s="79"/>
       <c r="I114" s="157">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J114" s="140"/>
       <c r="K114" s="141"/>
-      <c r="N114" s="155">
-        <v>1.56</v>
+      <c r="O114" s="155">
+        <v>1.8</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -37841,120 +37899,122 @@
         <v>142</v>
       </c>
       <c r="B115" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C115" t="s">
-        <v>651</v>
-      </c>
-      <c r="D115" s="79" t="e">
-        <f>E115*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>111</v>
+      </c>
+      <c r="D115" s="79">
+        <f>E115*(1+$T$1)</f>
+        <v>1.875</v>
       </c>
       <c r="E115" s="79">
         <f>AVERAGE(G115:Q115)</f>
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="F115" s="79" t="e">
         <f>STDEV(G115:Q115)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G115" s="140"/>
-      <c r="H115" s="140"/>
-      <c r="I115" s="157"/>
+      <c r="G115" s="79"/>
+      <c r="H115" s="79"/>
+      <c r="I115" s="157">
+        <v>1.25</v>
+      </c>
       <c r="J115" s="140"/>
       <c r="K115" s="141"/>
-      <c r="O115" s="155">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="116" spans="1:16">
       <c r="A116" s="156" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="B116" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C116" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="D116" s="79">
         <f>E116*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>2.25</v>
       </c>
       <c r="E116" s="79">
         <f>AVERAGE(G116:Q116)</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F116" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="F116" s="79" t="e">
         <f>STDEV(G116:Q116)</f>
-        <v>0</v>
-      </c>
-      <c r="G116" s="79">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H116" s="79">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I116" s="157"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G116" s="79"/>
+      <c r="H116" s="79"/>
+      <c r="I116" s="157">
+        <v>1.5</v>
+      </c>
       <c r="J116" s="140"/>
       <c r="K116" s="141"/>
     </row>
     <row r="117" spans="1:16">
       <c r="A117" s="156" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B117" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C117" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="D117" s="79">
         <f>E117*(1+$T$1)</f>
-        <v>2.625</v>
+        <v>2.25</v>
       </c>
       <c r="E117" s="79">
         <f>AVERAGE(G117:Q117)</f>
-        <v>1.75</v>
-      </c>
-      <c r="F117" s="79" t="e">
+        <v>1.5</v>
+      </c>
+      <c r="F117" s="79">
         <f>STDEV(G117:Q117)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G117" s="79"/>
-      <c r="H117" s="79"/>
-      <c r="I117" s="157">
-        <v>1.75</v>
-      </c>
+        <v>0.17320508075688776</v>
+      </c>
+      <c r="G117" s="79">
+        <v>1.4</v>
+      </c>
+      <c r="H117" s="79">
+        <v>1.7</v>
+      </c>
+      <c r="I117" s="157"/>
       <c r="J117" s="140"/>
       <c r="K117" s="141"/>
+      <c r="L117" s="155">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="118" spans="1:16">
       <c r="A118" s="156" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B118" t="s">
-        <v>33</v>
-      </c>
-      <c r="C118" s="66" t="s">
-        <v>94</v>
+        <v>26</v>
+      </c>
+      <c r="C118" t="s">
+        <v>78</v>
       </c>
       <c r="D118" s="79">
         <f>E118*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="E118" s="79">
         <f>AVERAGE(G118:Q118)</f>
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F118" s="79" t="e">
         <f>STDEV(G118:Q118)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G118" s="140"/>
-      <c r="H118" s="140"/>
+      <c r="G118" s="79"/>
+      <c r="H118" s="79"/>
       <c r="I118" s="157">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J118" s="140"/>
       <c r="K118" s="141"/>
@@ -37964,201 +38024,205 @@
         <v>892</v>
       </c>
       <c r="B119" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C119" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D119" s="79">
         <f>E119*(1+$T$1)</f>
-        <v>2.4937500000000004</v>
+        <v>2.2949999999999999</v>
       </c>
       <c r="E119" s="79">
         <f>AVERAGE(G119:Q119)</f>
-        <v>1.6625000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="F119" s="79">
         <f>STDEV(G119:Q119)</f>
-        <v>0.28686524130097363</v>
-      </c>
-      <c r="G119" s="79"/>
-      <c r="H119" s="79">
-        <v>2</v>
-      </c>
-      <c r="I119" s="157"/>
+        <v>4.2426406871192889E-2</v>
+      </c>
+      <c r="G119" s="140"/>
+      <c r="H119" s="140"/>
+      <c r="I119" s="157">
+        <v>1.5</v>
+      </c>
       <c r="J119" s="140"/>
       <c r="K119" s="141"/>
-      <c r="L119" s="155">
-        <v>1.4</v>
-      </c>
-      <c r="O119" s="155">
-        <v>1.8</v>
-      </c>
-      <c r="P119" s="155">
-        <v>1.45</v>
+      <c r="N119" s="155">
+        <v>1.56</v>
       </c>
     </row>
     <row r="120" spans="1:16">
       <c r="A120" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B120" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C120" t="s">
-        <v>81</v>
-      </c>
-      <c r="D120" s="79">
-        <f>E120*(1+$T$1)</f>
-        <v>2.5500000000000003</v>
+        <v>651</v>
+      </c>
+      <c r="D120" s="79" t="e">
+        <f>E120*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E120" s="79">
         <f>AVERAGE(G120:Q120)</f>
-        <v>1.7000000000000002</v>
-      </c>
-      <c r="F120" s="79">
+        <v>2.1</v>
+      </c>
+      <c r="F120" s="79" t="e">
         <f>STDEV(G120:Q120)</f>
-        <v>0.14142135623730948</v>
-      </c>
-      <c r="G120" s="79"/>
-      <c r="H120" s="79">
-        <v>1.6</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G120" s="140"/>
+      <c r="H120" s="140"/>
       <c r="I120" s="157"/>
       <c r="J120" s="140"/>
       <c r="K120" s="141"/>
       <c r="O120" s="155">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="121" spans="1:16">
       <c r="A121" s="156" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="B121" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C121" t="s">
-        <v>937</v>
-      </c>
-      <c r="D121" s="79" t="e">
-        <f>E121*(1+$O$1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E121" s="79" t="e">
+        <v>109</v>
+      </c>
+      <c r="D121" s="79">
+        <f>E121*(1+$T$1)</f>
+        <v>1.6500000000000001</v>
+      </c>
+      <c r="E121" s="79">
         <f>AVERAGE(G121:Q121)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F121" s="79" t="e">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F121" s="79">
         <f>STDEV(G121:Q121)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G121" s="79"/>
-      <c r="H121" s="79"/>
+        <v>0</v>
+      </c>
+      <c r="G121" s="79">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H121" s="79">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="I121" s="157"/>
       <c r="J121" s="140"/>
       <c r="K121" s="141"/>
     </row>
     <row r="122" spans="1:16">
       <c r="A122" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B122" t="s">
         <v>51</v>
       </c>
       <c r="C122" t="s">
-        <v>938</v>
+        <v>139</v>
       </c>
       <c r="D122" s="79">
         <f>E122*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>2.625</v>
       </c>
       <c r="E122" s="79">
         <f>AVERAGE(G122:Q122)</f>
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="F122" s="79" t="e">
         <f>STDEV(G122:Q122)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G122" s="79">
-        <v>1.5</v>
-      </c>
+      <c r="G122" s="79"/>
       <c r="H122" s="79"/>
-      <c r="I122" s="157"/>
+      <c r="I122" s="157">
+        <v>1.75</v>
+      </c>
       <c r="J122" s="140"/>
       <c r="K122" s="141"/>
     </row>
     <row r="123" spans="1:16">
       <c r="A123" s="156" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B123" t="s">
-        <v>51</v>
-      </c>
-      <c r="C123" t="s">
-        <v>134</v>
+        <v>33</v>
+      </c>
+      <c r="C123" s="66" t="s">
+        <v>94</v>
       </c>
       <c r="D123" s="79">
         <f>E123*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>2.25</v>
       </c>
       <c r="E123" s="79">
         <f>AVERAGE(G123:Q123)</f>
-        <v>1.1000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="F123" s="79" t="e">
         <f>STDEV(G123:Q123)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G123" s="79"/>
-      <c r="H123" s="79">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I123" s="157"/>
+      <c r="G123" s="140"/>
+      <c r="H123" s="140"/>
+      <c r="I123" s="157">
+        <v>1.5</v>
+      </c>
       <c r="J123" s="140"/>
       <c r="K123" s="141"/>
     </row>
     <row r="124" spans="1:16">
       <c r="A124" s="156" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B124" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C124" t="s">
-        <v>918</v>
-      </c>
-      <c r="D124" s="79" t="e">
-        <f>E124*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>311</v>
+      </c>
+      <c r="D124" s="79">
+        <f>E124*(1+$T$1)</f>
+        <v>2.4937500000000004</v>
       </c>
       <c r="E124" s="79">
         <f>AVERAGE(G124:Q124)</f>
-        <v>1.5</v>
-      </c>
-      <c r="F124" s="79" t="e">
+        <v>1.6625000000000001</v>
+      </c>
+      <c r="F124" s="79">
         <f>STDEV(G124:Q124)</f>
-        <v>#DIV/0!</v>
+        <v>0.28686524130097363</v>
       </c>
       <c r="G124" s="79"/>
-      <c r="H124" s="79"/>
+      <c r="H124" s="79">
+        <v>2</v>
+      </c>
       <c r="I124" s="157"/>
       <c r="J124" s="140"/>
       <c r="K124" s="141"/>
+      <c r="L124" s="155">
+        <v>1.4</v>
+      </c>
       <c r="O124" s="155">
-        <v>1.5</v>
+        <v>1.8</v>
+      </c>
+      <c r="P124" s="155">
+        <v>1.45</v>
       </c>
     </row>
     <row r="125" spans="1:16">
       <c r="A125" s="156" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="B125" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C125" t="s">
-        <v>919</v>
+        <v>937</v>
       </c>
       <c r="D125" s="79" t="e">
         <f>E125*(1+$O$1)</f>
@@ -38166,54 +38230,46 @@
       </c>
       <c r="E125" s="79">
         <f>AVERAGE(G125:Q125)</f>
-        <v>1.2333333333333334</v>
-      </c>
-      <c r="F125" s="79">
+        <v>2</v>
+      </c>
+      <c r="F125" s="79" t="e">
         <f>STDEV(G125:Q125)</f>
-        <v>0.25166114784235771</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G125" s="79"/>
       <c r="H125" s="79"/>
-      <c r="I125" s="157"/>
-      <c r="J125" s="140">
-        <v>1</v>
-      </c>
+      <c r="I125" s="157">
+        <v>2</v>
+      </c>
+      <c r="J125" s="140"/>
       <c r="K125" s="141"/>
-      <c r="N125" s="155">
-        <v>1.2</v>
-      </c>
-      <c r="O125" s="155">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="126" spans="1:16">
       <c r="A126" s="156" t="s">
-        <v>55</v>
+        <v>892</v>
       </c>
       <c r="B126" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C126" t="s">
-        <v>75</v>
+        <v>938</v>
       </c>
       <c r="D126" s="79">
         <f>E126*(1+$T$1)</f>
-        <v>1.5750000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="E126" s="79">
         <f>AVERAGE(G126:Q126)</f>
-        <v>1.05</v>
-      </c>
-      <c r="F126" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="F126" s="79" t="e">
         <f>STDEV(G126:Q126)</f>
-        <v>7.0710678118654821E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G126" s="79">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H126" s="79">
-        <v>1</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="H126" s="79"/>
       <c r="I126" s="157"/>
       <c r="J126" s="140"/>
       <c r="K126" s="141"/>
@@ -38223,158 +38279,139 @@
         <v>892</v>
       </c>
       <c r="B127" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C127" t="s">
-        <v>920</v>
-      </c>
-      <c r="D127" s="79" t="e">
-        <f>E127*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>134</v>
+      </c>
+      <c r="D127" s="79">
+        <f>E127*(1+$T$1)</f>
+        <v>1.6500000000000001</v>
       </c>
       <c r="E127" s="79">
         <f>AVERAGE(G127:Q127)</f>
-        <v>1.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F127" s="79" t="e">
         <f>STDEV(G127:Q127)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G127" s="79"/>
-      <c r="H127" s="79"/>
+      <c r="H127" s="79">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="I127" s="157"/>
       <c r="J127" s="140"/>
       <c r="K127" s="141"/>
-      <c r="O127" s="155">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="128" spans="1:16">
       <c r="A128" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B128" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C128" t="s">
-        <v>97</v>
-      </c>
-      <c r="D128" s="79">
-        <f>E128*(1+$T$1)</f>
-        <v>1.6949999999999998</v>
+        <v>918</v>
+      </c>
+      <c r="D128" s="79" t="e">
+        <f>E128*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E128" s="79">
         <f>AVERAGE(G128:Q128)</f>
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="F128" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="F128" s="79" t="e">
         <f>STDEV(G128:Q128)</f>
-        <v>0.30331501776206288</v>
-      </c>
-      <c r="G128" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="H128" s="79">
-        <v>1</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G128" s="79"/>
+      <c r="H128" s="79"/>
       <c r="I128" s="157"/>
       <c r="J128" s="140"/>
       <c r="K128" s="141"/>
-      <c r="N128" s="155">
-        <v>1.1499999999999999</v>
-      </c>
       <c r="O128" s="155">
         <v>1.5</v>
       </c>
-      <c r="P128" s="155">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="129" spans="1:16">
       <c r="A129" s="156" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="B129" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C129" t="s">
-        <v>40</v>
-      </c>
-      <c r="D129" s="79">
-        <f>E129*(1+$T$1)</f>
-        <v>2.3525</v>
+        <v>919</v>
+      </c>
+      <c r="D129" s="79" t="e">
+        <f>E129*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E129" s="79">
         <f>AVERAGE(G129:Q129)</f>
-        <v>1.5683333333333334</v>
+        <v>1.2333333333333334</v>
       </c>
       <c r="F129" s="79">
         <f>STDEV(G129:Q129)</f>
-        <v>0.27462095088806732</v>
-      </c>
-      <c r="G129" s="79">
-        <v>1.4</v>
-      </c>
-      <c r="H129" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="I129" s="157">
-        <v>1.75</v>
-      </c>
-      <c r="J129" s="140"/>
+        <v>0.25166114784235771</v>
+      </c>
+      <c r="G129" s="79"/>
+      <c r="H129" s="79"/>
+      <c r="I129" s="157"/>
+      <c r="J129" s="140">
+        <v>1</v>
+      </c>
       <c r="K129" s="141"/>
       <c r="N129" s="155">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="O129" s="155">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="P129" s="155">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="130" spans="1:16">
       <c r="A130" s="156" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B130" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C130" t="s">
-        <v>88</v>
+        <v>946</v>
       </c>
       <c r="D130" s="79">
         <f>E130*(1+$T$1)</f>
-        <v>2.3774999999999999</v>
+        <v>1.5750000000000002</v>
       </c>
       <c r="E130" s="79">
         <f>AVERAGE(G130:Q130)</f>
-        <v>1.585</v>
+        <v>1.05</v>
       </c>
       <c r="F130" s="79">
         <f>STDEV(G130:Q130)</f>
-        <v>0.26162950903902327</v>
+        <v>7.0710678118654821E-2</v>
       </c>
       <c r="G130" s="79">
-        <v>1.4</v>
-      </c>
-      <c r="H130" s="79"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H130" s="79">
+        <v>1</v>
+      </c>
       <c r="I130" s="157"/>
       <c r="J130" s="140"/>
       <c r="K130" s="141"/>
-      <c r="O130" s="155">
-        <v>1.77</v>
-      </c>
     </row>
     <row r="131" spans="1:16">
       <c r="A131" s="156" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B131" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C131" t="s">
-        <v>655</v>
+        <v>920</v>
       </c>
       <c r="D131" s="79" t="e">
         <f>E131*(1+$O$1)</f>
@@ -38382,152 +38419,147 @@
       </c>
       <c r="E131" s="79">
         <f>AVERAGE(G131:Q131)</f>
-        <v>2.5333333333333332</v>
-      </c>
-      <c r="F131" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="F131" s="79" t="e">
         <f>STDEV(G131:Q131)</f>
-        <v>0.25166114784235832</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G131" s="79"/>
-      <c r="H131" s="79">
-        <v>2.2999999999999998</v>
-      </c>
+      <c r="H131" s="79"/>
       <c r="I131" s="157"/>
       <c r="J131" s="140"/>
       <c r="K131" s="141"/>
-      <c r="L131" s="155">
-        <v>2.8</v>
-      </c>
       <c r="O131" s="155">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="132" spans="1:16">
       <c r="A132" s="156" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B132" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C132" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="D132" s="79">
         <f>E132*(1+$T$1)</f>
-        <v>2.7349999999999999</v>
+        <v>1.6949999999999998</v>
       </c>
       <c r="E132" s="79">
         <f>AVERAGE(G132:Q132)</f>
-        <v>1.8233333333333333</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F132" s="79">
         <f>STDEV(G132:Q132)</f>
-        <v>0.5857189314566047</v>
-      </c>
-      <c r="G132" s="79"/>
+        <v>0.30331501776206288</v>
+      </c>
+      <c r="G132" s="79">
+        <v>1.3</v>
+      </c>
       <c r="H132" s="79">
-        <v>1.99</v>
+        <v>1</v>
       </c>
       <c r="I132" s="157"/>
-      <c r="J132" s="140">
-        <v>1.7</v>
-      </c>
+      <c r="J132" s="140"/>
       <c r="K132" s="141"/>
-      <c r="L132" s="155">
+      <c r="N132" s="155">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="O132" s="155">
         <v>1.5</v>
       </c>
-      <c r="N132" s="155">
-        <v>1</v>
-      </c>
-      <c r="O132" s="155">
-        <v>2.75</v>
-      </c>
       <c r="P132" s="155">
-        <v>2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="133" spans="1:16">
-      <c r="A133" s="94" t="s">
-        <v>142</v>
+      <c r="A133" s="156" t="s">
+        <v>30</v>
       </c>
       <c r="B133" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C133" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="D133" s="79">
         <f>E133*(1+$T$1)</f>
-        <v>1.78125</v>
+        <v>2.3525</v>
       </c>
       <c r="E133" s="79">
         <f>AVERAGE(G133:Q133)</f>
-        <v>1.1875</v>
+        <v>1.5683333333333334</v>
       </c>
       <c r="F133" s="79">
         <f>STDEV(G133:Q133)</f>
-        <v>0.13149778198382917</v>
-      </c>
-      <c r="G133" s="79"/>
+        <v>0.27462095088806732</v>
+      </c>
+      <c r="G133" s="79">
+        <v>1.4</v>
+      </c>
       <c r="H133" s="79">
-        <v>1</v>
-      </c>
-      <c r="I133" s="105"/>
-      <c r="J133" s="140">
-        <v>1.25</v>
-      </c>
+        <v>1.3</v>
+      </c>
+      <c r="I133" s="157">
+        <v>1.75</v>
+      </c>
+      <c r="J133" s="140"/>
       <c r="K133" s="141"/>
-      <c r="L133" s="155">
-        <v>1.3</v>
+      <c r="N133" s="155">
+        <v>1.35</v>
+      </c>
+      <c r="O133" s="155">
+        <v>2.0099999999999998</v>
       </c>
       <c r="P133" s="155">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="134" spans="1:16">
-      <c r="A134" s="322" t="s">
-        <v>21</v>
+      <c r="A134" s="156" t="s">
+        <v>142</v>
       </c>
       <c r="B134" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C134" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D134" s="79">
         <f>E134*(1+$T$1)</f>
-        <v>3.7650000000000006</v>
+        <v>2.3774999999999999</v>
       </c>
       <c r="E134" s="79">
         <f>AVERAGE(G134:Q134)</f>
-        <v>2.5100000000000002</v>
+        <v>1.585</v>
       </c>
       <c r="F134" s="79">
         <f>STDEV(G134:Q134)</f>
-        <v>0.61506097258727077</v>
-      </c>
-      <c r="G134" s="79"/>
-      <c r="H134" s="79">
-        <v>1.9</v>
-      </c>
-      <c r="I134" s="201">
-        <v>2.5</v>
-      </c>
+        <v>0.26162950903902327</v>
+      </c>
+      <c r="G134" s="79">
+        <v>1.4</v>
+      </c>
+      <c r="H134" s="79"/>
+      <c r="I134" s="157"/>
       <c r="J134" s="140"/>
       <c r="K134" s="141"/>
       <c r="O134" s="155">
-        <v>3.13</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="135" spans="1:16">
-      <c r="A135" t="s">
-        <v>21</v>
+      <c r="A135" s="156" t="s">
+        <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C135" t="s">
-        <v>921</v>
+        <v>655</v>
       </c>
       <c r="D135" s="79" t="e">
         <f>E135*(1+$O$1)</f>
@@ -38535,303 +38567,322 @@
       </c>
       <c r="E135" s="79">
         <f>AVERAGE(G135:Q135)</f>
-        <v>2.25</v>
+        <v>2.5333333333333332</v>
       </c>
       <c r="F135" s="79">
         <f>STDEV(G135:Q135)</f>
-        <v>0.45000000000000062</v>
+        <v>0.25166114784235832</v>
       </c>
       <c r="G135" s="79"/>
       <c r="H135" s="79">
-        <v>2.25</v>
-      </c>
-      <c r="I135" s="79"/>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I135" s="157"/>
       <c r="J135" s="140"/>
       <c r="K135" s="141"/>
       <c r="L135" s="155">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="O135" s="155">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="136" spans="1:16">
-      <c r="A136" s="322" t="s">
-        <v>21</v>
+      <c r="A136" s="156" t="s">
+        <v>142</v>
       </c>
       <c r="B136" t="s">
         <v>22</v>
       </c>
       <c r="C136" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D136" s="79">
         <f>E136*(1+$T$1)</f>
-        <v>4.1999999999999993</v>
+        <v>2.7349999999999999</v>
       </c>
       <c r="E136" s="79">
         <f>AVERAGE(G136:Q136)</f>
-        <v>2.8</v>
+        <v>1.8233333333333333</v>
       </c>
       <c r="F136" s="79">
         <f>STDEV(G136:Q136)</f>
-        <v>0.85244745683629541</v>
+        <v>0.5857189314566047</v>
       </c>
       <c r="G136" s="79"/>
       <c r="H136" s="79">
-        <v>4</v>
-      </c>
-      <c r="I136" s="79">
-        <v>2.5</v>
-      </c>
-      <c r="J136" s="140"/>
+        <v>1.99</v>
+      </c>
+      <c r="I136" s="157"/>
+      <c r="J136" s="140">
+        <v>1.7</v>
+      </c>
       <c r="K136" s="141"/>
       <c r="L136" s="155">
+        <v>1.5</v>
+      </c>
+      <c r="N136" s="155">
+        <v>1</v>
+      </c>
+      <c r="O136" s="155">
+        <v>2.75</v>
+      </c>
+      <c r="P136" s="155">
         <v>2</v>
       </c>
-      <c r="O136" s="155">
-        <v>2.7</v>
-      </c>
     </row>
     <row r="137" spans="1:16">
-      <c r="A137" s="322" t="s">
-        <v>21</v>
+      <c r="A137" s="94" t="s">
+        <v>142</v>
       </c>
       <c r="B137" t="s">
         <v>26</v>
       </c>
       <c r="C137" t="s">
-        <v>922</v>
+        <v>89</v>
       </c>
       <c r="D137" s="79">
         <f>E137*(1+$T$1)</f>
-        <v>2.3250000000000002</v>
+        <v>1.78125</v>
       </c>
       <c r="E137" s="79">
         <f>AVERAGE(G137:Q137)</f>
-        <v>1.55</v>
+        <v>1.1875</v>
       </c>
       <c r="F137" s="79">
         <f>STDEV(G137:Q137)</f>
-        <v>0.47749345545253263</v>
+        <v>0.13149778198382917</v>
       </c>
       <c r="G137" s="79"/>
       <c r="H137" s="79">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I137" s="79">
-        <v>2</v>
-      </c>
-      <c r="J137" s="140"/>
+        <v>1</v>
+      </c>
+      <c r="I137" s="105"/>
+      <c r="J137" s="140">
+        <v>1.25</v>
+      </c>
       <c r="K137" s="141"/>
       <c r="L137" s="155">
-        <v>1.6</v>
-      </c>
-      <c r="N137" s="155">
-        <v>0.85</v>
-      </c>
-      <c r="O137" s="155">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="P137" s="155">
-        <v>2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="138" spans="1:16">
-      <c r="A138" s="156" t="s">
-        <v>142</v>
+      <c r="A138" s="322" t="s">
+        <v>21</v>
       </c>
       <c r="B138" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C138" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="D138" s="79">
         <f>E138*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>3.7650000000000006</v>
       </c>
       <c r="E138" s="79">
         <f>AVERAGE(G138:Q138)</f>
-        <v>1.5</v>
-      </c>
-      <c r="F138" s="79" t="e">
+        <v>2.5100000000000002</v>
+      </c>
+      <c r="F138" s="79">
         <f>STDEV(G138:Q138)</f>
-        <v>#DIV/0!</v>
+        <v>0.61506097258727077</v>
       </c>
       <c r="G138" s="79"/>
-      <c r="H138" s="79"/>
-      <c r="I138" s="157">
-        <v>1.5</v>
+      <c r="H138" s="79">
+        <v>1.9</v>
+      </c>
+      <c r="I138" s="201">
+        <v>2.5</v>
       </c>
       <c r="J138" s="140"/>
       <c r="K138" s="141"/>
+      <c r="O138" s="155">
+        <v>3.13</v>
+      </c>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" s="322" t="s">
-        <v>892</v>
+      <c r="A139" t="s">
+        <v>21</v>
       </c>
       <c r="B139" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C139" t="s">
-        <v>103</v>
-      </c>
-      <c r="D139" s="79">
-        <f>E139*(1+$T$1)</f>
-        <v>2.0250000000000004</v>
+        <v>921</v>
+      </c>
+      <c r="D139" s="79" t="e">
+        <f>E139*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E139" s="79">
         <f>AVERAGE(G139:Q139)</f>
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="F139" s="79">
         <f>STDEV(G139:Q139)</f>
-        <v>0.21213203435596303</v>
-      </c>
-      <c r="G139" s="79">
-        <v>1.2</v>
-      </c>
-      <c r="H139" s="79"/>
+        <v>0.45000000000000062</v>
+      </c>
+      <c r="G139" s="79"/>
+      <c r="H139" s="79">
+        <v>2.25</v>
+      </c>
       <c r="I139" s="79"/>
       <c r="J139" s="140"/>
       <c r="K139" s="141"/>
+      <c r="L139" s="155">
+        <v>1.8</v>
+      </c>
       <c r="O139" s="155">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="140" spans="1:16">
       <c r="A140" s="322" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="B140" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C140" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="D140" s="79">
         <f>E140*(1+$T$1)</f>
-        <v>2.0999999999999996</v>
+        <v>4.1999999999999993</v>
       </c>
       <c r="E140" s="79">
         <f>AVERAGE(G140:Q140)</f>
-        <v>1.4</v>
-      </c>
-      <c r="F140" s="79" t="e">
+        <v>2.8</v>
+      </c>
+      <c r="F140" s="79">
         <f>STDEV(G140:Q140)</f>
-        <v>#DIV/0!</v>
+        <v>0.85244745683629541</v>
       </c>
       <c r="G140" s="79"/>
-      <c r="H140" s="79"/>
+      <c r="H140" s="79">
+        <v>4</v>
+      </c>
       <c r="I140" s="79">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J140" s="140"/>
       <c r="K140" s="141"/>
+      <c r="L140" s="155">
+        <v>2</v>
+      </c>
+      <c r="O140" s="155">
+        <v>2.7</v>
+      </c>
     </row>
     <row r="141" spans="1:16">
       <c r="A141" s="322" t="s">
-        <v>892</v>
+        <v>21</v>
       </c>
       <c r="B141" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C141" t="s">
-        <v>96</v>
+        <v>922</v>
       </c>
       <c r="D141" s="79">
         <f>E141*(1+$T$1)</f>
-        <v>2.1949999999999998</v>
+        <v>2.3250000000000002</v>
       </c>
       <c r="E141" s="79">
         <f>AVERAGE(G141:Q141)</f>
-        <v>1.4633333333333332</v>
+        <v>1.55</v>
       </c>
       <c r="F141" s="79">
         <f>STDEV(G141:Q141)</f>
-        <v>0.44613152021946778</v>
+        <v>0.47749345545253263</v>
       </c>
       <c r="G141" s="79"/>
       <c r="H141" s="79">
-        <v>1</v>
-      </c>
-      <c r="I141" s="79"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I141" s="79">
+        <v>2</v>
+      </c>
       <c r="J141" s="140"/>
       <c r="K141" s="141"/>
+      <c r="L141" s="155">
+        <v>1.6</v>
+      </c>
       <c r="N141" s="155">
-        <v>1.5</v>
+        <v>0.85</v>
       </c>
       <c r="O141" s="155">
-        <v>1.89</v>
+        <v>1.75</v>
+      </c>
+      <c r="P141" s="155">
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" s="322" t="s">
+      <c r="A142" s="156" t="s">
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C142" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D142" s="79">
         <f>E142*(1+$T$1)</f>
-        <v>1.9000000000000004</v>
+        <v>2.25</v>
       </c>
       <c r="E142" s="79">
         <f>AVERAGE(G142:Q142)</f>
-        <v>1.2666666666666668</v>
-      </c>
-      <c r="F142" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="F142" s="79" t="e">
         <f>STDEV(G142:Q142)</f>
-        <v>0.30550504633038922</v>
-      </c>
-      <c r="G142" s="79">
-        <v>1.2</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G142" s="79"/>
       <c r="H142" s="79"/>
-      <c r="I142" s="79">
-        <v>1</v>
+      <c r="I142" s="157">
+        <v>1.5</v>
       </c>
       <c r="J142" s="140"/>
       <c r="K142" s="141"/>
-      <c r="O142" s="155">
-        <v>1.6</v>
-      </c>
     </row>
     <row r="143" spans="1:16">
       <c r="A143" s="322" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B143" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C143" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="D143" s="79">
         <f>E143*(1+$T$1)</f>
-        <v>2.3849999999999998</v>
+        <v>2.0250000000000004</v>
       </c>
       <c r="E143" s="79">
         <f>AVERAGE(G143:Q143)</f>
-        <v>1.5899999999999999</v>
+        <v>1.35</v>
       </c>
       <c r="F143" s="79">
         <f>STDEV(G143:Q143)</f>
-        <v>8.4852813742385624E-2</v>
-      </c>
-      <c r="G143" s="79"/>
+        <v>0.21213203435596303</v>
+      </c>
+      <c r="G143" s="79">
+        <v>1.2</v>
+      </c>
       <c r="H143" s="79"/>
-      <c r="I143" s="79">
-        <v>1.65</v>
-      </c>
+      <c r="I143" s="79"/>
       <c r="J143" s="140"/>
       <c r="K143" s="141"/>
       <c r="O143" s="155">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -38839,18 +38890,18 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C144" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="D144" s="79">
         <f>E144*(1+$T$1)</f>
-        <v>1.125</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="E144" s="79">
         <f>AVERAGE(G144:Q144)</f>
-        <v>0.75</v>
+        <v>1.4</v>
       </c>
       <c r="F144" s="79" t="e">
         <f>STDEV(G144:Q144)</f>
@@ -38859,40 +38910,45 @@
       <c r="G144" s="79"/>
       <c r="H144" s="79"/>
       <c r="I144" s="79">
-        <v>0.75</v>
+        <v>1.4</v>
       </c>
       <c r="J144" s="140"/>
       <c r="K144" s="141"/>
     </row>
     <row r="145" spans="1:15">
       <c r="A145" s="322" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B145" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C145" t="s">
-        <v>897</v>
+        <v>96</v>
       </c>
       <c r="D145" s="79">
         <f>E145*(1+$T$1)</f>
-        <v>2.9249999999999998</v>
+        <v>2.1949999999999998</v>
       </c>
       <c r="E145" s="79">
         <f>AVERAGE(G145:Q145)</f>
-        <v>1.95</v>
-      </c>
-      <c r="F145" s="79" t="e">
+        <v>1.4633333333333332</v>
+      </c>
+      <c r="F145" s="79">
         <f>STDEV(G145:Q145)</f>
-        <v>#DIV/0!</v>
+        <v>0.44613152021946778</v>
       </c>
       <c r="G145" s="79"/>
-      <c r="H145" s="79"/>
+      <c r="H145" s="79">
+        <v>1</v>
+      </c>
       <c r="I145" s="79"/>
       <c r="J145" s="140"/>
       <c r="K145" s="141"/>
+      <c r="N145" s="155">
+        <v>1.5</v>
+      </c>
       <c r="O145" s="155">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="146" spans="1:15">
@@ -38900,64 +38956,86 @@
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C146" t="s">
-        <v>898</v>
+        <v>91</v>
       </c>
       <c r="D146" s="79">
         <f>E146*(1+$T$1)</f>
-        <v>3.6524999999999999</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="E146" s="79">
         <f>AVERAGE(G146:Q146)</f>
-        <v>2.4350000000000001</v>
+        <v>1.2666666666666668</v>
       </c>
       <c r="F146" s="79">
         <f>STDEV(G146:Q146)</f>
-        <v>9.1923881554251102E-2</v>
-      </c>
-      <c r="G146" s="79"/>
+        <v>0.30550504633038922</v>
+      </c>
+      <c r="G146" s="79">
+        <v>1.2</v>
+      </c>
       <c r="H146" s="79"/>
-      <c r="I146" s="79"/>
+      <c r="I146" s="79">
+        <v>1</v>
+      </c>
       <c r="J146" s="140"/>
       <c r="K146" s="141"/>
-      <c r="N146" s="155">
-        <v>2.5</v>
-      </c>
       <c r="O146" s="155">
-        <v>2.37</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="147" spans="1:15">
-      <c r="A147" s="322"/>
-      <c r="D147" s="79" t="e">
+      <c r="A147" s="322" t="s">
+        <v>142</v>
+      </c>
+      <c r="B147" t="s">
+        <v>22</v>
+      </c>
+      <c r="C147" t="s">
+        <v>54</v>
+      </c>
+      <c r="D147" s="79">
         <f>E147*(1+$T$1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E147" s="79" t="e">
+        <v>2.3849999999999998</v>
+      </c>
+      <c r="E147" s="79">
         <f>AVERAGE(G147:Q147)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F147" s="79" t="e">
+        <v>1.5899999999999999</v>
+      </c>
+      <c r="F147" s="79">
         <f>STDEV(G147:Q147)</f>
-        <v>#DIV/0!</v>
+        <v>8.4852813742385624E-2</v>
       </c>
       <c r="G147" s="79"/>
       <c r="H147" s="79"/>
-      <c r="I147" s="79"/>
+      <c r="I147" s="79">
+        <v>1.65</v>
+      </c>
       <c r="J147" s="140"/>
       <c r="K147" s="141"/>
+      <c r="O147" s="155">
+        <v>1.53</v>
+      </c>
     </row>
     <row r="148" spans="1:15">
-      <c r="A148" s="322"/>
-      <c r="D148" s="79" t="e">
+      <c r="A148" s="322" t="s">
+        <v>142</v>
+      </c>
+      <c r="B148" t="s">
+        <v>41</v>
+      </c>
+      <c r="C148" t="s">
+        <v>110</v>
+      </c>
+      <c r="D148" s="79">
         <f>E148*(1+$T$1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E148" s="79" t="e">
+        <v>1.125</v>
+      </c>
+      <c r="E148" s="79">
         <f>AVERAGE(G148:Q148)</f>
-        <v>#DIV/0!</v>
+        <v>0.75</v>
       </c>
       <c r="F148" s="79" t="e">
         <f>STDEV(G148:Q148)</f>
@@ -38965,19 +39043,29 @@
       </c>
       <c r="G148" s="79"/>
       <c r="H148" s="79"/>
-      <c r="I148" s="79"/>
+      <c r="I148" s="79">
+        <v>0.75</v>
+      </c>
       <c r="J148" s="140"/>
       <c r="K148" s="141"/>
     </row>
     <row r="149" spans="1:15">
-      <c r="A149" s="322"/>
-      <c r="D149" s="79" t="e">
+      <c r="A149" s="322" t="s">
+        <v>142</v>
+      </c>
+      <c r="B149" t="s">
+        <v>49</v>
+      </c>
+      <c r="C149" t="s">
+        <v>897</v>
+      </c>
+      <c r="D149" s="79">
         <f>E149*(1+$T$1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E149" s="79" t="e">
+        <v>2.9249999999999998</v>
+      </c>
+      <c r="E149" s="79">
         <f>AVERAGE(G149:Q149)</f>
-        <v>#DIV/0!</v>
+        <v>1.95</v>
       </c>
       <c r="F149" s="79" t="e">
         <f>STDEV(G149:Q149)</f>
@@ -38988,26 +39076,43 @@
       <c r="I149" s="79"/>
       <c r="J149" s="140"/>
       <c r="K149" s="141"/>
+      <c r="O149" s="155">
+        <v>1.95</v>
+      </c>
     </row>
     <row r="150" spans="1:15">
-      <c r="A150" s="322"/>
-      <c r="D150" s="79" t="e">
+      <c r="A150" s="322" t="s">
+        <v>142</v>
+      </c>
+      <c r="B150" t="s">
+        <v>33</v>
+      </c>
+      <c r="C150" t="s">
+        <v>898</v>
+      </c>
+      <c r="D150" s="79">
         <f>E150*(1+$T$1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E150" s="79" t="e">
+        <v>3.6524999999999999</v>
+      </c>
+      <c r="E150" s="79">
         <f>AVERAGE(G150:Q150)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F150" s="79" t="e">
+        <v>2.4350000000000001</v>
+      </c>
+      <c r="F150" s="79">
         <f>STDEV(G150:Q150)</f>
-        <v>#DIV/0!</v>
+        <v>9.1923881554251102E-2</v>
       </c>
       <c r="G150" s="79"/>
       <c r="H150" s="79"/>
       <c r="I150" s="79"/>
       <c r="J150" s="140"/>
       <c r="K150" s="141"/>
+      <c r="N150" s="155">
+        <v>2.5</v>
+      </c>
+      <c r="O150" s="155">
+        <v>2.37</v>
+      </c>
     </row>
     <row r="151" spans="1:15">
       <c r="A151" s="322"/>
@@ -39110,7 +39215,7 @@
       <c r="K155" s="141"/>
     </row>
     <row r="156" spans="1:15">
-      <c r="A156" s="156"/>
+      <c r="A156" s="322"/>
       <c r="D156" s="79" t="e">
         <f>E156*(1+$T$1)</f>
         <v>#DIV/0!</v>
@@ -39125,12 +39230,12 @@
       </c>
       <c r="G156" s="79"/>
       <c r="H156" s="79"/>
-      <c r="I156" s="157"/>
+      <c r="I156" s="79"/>
       <c r="J156" s="140"/>
       <c r="K156" s="141"/>
     </row>
     <row r="157" spans="1:15">
-      <c r="A157" s="156"/>
+      <c r="A157" s="322"/>
       <c r="D157" s="79" t="e">
         <f>E157*(1+$T$1)</f>
         <v>#DIV/0!</v>
@@ -39145,12 +39250,12 @@
       </c>
       <c r="G157" s="79"/>
       <c r="H157" s="79"/>
-      <c r="I157" s="157"/>
+      <c r="I157" s="79"/>
       <c r="J157" s="140"/>
       <c r="K157" s="141"/>
     </row>
     <row r="158" spans="1:15">
-      <c r="A158" s="156"/>
+      <c r="A158" s="322"/>
       <c r="D158" s="79" t="e">
         <f>E158*(1+$T$1)</f>
         <v>#DIV/0!</v>
@@ -39165,12 +39270,12 @@
       </c>
       <c r="G158" s="79"/>
       <c r="H158" s="79"/>
-      <c r="I158" s="157"/>
+      <c r="I158" s="79"/>
       <c r="J158" s="140"/>
       <c r="K158" s="141"/>
     </row>
     <row r="159" spans="1:15">
-      <c r="A159" s="156"/>
+      <c r="A159" s="322"/>
       <c r="D159" s="79" t="e">
         <f>E159*(1+$T$1)</f>
         <v>#DIV/0!</v>
@@ -39185,7 +39290,7 @@
       </c>
       <c r="G159" s="79"/>
       <c r="H159" s="79"/>
-      <c r="I159" s="157"/>
+      <c r="I159" s="79"/>
       <c r="J159" s="140"/>
       <c r="K159" s="141"/>
     </row>
@@ -39210,7 +39315,7 @@
       <c r="K160" s="141"/>
     </row>
     <row r="161" spans="1:11">
-      <c r="A161" s="322"/>
+      <c r="A161" s="156"/>
       <c r="D161" s="79" t="e">
         <f>E161*(1+$T$1)</f>
         <v>#DIV/0!</v>
@@ -39225,12 +39330,12 @@
       </c>
       <c r="G161" s="79"/>
       <c r="H161" s="79"/>
-      <c r="I161" s="79"/>
+      <c r="I161" s="157"/>
       <c r="J161" s="140"/>
       <c r="K161" s="141"/>
     </row>
     <row r="162" spans="1:11">
-      <c r="A162" s="322"/>
+      <c r="A162" s="156"/>
       <c r="D162" s="79" t="e">
         <f>E162*(1+$T$1)</f>
         <v>#DIV/0!</v>
@@ -39245,12 +39350,12 @@
       </c>
       <c r="G162" s="79"/>
       <c r="H162" s="79"/>
-      <c r="I162" s="79"/>
+      <c r="I162" s="157"/>
       <c r="J162" s="140"/>
       <c r="K162" s="141"/>
     </row>
     <row r="163" spans="1:11">
-      <c r="A163" s="322"/>
+      <c r="A163" s="156"/>
       <c r="D163" s="79" t="e">
         <f>E163*(1+$T$1)</f>
         <v>#DIV/0!</v>
@@ -39265,12 +39370,12 @@
       </c>
       <c r="G163" s="79"/>
       <c r="H163" s="79"/>
-      <c r="I163" s="79"/>
+      <c r="I163" s="157"/>
       <c r="J163" s="140"/>
       <c r="K163" s="141"/>
     </row>
     <row r="164" spans="1:11">
-      <c r="A164" s="322"/>
+      <c r="A164" s="156"/>
       <c r="D164" s="79" t="e">
         <f>E164*(1+$T$1)</f>
         <v>#DIV/0!</v>
@@ -39285,7 +39390,7 @@
       </c>
       <c r="G164" s="79"/>
       <c r="H164" s="79"/>
-      <c r="I164" s="79"/>
+      <c r="I164" s="157"/>
       <c r="J164" s="140"/>
       <c r="K164" s="141"/>
     </row>
@@ -39303,8 +39408,8 @@
         <f>STDEV(G165:Q165)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G165" s="140"/>
-      <c r="H165" s="140"/>
+      <c r="G165" s="79"/>
+      <c r="H165" s="79"/>
       <c r="I165" s="79"/>
       <c r="J165" s="140"/>
       <c r="K165" s="141"/>
@@ -39323,8 +39428,8 @@
         <f>STDEV(G166:Q166)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G166" s="140"/>
-      <c r="H166" s="140"/>
+      <c r="G166" s="79"/>
+      <c r="H166" s="79"/>
       <c r="I166" s="79"/>
       <c r="J166" s="140"/>
       <c r="K166" s="141"/>
@@ -39343,8 +39448,8 @@
         <f>STDEV(G167:Q167)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G167" s="140"/>
-      <c r="H167" s="140"/>
+      <c r="G167" s="79"/>
+      <c r="H167" s="79"/>
       <c r="I167" s="79"/>
       <c r="J167" s="140"/>
       <c r="K167" s="141"/>
@@ -39363,8 +39468,8 @@
         <f>STDEV(G168:Q168)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G168" s="140"/>
-      <c r="H168" s="140"/>
+      <c r="G168" s="79"/>
+      <c r="H168" s="79"/>
       <c r="I168" s="79"/>
       <c r="J168" s="140"/>
       <c r="K168" s="141"/>
@@ -40352,7 +40457,7 @@
     <row r="218" spans="1:11">
       <c r="A218" s="322"/>
       <c r="D218" s="79" t="e">
-        <f>E218*(1+$O$1)</f>
+        <f>E218*(1+$T$1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E218" s="79" t="e">
@@ -40372,7 +40477,7 @@
     <row r="219" spans="1:11">
       <c r="A219" s="322"/>
       <c r="D219" s="79" t="e">
-        <f>E219*(1+$O$1)</f>
+        <f>E219*(1+$T$1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E219" s="79" t="e">
@@ -40392,7 +40497,7 @@
     <row r="220" spans="1:11">
       <c r="A220" s="322"/>
       <c r="D220" s="79" t="e">
-        <f>E220*(1+$O$1)</f>
+        <f>E220*(1+$T$1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E220" s="79" t="e">
@@ -40412,7 +40517,7 @@
     <row r="221" spans="1:11">
       <c r="A221" s="322"/>
       <c r="D221" s="79" t="e">
-        <f>E221*(1+$O$1)</f>
+        <f>E221*(1+$T$1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E221" s="79" t="e">
@@ -40615,11 +40720,11 @@
         <f>E231*(1+$O$1)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E231" s="140" t="e">
+      <c r="E231" s="79" t="e">
         <f>AVERAGE(G231:Q231)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F231" s="140" t="e">
+      <c r="F231" s="79" t="e">
         <f>STDEV(G231:Q231)</f>
         <v>#DIV/0!</v>
       </c>
@@ -40635,11 +40740,11 @@
         <f>E232*(1+$O$1)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E232" s="140" t="e">
+      <c r="E232" s="79" t="e">
         <f>AVERAGE(G232:Q232)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F232" s="140" t="e">
+      <c r="F232" s="79" t="e">
         <f>STDEV(G232:Q232)</f>
         <v>#DIV/0!</v>
       </c>
@@ -40655,11 +40760,11 @@
         <f>E233*(1+$O$1)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E233" s="140" t="e">
+      <c r="E233" s="79" t="e">
         <f>AVERAGE(G233:Q233)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F233" s="140" t="e">
+      <c r="F233" s="79" t="e">
         <f>STDEV(G233:Q233)</f>
         <v>#DIV/0!</v>
       </c>
@@ -40675,11 +40780,11 @@
         <f>E234*(1+$O$1)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E234" s="140" t="e">
+      <c r="E234" s="79" t="e">
         <f>AVERAGE(G234:Q234)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F234" s="140" t="e">
+      <c r="F234" s="79" t="e">
         <f>STDEV(G234:Q234)</f>
         <v>#DIV/0!</v>
       </c>
@@ -40830,6 +40935,7 @@
       <c r="K241" s="141"/>
     </row>
     <row r="242" spans="1:11">
+      <c r="A242" s="322"/>
       <c r="D242" s="79" t="e">
         <f>E242*(1+$O$1)</f>
         <v>#DIV/0!</v>
@@ -40844,7 +40950,7 @@
       </c>
       <c r="G242" s="140"/>
       <c r="H242" s="140"/>
-      <c r="I242" s="140"/>
+      <c r="I242" s="79"/>
       <c r="J242" s="140"/>
       <c r="K242" s="141"/>
     </row>
@@ -40909,7 +41015,6 @@
       <c r="K245" s="141"/>
     </row>
     <row r="246" spans="1:11">
-      <c r="A246" s="322"/>
       <c r="D246" s="79" t="e">
         <f>E246*(1+$O$1)</f>
         <v>#DIV/0!</v>
@@ -40924,7 +41029,7 @@
       </c>
       <c r="G246" s="140"/>
       <c r="H246" s="140"/>
-      <c r="I246" s="79"/>
+      <c r="I246" s="140"/>
       <c r="J246" s="140"/>
       <c r="K246" s="141"/>
     </row>
@@ -41469,6 +41574,7 @@
       <c r="K273" s="141"/>
     </row>
     <row r="274" spans="1:11">
+      <c r="A274" s="322"/>
       <c r="D274" s="79" t="e">
         <f>E274*(1+$O$1)</f>
         <v>#DIV/0!</v>
@@ -41488,6 +41594,7 @@
       <c r="K274" s="141"/>
     </row>
     <row r="275" spans="1:11">
+      <c r="A275" s="322"/>
       <c r="D275" s="79" t="e">
         <f>E275*(1+$O$1)</f>
         <v>#DIV/0!</v>
@@ -41502,11 +41609,12 @@
       </c>
       <c r="G275" s="140"/>
       <c r="H275" s="140"/>
-      <c r="I275" s="140"/>
+      <c r="I275" s="79"/>
       <c r="J275" s="140"/>
       <c r="K275" s="141"/>
     </row>
     <row r="276" spans="1:11">
+      <c r="A276" s="322"/>
       <c r="D276" s="79" t="e">
         <f>E276*(1+$O$1)</f>
         <v>#DIV/0!</v>
@@ -41521,11 +41629,12 @@
       </c>
       <c r="G276" s="140"/>
       <c r="H276" s="140"/>
-      <c r="I276" s="140"/>
+      <c r="I276" s="79"/>
       <c r="J276" s="140"/>
       <c r="K276" s="141"/>
     </row>
     <row r="277" spans="1:11">
+      <c r="A277" s="322"/>
       <c r="D277" s="79" t="e">
         <f>E277*(1+$O$1)</f>
         <v>#DIV/0!</v>
@@ -41540,12 +41649,11 @@
       </c>
       <c r="G277" s="140"/>
       <c r="H277" s="140"/>
-      <c r="I277" s="140"/>
+      <c r="I277" s="79"/>
       <c r="J277" s="140"/>
       <c r="K277" s="141"/>
     </row>
     <row r="278" spans="1:11">
-      <c r="A278" s="322"/>
       <c r="D278" s="79" t="e">
         <f>E278*(1+$O$1)</f>
         <v>#DIV/0!</v>
@@ -41622,6 +41730,7 @@
       <c r="K281" s="141"/>
     </row>
     <row r="282" spans="1:11">
+      <c r="A282" s="322"/>
       <c r="D282" s="79" t="e">
         <f>E282*(1+$O$1)</f>
         <v>#DIV/0!</v>
@@ -41636,7 +41745,7 @@
       </c>
       <c r="G282" s="140"/>
       <c r="H282" s="140"/>
-      <c r="I282" s="140"/>
+      <c r="I282" s="79"/>
       <c r="J282" s="140"/>
       <c r="K282" s="141"/>
     </row>
@@ -41793,7 +41902,6 @@
       <c r="K290" s="141"/>
     </row>
     <row r="291" spans="1:11">
-      <c r="A291" s="156"/>
       <c r="D291" s="79" t="e">
         <f>E291*(1+$O$1)</f>
         <v>#DIV/0!</v>
@@ -41808,12 +41916,11 @@
       </c>
       <c r="G291" s="140"/>
       <c r="H291" s="140"/>
-      <c r="I291" s="157"/>
+      <c r="I291" s="140"/>
       <c r="J291" s="140"/>
       <c r="K291" s="141"/>
     </row>
     <row r="292" spans="1:11">
-      <c r="A292" s="156"/>
       <c r="D292" s="79" t="e">
         <f>E292*(1+$O$1)</f>
         <v>#DIV/0!</v>
@@ -41828,7 +41935,7 @@
       </c>
       <c r="G292" s="140"/>
       <c r="H292" s="140"/>
-      <c r="I292" s="157"/>
+      <c r="I292" s="140"/>
       <c r="J292" s="140"/>
       <c r="K292" s="141"/>
     </row>
@@ -41850,6 +41957,84 @@
       <c r="I293" s="140"/>
       <c r="J293" s="140"/>
       <c r="K293" s="141"/>
+    </row>
+    <row r="294" spans="1:11">
+      <c r="D294" s="79" t="e">
+        <f>E294*(1+$O$1)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E294" s="140" t="e">
+        <f>AVERAGE(G294:Q294)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F294" s="140" t="e">
+        <f>STDEV(G294:Q294)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G294" s="140"/>
+      <c r="H294" s="140"/>
+      <c r="I294" s="140"/>
+      <c r="J294" s="140"/>
+      <c r="K294" s="141"/>
+    </row>
+    <row r="295" spans="1:11">
+      <c r="A295" s="156"/>
+      <c r="D295" s="79" t="e">
+        <f>E295*(1+$O$1)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E295" s="140" t="e">
+        <f>AVERAGE(G295:Q295)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F295" s="140" t="e">
+        <f>STDEV(G295:Q295)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G295" s="140"/>
+      <c r="H295" s="140"/>
+      <c r="I295" s="157"/>
+      <c r="J295" s="140"/>
+      <c r="K295" s="141"/>
+    </row>
+    <row r="296" spans="1:11">
+      <c r="A296" s="156"/>
+      <c r="D296" s="79" t="e">
+        <f>E296*(1+$O$1)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E296" s="140" t="e">
+        <f>AVERAGE(G296:Q296)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F296" s="140" t="e">
+        <f>STDEV(G296:Q296)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G296" s="140"/>
+      <c r="H296" s="140"/>
+      <c r="I296" s="157"/>
+      <c r="J296" s="140"/>
+      <c r="K296" s="141"/>
+    </row>
+    <row r="297" spans="1:11">
+      <c r="D297" s="79" t="e">
+        <f>E297*(1+$O$1)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E297" s="140" t="e">
+        <f>AVERAGE(G297:Q297)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F297" s="140" t="e">
+        <f>STDEV(G297:Q297)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G297" s="140"/>
+      <c r="H297" s="140"/>
+      <c r="I297" s="140"/>
+      <c r="J297" s="140"/>
+      <c r="K297" s="141"/>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
@@ -60208,9 +60393,9 @@
       <c r="C4" s="246" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="248" t="e">
+      <c r="D4" s="248">
         <f>SUMPRODUCT(I4:I9, E4:E9)</f>
-        <v>#DIV/0!</v>
+        <v>22.89473511904762</v>
       </c>
       <c r="E4" s="212">
         <v>3</v>
@@ -60224,7 +60409,7 @@
       </c>
       <c r="I4" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Early Spring*", 'Master Variety List'!B:B, "*Focal*")</f>
-        <v>2.6483333333333334</v>
+        <v>2.5036666666666667</v>
       </c>
       <c r="J4" s="179">
         <v>500</v>
@@ -60298,9 +60483,9 @@
       <c r="H6" t="s">
         <v>159</v>
       </c>
-      <c r="I6" s="80" t="e">
+      <c r="I6" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Early Spring*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>#DIV/0!</v>
+        <v>1.6676041666666666</v>
       </c>
       <c r="J6" s="179">
         <v>100</v>
@@ -60331,7 +60516,7 @@
       </c>
       <c r="I7" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Early Spring*", 'Master Variety List'!B:B, "*Float*")</f>
-        <v>1.606111111111111</v>
+        <v>1.5766666666666667</v>
       </c>
       <c r="J7" s="179">
         <v>400</v>
@@ -62901,7 +63086,7 @@
       </c>
       <c r="E4" s="248">
         <f>SUMPRODUCT(F4:F9, J4:J9)</f>
-        <v>60.315841697010818</v>
+        <v>58.764747231627346</v>
       </c>
       <c r="F4" s="212">
         <v>6</v>
@@ -62915,7 +63100,7 @@
       </c>
       <c r="J4" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Late Spring*", 'Master Variety List'!B:B, "*Focal*")</f>
-        <v>3.7952380952380955</v>
+        <v>3.5614583333333334</v>
       </c>
       <c r="K4" s="181">
         <v>500</v>
@@ -62944,7 +63129,7 @@
       </c>
       <c r="J5" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Late Spring*", 'Master Variety List'!B:B, "*Foundation*")</f>
-        <v>1.6468928571428569</v>
+        <v>1.6612666666666667</v>
       </c>
       <c r="K5" s="181">
         <v>1711</v>
@@ -62973,7 +63158,7 @@
       </c>
       <c r="J6" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Late Spring*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>1.6592708333333335</v>
+        <v>1.6491111111111112</v>
       </c>
       <c r="K6" s="181">
         <v>264</v>
@@ -63002,7 +63187,7 @@
       </c>
       <c r="J7" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Late Spring*", 'Master Variety List'!B:B, "*Float*")</f>
-        <v>1.4887500000000002</v>
+        <v>1.4819230769230769</v>
       </c>
       <c r="K7" s="181">
         <v>83</v>
@@ -63031,7 +63216,7 @@
       </c>
       <c r="J8" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Late Spring*", 'Master Variety List'!B:B, "*Finisher*")</f>
-        <v>1.7462500000000001</v>
+        <v>1.7894791666666667</v>
       </c>
       <c r="K8" s="181">
         <v>30</v>
@@ -63061,7 +63246,7 @@
       </c>
       <c r="J9" s="170">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Late Spring*", 'Master Variety List'!B:B, "*Foliage*")</f>
-        <v>1.4645454545454548</v>
+        <v>1.4383333333333335</v>
       </c>
       <c r="K9" s="182">
         <v>1000</v>
@@ -63985,9 +64170,9 @@
       <c r="D4" s="246" t="s">
         <v>123</v>
       </c>
-      <c r="E4" s="248" t="e">
+      <c r="E4" s="248">
         <f>SUMPRODUCT(J4:J9, F4:F9)</f>
-        <v>#DIV/0!</v>
+        <v>39.527724547382448</v>
       </c>
       <c r="F4" s="212">
         <v>3</v>
@@ -64032,7 +64217,7 @@
       </c>
       <c r="J5" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Summer*", 'Master Variety List'!B:B, "*Foundation*")</f>
-        <v>1.6459353741496598</v>
+        <v>1.6591883116883117</v>
       </c>
       <c r="K5" s="184">
         <v>2000</v>
@@ -64061,9 +64246,9 @@
       <c r="I6" t="s">
         <v>159</v>
       </c>
-      <c r="J6" s="80" t="e">
+      <c r="J6" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Summer*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>#DIV/0!</v>
+        <v>1.6082894736842104</v>
       </c>
       <c r="K6" s="184">
         <v>500</v>
@@ -64125,7 +64310,7 @@
       </c>
       <c r="J8" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Summer*", 'Master Variety List'!B:B, "*Finisher*")</f>
-        <v>1.7997916666666669</v>
+        <v>1.7747807017543862</v>
       </c>
       <c r="K8" s="184">
         <v>50</v>
@@ -64157,7 +64342,7 @@
       </c>
       <c r="J9" s="170">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Summer*", 'Master Variety List'!B:B, "*Foliage*")</f>
-        <v>1.461153846153846</v>
+        <v>1.4392307692307693</v>
       </c>
       <c r="K9" s="185">
         <v>150</v>
@@ -67080,9 +67265,9 @@
       <c r="J2" s="73"/>
       <c r="K2" s="80"/>
       <c r="L2" s="80"/>
-      <c r="O2" s="163" t="e">
+      <c r="O2" s="163">
         <f>MIN($D$24)</f>
-        <v>#DIV/0!</v>
+        <v>55.962819066898014</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="21" customHeight="1">
@@ -67115,9 +67300,9 @@
       <c r="K4" s="159"/>
       <c r="L4" s="159"/>
       <c r="M4" s="159"/>
-      <c r="O4" t="e">
+      <c r="O4" t="b">
         <f>$D$24&lt;=37</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="19">
@@ -67134,9 +67319,9 @@
       <c r="K5" s="159"/>
       <c r="L5" s="159"/>
       <c r="M5" s="159"/>
-      <c r="O5" t="e">
+      <c r="O5" t="b">
         <f>$D$24&gt;=34.5</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="19">
@@ -67275,9 +67460,9 @@
       <c r="C13" s="246" t="s">
         <v>511</v>
       </c>
-      <c r="D13" s="248" t="e">
+      <c r="D13" s="248">
         <f>SUMPRODUCT(E13:E18, I13:I18)</f>
-        <v>#DIV/0!</v>
+        <v>34.883142068457857</v>
       </c>
       <c r="E13" s="212">
         <v>3</v>
@@ -67325,7 +67510,7 @@
       </c>
       <c r="I14" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foundation*")</f>
-        <v>1.6459353741496598</v>
+        <v>1.6591883116883117</v>
       </c>
       <c r="J14" s="188">
         <v>400</v>
@@ -67357,9 +67542,9 @@
       <c r="H15" t="s">
         <v>159</v>
       </c>
-      <c r="I15" s="80" t="e">
+      <c r="I15" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>#DIV/0!</v>
+        <v>1.6082894736842104</v>
       </c>
       <c r="J15" s="188">
         <v>120</v>
@@ -67427,7 +67612,7 @@
       </c>
       <c r="I17" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Finisher*")</f>
-        <v>1.7997916666666669</v>
+        <v>1.7747807017543862</v>
       </c>
       <c r="J17" s="188">
         <v>250</v>
@@ -67462,7 +67647,7 @@
       </c>
       <c r="I18" s="170">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foliage*")</f>
-        <v>1.461153846153846</v>
+        <v>1.4392307692307693</v>
       </c>
       <c r="J18" s="189">
         <v>300</v>
@@ -67573,9 +67758,9 @@
       <c r="C24" s="246" t="s">
         <v>511</v>
       </c>
-      <c r="D24" s="248" t="e">
+      <c r="D24" s="248">
         <f>SUMPRODUCT(I24:I29, E24:E29)</f>
-        <v>#DIV/0!</v>
+        <v>55.962819066898014</v>
       </c>
       <c r="E24" s="212">
         <v>5</v>
@@ -67620,7 +67805,7 @@
       </c>
       <c r="I25" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foundation*")</f>
-        <v>1.6459353741496598</v>
+        <v>1.6591883116883117</v>
       </c>
       <c r="J25" s="192">
         <f t="shared" si="2"/>
@@ -67649,9 +67834,9 @@
       <c r="H26" t="s">
         <v>159</v>
       </c>
-      <c r="I26" s="80" t="e">
+      <c r="I26" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>#DIV/0!</v>
+        <v>1.6082894736842104</v>
       </c>
       <c r="J26" s="192">
         <f t="shared" si="2"/>
@@ -67713,7 +67898,7 @@
       </c>
       <c r="I28" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Finisher*")</f>
-        <v>1.7997916666666669</v>
+        <v>1.7747807017543862</v>
       </c>
       <c r="J28" s="192">
         <f t="shared" si="2"/>
@@ -67745,7 +67930,7 @@
       </c>
       <c r="I29" s="170">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foliage*")</f>
-        <v>1.461153846153846</v>
+        <v>1.4392307692307693</v>
       </c>
       <c r="J29" s="193">
         <f t="shared" si="2"/>
@@ -67826,9 +68011,9 @@
       <c r="C34" s="246" t="s">
         <v>511</v>
       </c>
-      <c r="D34" s="248" t="e">
+      <c r="D34" s="248">
         <f>SUMPRODUCT(E34:E39, I34:I39)</f>
-        <v>#DIV/0!</v>
+        <v>21.882016562384987</v>
       </c>
       <c r="E34" s="212">
         <v>1</v>
@@ -67873,7 +68058,7 @@
       </c>
       <c r="I35" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foundation*")</f>
-        <v>1.6459353741496598</v>
+        <v>1.6591883116883117</v>
       </c>
       <c r="J35" s="192">
         <f t="shared" si="5"/>
@@ -67902,9 +68087,9 @@
       <c r="H36" t="s">
         <v>159</v>
       </c>
-      <c r="I36" s="80" t="e">
+      <c r="I36" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>#DIV/0!</v>
+        <v>1.6082894736842104</v>
       </c>
       <c r="J36" s="192">
         <f t="shared" si="5"/>
@@ -67966,7 +68151,7 @@
       </c>
       <c r="I38" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Finisher*")</f>
-        <v>1.7997916666666669</v>
+        <v>1.7747807017543862</v>
       </c>
       <c r="J38" s="192">
         <f t="shared" si="5"/>
@@ -67998,7 +68183,7 @@
       </c>
       <c r="I39" s="170">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foliage*")</f>
-        <v>1.461153846153846</v>
+        <v>1.4392307692307693</v>
       </c>
       <c r="J39" s="192">
         <f t="shared" si="5"/>
@@ -68056,9 +68241,9 @@
       <c r="C43" s="246" t="s">
         <v>511</v>
       </c>
-      <c r="D43" s="248" t="e">
+      <c r="D43" s="248">
         <f>SUMPRODUCT(E43:E48, I43:I48)</f>
-        <v>#DIV/0!</v>
+        <v>23.506125506072873</v>
       </c>
       <c r="E43" s="212">
         <v>7</v>
@@ -68103,7 +68288,7 @@
       </c>
       <c r="I44" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foundation*")</f>
-        <v>1.6459353741496598</v>
+        <v>1.6591883116883117</v>
       </c>
       <c r="J44" s="192">
         <f t="shared" si="9"/>
@@ -68132,9 +68317,9 @@
       <c r="H45" t="s">
         <v>159</v>
       </c>
-      <c r="I45" s="80" t="e">
+      <c r="I45" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>#DIV/0!</v>
+        <v>1.6082894736842104</v>
       </c>
       <c r="J45" s="192">
         <f t="shared" si="9"/>
@@ -68196,7 +68381,7 @@
       </c>
       <c r="I47" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Finisher*")</f>
-        <v>1.7997916666666669</v>
+        <v>1.7747807017543862</v>
       </c>
       <c r="J47" s="192">
         <f t="shared" si="9"/>
@@ -68228,7 +68413,7 @@
       </c>
       <c r="I48" s="170">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foliage*")</f>
-        <v>1.461153846153846</v>
+        <v>1.4392307692307693</v>
       </c>
       <c r="J48" s="192">
         <f t="shared" si="9"/>

--- a/data/CANONICAL Bouquet Recipe Master Sheet.xlsx
+++ b/data/CANONICAL Bouquet Recipe Master Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sharon/Documents/Sweet Piedmont/Offerings/Software and Code/bouquet-blueprint-app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3070DFDE-9FCF-4747-B5F0-C2F68FD84ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB7FD66-BB92-F64B-9D53-C7443EC64516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="920" windowWidth="34240" windowHeight="21260" firstSheet="1" activeTab="1" xr2:uid="{835A2F5B-2282-E345-9D43-16C3FBECA701}"/>
   </bookViews>
@@ -543,7 +543,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5349" uniqueCount="947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5356" uniqueCount="954">
   <si>
     <t>CANONICAL PRICING WORKBOOK</t>
   </si>
@@ -3417,6 +3417,27 @@
   </si>
   <si>
     <t>Spirea branch</t>
+  </si>
+  <si>
+    <t>focal average</t>
+  </si>
+  <si>
+    <t>foundation average</t>
+  </si>
+  <si>
+    <t>filler average</t>
+  </si>
+  <si>
+    <t>floater average</t>
+  </si>
+  <si>
+    <t>finisher average</t>
+  </si>
+  <si>
+    <t>foliage average</t>
+  </si>
+  <si>
+    <t>average</t>
   </si>
 </sst>
 </file>
@@ -11671,7 +11692,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{63FB889B-362F-FA4D-9D4D-A49BD91E0CC2}" name="Table31615" displayName="Table31615" ref="A1:K297" totalsRowShown="0" headerRowDxfId="143" dataDxfId="142" tableBorderDxfId="141" headerRowCellStyle="Currency" dataCellStyle="Currency">
   <autoFilter ref="A1:K297" xr:uid="{63FB889B-362F-FA4D-9D4D-A49BD91E0CC2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K297">
-    <sortCondition ref="C1:C297"/>
+    <sortCondition ref="B1:B297"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{CD3DACDE-DD55-C44F-80CC-C1C7B474F6D3}" name="Season"/>
@@ -33940,26 +33961,24 @@
         <v>142</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D2" s="79">
-        <f>E2*(1+$T$1)</f>
-        <v>1.9424999999999999</v>
+        <v>906</v>
+      </c>
+      <c r="D2" s="79" t="e">
+        <f>E2*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E2" s="79">
         <f>AVERAGE(G2:Q2)</f>
-        <v>1.2949999999999999</v>
-      </c>
-      <c r="F2" s="79">
+        <v>1.29</v>
+      </c>
+      <c r="F2" s="79" t="e">
         <f>STDEV(G2:Q2)</f>
-        <v>7.0710678118654814E-3</v>
-      </c>
-      <c r="G2" s="79">
-        <v>1.3</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G2" s="79"/>
       <c r="H2" s="79"/>
       <c r="I2" s="79"/>
       <c r="J2" s="140"/>
@@ -33971,68 +33990,80 @@
       <c r="T2" s="159"/>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="322" t="s">
-        <v>30</v>
+      <c r="A3" t="s">
+        <v>142</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D3" s="79">
         <f>E3*(1+$T$1)</f>
-        <v>1.5</v>
+        <v>5.6999999999999993</v>
       </c>
       <c r="E3" s="79">
         <f>AVERAGE(G3:Q3)</f>
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="F3" s="79" t="e">
         <f>STDEV(G3:Q3)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79">
-        <v>1</v>
-      </c>
+      <c r="H3" s="79">
+        <v>3.8</v>
+      </c>
+      <c r="I3" s="79"/>
       <c r="J3" s="140"/>
       <c r="K3" s="141"/>
-      <c r="S3" s="112"/>
+      <c r="R3">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="S3" s="159" t="s">
+        <v>947</v>
+      </c>
       <c r="T3" s="159"/>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="322" t="s">
-        <v>55</v>
+        <v>892</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>896</v>
+        <v>916</v>
       </c>
       <c r="D4" s="79">
         <f>E4*(1+$T$1)</f>
-        <v>2.4000000000000004</v>
+        <v>2.5425</v>
       </c>
       <c r="E4" s="79">
         <f>AVERAGE(G4:Q4)</f>
-        <v>1.6</v>
-      </c>
-      <c r="F4" s="79" t="e">
+        <v>1.6950000000000001</v>
+      </c>
+      <c r="F4" s="79">
         <f>STDEV(G4:Q4)</f>
-        <v>#DIV/0!</v>
+        <v>0.134350288425444</v>
       </c>
       <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
+      <c r="H4" s="79">
+        <v>1.79</v>
+      </c>
       <c r="I4" s="79"/>
       <c r="J4" s="140"/>
       <c r="K4" s="141"/>
       <c r="O4" s="155">
         <v>1.6</v>
       </c>
-      <c r="S4" s="112"/>
+      <c r="R4">
+        <v>1.73</v>
+      </c>
+      <c r="S4" s="159" t="s">
+        <v>948</v>
+      </c>
       <c r="T4" s="159"/>
     </row>
     <row r="5" spans="1:20">
@@ -34040,30 +34071,30 @@
         <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>895</v>
+        <v>70</v>
       </c>
       <c r="D5" s="79">
         <f>E5*(1+$T$1)</f>
-        <v>2.5687500000000001</v>
+        <v>4.3312500000000007</v>
       </c>
       <c r="E5" s="79">
         <f>AVERAGE(G5:Q5)</f>
-        <v>1.7125000000000001</v>
+        <v>2.8875000000000002</v>
       </c>
       <c r="F5" s="79">
         <f>STDEV(G5:Q5)</f>
-        <v>0.35677957714346031</v>
-      </c>
-      <c r="G5" s="79"/>
+        <v>1.2976742015364773</v>
+      </c>
+      <c r="G5" s="79">
+        <v>4</v>
+      </c>
       <c r="H5" s="79">
-        <v>1.5</v>
-      </c>
-      <c r="I5" s="79">
-        <v>1.75</v>
-      </c>
+        <v>3.95</v>
+      </c>
+      <c r="I5" s="79"/>
       <c r="J5" s="140"/>
       <c r="K5" s="141"/>
       <c r="L5" s="155">
@@ -34072,36 +34103,41 @@
       <c r="O5" s="155">
         <v>2.2000000000000002</v>
       </c>
-      <c r="S5" s="112"/>
+      <c r="R5">
+        <v>1.79</v>
+      </c>
+      <c r="S5" s="159" t="s">
+        <v>949</v>
+      </c>
       <c r="T5" s="159"/>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="322" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="D6" s="79">
         <f>E6*(1+$T$1)</f>
-        <v>2.9125000000000001</v>
+        <v>4.3975</v>
       </c>
       <c r="E6" s="79">
         <f>AVERAGE(G6:Q6)</f>
-        <v>1.9416666666666667</v>
+        <v>2.9316666666666666</v>
       </c>
       <c r="F6" s="79">
         <f>STDEV(G6:Q6)</f>
-        <v>0.56325541867492657</v>
+        <v>1.3059160258863001</v>
       </c>
       <c r="G6" s="79">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="79">
-        <v>1.71</v>
+        <v>4.95</v>
       </c>
       <c r="I6" s="79"/>
       <c r="J6" s="140"/>
@@ -34118,34 +34154,41 @@
       <c r="P6" s="155">
         <v>2.99</v>
       </c>
-      <c r="S6" s="112"/>
+      <c r="R6" s="155">
+        <v>1.94</v>
+      </c>
+      <c r="S6" s="159" t="s">
+        <v>950</v>
+      </c>
       <c r="T6" s="159"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="322" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="D7" s="79">
         <f>E7*(1+$T$1)</f>
-        <v>3.5287500000000001</v>
+        <v>4.6229999999999993</v>
       </c>
       <c r="E7" s="79">
         <f>AVERAGE(G7:Q7)</f>
-        <v>2.3525</v>
+        <v>3.0819999999999999</v>
       </c>
       <c r="F7" s="79">
         <f>STDEV(G7:Q7)</f>
-        <v>0.27158485475691263</v>
-      </c>
-      <c r="G7" s="79"/>
+        <v>0.81619237928321953</v>
+      </c>
+      <c r="G7" s="79">
+        <v>4</v>
+      </c>
       <c r="H7" s="79">
-        <v>1.95</v>
+        <v>3.95</v>
       </c>
       <c r="I7" s="79"/>
       <c r="J7" s="140"/>
@@ -34159,7 +34202,12 @@
       <c r="P7" s="155">
         <v>2.5299999999999998</v>
       </c>
-      <c r="S7" s="112"/>
+      <c r="R7">
+        <v>1.65</v>
+      </c>
+      <c r="S7" s="159" t="s">
+        <v>951</v>
+      </c>
       <c r="T7" s="159"/>
     </row>
     <row r="8" spans="1:20">
@@ -34167,28 +34215,28 @@
         <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D8" s="79">
         <f>E8*(1+$T$1)</f>
-        <v>2.9475000000000002</v>
+        <v>4.1474999999999991</v>
       </c>
       <c r="E8" s="79">
         <f>AVERAGE(G8:Q8)</f>
-        <v>1.9650000000000001</v>
+        <v>2.7649999999999997</v>
       </c>
       <c r="F8" s="79">
         <f>STDEV(G8:Q8)</f>
-        <v>0.60737138556240855</v>
+        <v>0.69057946682478399</v>
       </c>
       <c r="G8" s="79">
-        <v>1.1000000000000001</v>
+        <v>3</v>
       </c>
       <c r="H8" s="79">
-        <v>2.2999999999999998</v>
+        <v>3.6</v>
       </c>
       <c r="I8" s="79"/>
       <c r="J8" s="140"/>
@@ -34199,7 +34247,12 @@
       <c r="O8" s="155">
         <v>2.46</v>
       </c>
-      <c r="S8" s="112"/>
+      <c r="R8">
+        <v>1.65</v>
+      </c>
+      <c r="S8" s="159" t="s">
+        <v>952</v>
+      </c>
       <c r="T8" s="159"/>
     </row>
     <row r="9" spans="1:20">
@@ -34207,28 +34260,28 @@
         <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="D9" s="79">
         <f>E9*(1+$T$1)</f>
-        <v>2.9475000000000002</v>
+        <v>4.1662499999999998</v>
       </c>
       <c r="E9" s="79">
         <f>AVERAGE(G9:Q9)</f>
-        <v>1.9650000000000001</v>
+        <v>2.7774999999999999</v>
       </c>
       <c r="F9" s="79">
         <f>STDEV(G9:Q9)</f>
-        <v>0.60737138556240855</v>
+        <v>0.71088559792229122</v>
       </c>
       <c r="G9" s="79">
-        <v>1.1000000000000001</v>
+        <v>3</v>
       </c>
       <c r="H9" s="79">
-        <v>2.2999999999999998</v>
+        <v>3.65</v>
       </c>
       <c r="I9" s="79"/>
       <c r="J9" s="140"/>
@@ -34239,38 +34292,36 @@
       <c r="O9" s="155">
         <v>2.46</v>
       </c>
-      <c r="S9" s="112"/>
+      <c r="S9" s="159"/>
       <c r="T9" s="159"/>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="322" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>944</v>
       </c>
       <c r="D10" s="79">
         <f>E10*(1+$T$1)</f>
-        <v>2.8537500000000002</v>
+        <v>3.0300000000000002</v>
       </c>
       <c r="E10" s="79">
         <f>AVERAGE(G10:Q10)</f>
-        <v>1.9025000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="F10" s="79">
         <f>STDEV(G10:Q10)</f>
-        <v>0.7949999999999996</v>
-      </c>
-      <c r="G10" s="79">
-        <v>0.75</v>
-      </c>
-      <c r="H10" s="79">
-        <v>2.4</v>
-      </c>
-      <c r="I10" s="79"/>
+        <v>0.43034869582699925</v>
+      </c>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79">
+        <v>1.6</v>
+      </c>
       <c r="J10" s="140"/>
       <c r="K10" s="141"/>
       <c r="L10" s="155">
@@ -34279,39 +34330,44 @@
       <c r="O10" s="155">
         <v>2.46</v>
       </c>
-      <c r="S10" s="112"/>
+      <c r="R10">
+        <v>1.82</v>
+      </c>
+      <c r="S10" s="159" t="s">
+        <v>953</v>
+      </c>
       <c r="T10" s="159"/>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="322" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="79">
-        <f>E11*(1+$T$1)</f>
-        <v>2.8537500000000002</v>
+        <v>915</v>
+      </c>
+      <c r="D11" s="79" t="e">
+        <f>E11*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E11" s="79">
         <f>AVERAGE(G11:Q11)</f>
-        <v>1.9025000000000001</v>
+        <v>2.7649999999999997</v>
       </c>
       <c r="F11" s="79">
         <f>STDEV(G11:Q11)</f>
-        <v>0.7949999999999996</v>
-      </c>
-      <c r="G11" s="79">
-        <v>0.75</v>
-      </c>
+        <v>0.86230311762550682</v>
+      </c>
+      <c r="G11" s="79"/>
       <c r="H11" s="79">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="I11" s="79"/>
-      <c r="J11" s="140"/>
+      <c r="J11" s="140">
+        <v>2.6</v>
+      </c>
       <c r="K11" s="141"/>
       <c r="L11" s="155">
         <v>2</v>
@@ -34324,34 +34380,34 @@
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="322" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D12" s="79">
         <f>E12*(1+$T$1)</f>
-        <v>2.4299999999999997</v>
+        <v>2.9512499999999999</v>
       </c>
       <c r="E12" s="79">
         <f>AVERAGE(G12:Q12)</f>
-        <v>1.6199999999999999</v>
+        <v>1.9674999999999998</v>
       </c>
       <c r="F12" s="79">
         <f>STDEV(G12:Q12)</f>
-        <v>0.63895748424027965</v>
-      </c>
-      <c r="G12" s="79">
-        <v>1.1000000000000001</v>
-      </c>
+        <v>0.38221939598438426</v>
+      </c>
+      <c r="G12" s="79"/>
       <c r="H12" s="79">
-        <v>1.2</v>
+        <v>1.99</v>
       </c>
       <c r="I12" s="79"/>
-      <c r="J12" s="140"/>
+      <c r="J12" s="140">
+        <v>1.7</v>
+      </c>
       <c r="K12" s="141"/>
       <c r="L12" s="155">
         <v>2.5</v>
@@ -34364,29 +34420,33 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="322" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>923</v>
-      </c>
-      <c r="D13" s="79" t="e">
-        <f>E13*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>23</v>
+      </c>
+      <c r="D13" s="79">
+        <f>E13*(1+$T$1)</f>
+        <v>2.95</v>
       </c>
       <c r="E13" s="79">
         <f>AVERAGE(G13:Q13)</f>
-        <v>1.5</v>
-      </c>
-      <c r="F13" s="79" t="e">
+        <v>1.9666666666666668</v>
+      </c>
+      <c r="F13" s="79">
         <f>STDEV(G13:Q13)</f>
-        <v>#DIV/0!</v>
+        <v>0.50332229568471631</v>
       </c>
       <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="79"/>
+      <c r="H13" s="79">
+        <v>1.9</v>
+      </c>
+      <c r="I13" s="79">
+        <v>2.5</v>
+      </c>
       <c r="J13" s="140"/>
       <c r="K13" s="141"/>
       <c r="O13" s="155">
@@ -34396,14 +34456,14 @@
       <c r="T13" s="159"/>
     </row>
     <row r="14" spans="1:20">
-      <c r="A14" s="322" t="s">
-        <v>55</v>
+      <c r="A14" t="s">
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>899</v>
+        <v>921</v>
       </c>
       <c r="D14" s="79" t="e">
         <f>E14*(1+$O$1)</f>
@@ -34411,52 +34471,62 @@
       </c>
       <c r="E14" s="79">
         <f>AVERAGE(G14:Q14)</f>
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="F14" s="79" t="e">
+        <v>2.13</v>
+      </c>
+      <c r="F14" s="79">
         <f>STDEV(G14:Q14)</f>
-        <v>#DIV/0!</v>
+        <v>0.16970562748477155</v>
       </c>
       <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
+      <c r="H14" s="79">
+        <v>2.25</v>
+      </c>
       <c r="I14" s="79"/>
       <c r="J14" s="140"/>
       <c r="K14" s="141"/>
       <c r="O14" s="155">
         <v>2.0099999999999998</v>
       </c>
+      <c r="R14">
+        <v>1.73</v>
+      </c>
       <c r="S14" s="112"/>
       <c r="T14" s="159"/>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="322" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="D15" s="79">
         <f>E15*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>4.875</v>
       </c>
       <c r="E15" s="79">
         <f>AVERAGE(G15:Q15)</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F15" s="79" t="e">
+        <v>3.25</v>
+      </c>
+      <c r="F15" s="79">
         <f>STDEV(G15:Q15)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G15" s="140"/>
-      <c r="H15" s="140"/>
+        <v>1.0606601717798212</v>
+      </c>
+      <c r="G15" s="79"/>
+      <c r="H15" s="79">
+        <v>4</v>
+      </c>
       <c r="I15" s="79">
-        <v>1.1000000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="J15" s="140"/>
       <c r="K15" s="141"/>
+      <c r="R15">
+        <v>1.73</v>
+      </c>
       <c r="S15" s="112"/>
       <c r="T15" s="159"/>
     </row>
@@ -34465,30 +34535,33 @@
         <v>142</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="D16" s="79">
         <f>E16*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>2.4749999999999996</v>
       </c>
       <c r="E16" s="79">
         <f>AVERAGE(G16:Q16)</f>
-        <v>1.1000000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="F16" s="79" t="e">
         <f>STDEV(G16:Q16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="140"/>
-      <c r="H16" s="140"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="79"/>
       <c r="I16" s="79">
-        <v>1.1000000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="J16" s="140"/>
       <c r="K16" s="141"/>
+      <c r="R16">
+        <v>1.73</v>
+      </c>
       <c r="S16" s="112"/>
       <c r="T16" s="159"/>
     </row>
@@ -34497,27 +34570,25 @@
         <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>896</v>
       </c>
       <c r="D17" s="79">
         <f>E17*(1+$T$1)</f>
-        <v>1.7250000000000001</v>
+        <v>1.7625000000000002</v>
       </c>
       <c r="E17" s="79">
         <f>AVERAGE(G17:Q17)</f>
-        <v>1.1500000000000001</v>
+        <v>1.175</v>
       </c>
       <c r="F17" s="79">
         <f>STDEV(G17:Q17)</f>
-        <v>8.660254037844381E-2</v>
+        <v>0.10606601717798207</v>
       </c>
       <c r="G17" s="79"/>
-      <c r="H17" s="79">
-        <v>1.1000000000000001</v>
-      </c>
+      <c r="H17" s="79"/>
       <c r="I17" s="79"/>
       <c r="J17" s="140"/>
       <c r="K17" s="141"/>
@@ -34532,29 +34603,29 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18" s="322" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="D18" s="79">
         <f>E18*(1+$T$1)</f>
-        <v>1.7250000000000001</v>
+        <v>2.1500000000000004</v>
       </c>
       <c r="E18" s="79">
         <f>AVERAGE(G18:Q18)</f>
-        <v>1.1500000000000001</v>
+        <v>1.4333333333333336</v>
       </c>
       <c r="F18" s="79">
         <f>STDEV(G18:Q18)</f>
-        <v>8.660254037844381E-2</v>
+        <v>0.45368858629387254</v>
       </c>
       <c r="G18" s="79"/>
       <c r="H18" s="79">
-        <v>1.1000000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="I18" s="79"/>
       <c r="J18" s="140"/>
@@ -34570,28 +34641,32 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="322" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>900</v>
-      </c>
-      <c r="D19" s="79" t="e">
-        <f>E19*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>57</v>
+      </c>
+      <c r="D19" s="79">
+        <f>E19*(1+$T$1)</f>
+        <v>3.5750000000000002</v>
       </c>
       <c r="E19" s="79">
         <f>AVERAGE(G19:Q19)</f>
-        <v>3.75</v>
-      </c>
-      <c r="F19" s="79" t="e">
+        <v>2.3833333333333333</v>
+      </c>
+      <c r="F19" s="79">
         <f>STDEV(G19:Q19)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G19" s="79"/>
-      <c r="H19" s="79"/>
+        <v>1.3269639532908692</v>
+      </c>
+      <c r="G19" s="79">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H19" s="79">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="I19" s="79"/>
       <c r="J19" s="140"/>
       <c r="K19" s="141"/>
@@ -34602,32 +34677,34 @@
       <c r="T19" s="159"/>
     </row>
     <row r="20" spans="1:20">
-      <c r="A20" t="s">
-        <v>142</v>
+      <c r="A20" s="322" t="s">
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="D20" s="79">
         <f>E20*(1+$T$1)</f>
-        <v>2.5875000000000004</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="E20" s="79">
         <f>AVERAGE(G20:Q20)</f>
-        <v>1.7250000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="F20" s="79">
         <f>STDEV(G20:Q20)</f>
-        <v>0.31819805153394543</v>
-      </c>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="79">
-        <v>1.5</v>
-      </c>
+        <v>0.85293610546159904</v>
+      </c>
+      <c r="G20" s="79">
+        <v>0.75</v>
+      </c>
+      <c r="H20" s="79">
+        <v>2.4</v>
+      </c>
+      <c r="I20" s="79"/>
       <c r="J20" s="140"/>
       <c r="K20" s="141"/>
       <c r="O20" s="155">
@@ -34638,34 +34715,34 @@
     </row>
     <row r="21" spans="1:20">
       <c r="A21" s="322" t="s">
-        <v>55</v>
+        <v>892</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="79">
-        <f>E21*(1+$T$1)</f>
-        <v>2.3049999999999997</v>
-      </c>
-      <c r="E21" s="79">
+        <v>933</v>
+      </c>
+      <c r="D21" s="79" t="e">
+        <f>E21*(1+$O$1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E21" s="140">
         <f>AVERAGE(G21:Q21)</f>
-        <v>1.5366666666666664</v>
-      </c>
-      <c r="F21" s="79">
+        <v>1.3766666666666667</v>
+      </c>
+      <c r="F21" s="140">
         <f>STDEV(G21:Q21)</f>
-        <v>0.96256601505212824</v>
-      </c>
-      <c r="G21" s="79">
-        <v>0.75</v>
-      </c>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79">
-        <v>1.25</v>
-      </c>
-      <c r="J21" s="140"/>
+        <v>1.0759801732993659</v>
+      </c>
+      <c r="G21" s="140"/>
+      <c r="H21" s="140">
+        <v>0.89</v>
+      </c>
+      <c r="I21" s="79"/>
+      <c r="J21" s="140">
+        <v>0.63</v>
+      </c>
       <c r="K21" s="141"/>
       <c r="O21" s="155">
         <v>2.61</v>
@@ -34678,22 +34755,22 @@
         <v>142</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="79">
-        <f>E22*(1+$T$1)</f>
-        <v>2.5</v>
+        <v>904</v>
+      </c>
+      <c r="D22" s="79" t="e">
+        <f>E22*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E22" s="79">
         <f>AVERAGE(G22:Q22)</f>
-        <v>1.6666666666666667</v>
+        <v>1.6</v>
       </c>
       <c r="F22" s="79">
         <f>STDEV(G22:Q22)</f>
-        <v>0.23094010767585105</v>
+        <v>0.28284271247461756</v>
       </c>
       <c r="G22" s="79">
         <v>1.4</v>
@@ -34701,9 +34778,7 @@
       <c r="H22" s="79">
         <v>1.8</v>
       </c>
-      <c r="I22" s="79">
-        <v>1.8</v>
-      </c>
+      <c r="I22" s="79"/>
       <c r="J22" s="140"/>
       <c r="K22" s="141"/>
       <c r="S22" s="112"/>
@@ -34711,30 +34786,28 @@
     </row>
     <row r="23" spans="1:20">
       <c r="A23" s="322" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="79">
-        <f>E23*(1+$T$1)</f>
-        <v>2.125</v>
+        <v>934</v>
+      </c>
+      <c r="D23" s="79" t="e">
+        <f>E23*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E23" s="79">
         <f>AVERAGE(G23:Q23)</f>
-        <v>1.4166666666666667</v>
+        <v>1.625</v>
       </c>
       <c r="F23" s="79">
         <f>STDEV(G23:Q23)</f>
-        <v>0.38188130791298686</v>
+        <v>0.17677669529663689</v>
       </c>
       <c r="G23" s="79"/>
-      <c r="H23" s="79">
-        <v>1</v>
-      </c>
+      <c r="H23" s="79"/>
       <c r="I23" s="79"/>
       <c r="J23" s="140"/>
       <c r="K23" s="141"/>
@@ -34749,32 +34822,32 @@
     </row>
     <row r="24" spans="1:20">
       <c r="A24" s="322" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>935</v>
+        <v>28</v>
       </c>
       <c r="D24" s="79">
         <f>E24*(1+$T$1)</f>
-        <v>3.75</v>
-      </c>
-      <c r="E24" s="140">
+        <v>2.6749999999999998</v>
+      </c>
+      <c r="E24" s="79">
         <f>AVERAGE(G24:Q24)</f>
-        <v>2.5</v>
-      </c>
-      <c r="F24" s="140">
+        <v>1.7833333333333332</v>
+      </c>
+      <c r="F24" s="79">
         <f>STDEV(G24:Q24)</f>
-        <v>0.5</v>
-      </c>
-      <c r="G24" s="140"/>
-      <c r="H24" s="140">
-        <v>3</v>
+        <v>0.64485140407177088</v>
+      </c>
+      <c r="G24" s="79"/>
+      <c r="H24" s="79">
+        <v>1.6</v>
       </c>
       <c r="I24" s="79">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="J24" s="140"/>
       <c r="K24" s="141"/>
@@ -34786,28 +34859,28 @@
     </row>
     <row r="25" spans="1:20">
       <c r="A25" s="322" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>902</v>
+        <v>364</v>
       </c>
       <c r="D25" s="79" t="e">
         <f>E25*(1+$O$1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E25" s="140">
+      <c r="E25" s="79">
         <f>AVERAGE(G25:Q25)</f>
         <v>1.5</v>
       </c>
-      <c r="F25" s="140" t="e">
+      <c r="F25" s="79" t="e">
         <f>STDEV(G25:Q25)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G25" s="140"/>
-      <c r="H25" s="140"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="79"/>
       <c r="I25" s="79"/>
       <c r="J25" s="140"/>
       <c r="K25" s="141"/>
@@ -34819,34 +34892,32 @@
     </row>
     <row r="26" spans="1:20">
       <c r="A26" s="322" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>933</v>
-      </c>
-      <c r="D26" s="79" t="e">
-        <f>E26*(1+$O$1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E26" s="140">
+        <v>83</v>
+      </c>
+      <c r="D26" s="79">
+        <f>E26*(1+$T$1)</f>
+        <v>2.1750000000000003</v>
+      </c>
+      <c r="E26" s="79">
         <f>AVERAGE(G26:Q26)</f>
-        <v>0.8640000000000001</v>
-      </c>
-      <c r="F26" s="140">
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="F26" s="79">
         <f>STDEV(G26:Q26)</f>
-        <v>0.2353295561547675</v>
-      </c>
-      <c r="G26" s="140"/>
-      <c r="H26" s="140">
-        <v>0.89</v>
-      </c>
+        <v>1.0575128052810199</v>
+      </c>
+      <c r="G26" s="79">
+        <v>3</v>
+      </c>
+      <c r="H26" s="79"/>
       <c r="I26" s="79"/>
-      <c r="J26" s="140">
-        <v>0.63</v>
-      </c>
+      <c r="J26" s="140"/>
       <c r="K26" s="141"/>
       <c r="L26" s="155">
         <v>0.95</v>
@@ -34862,32 +34933,30 @@
     </row>
     <row r="27" spans="1:20">
       <c r="A27" s="322" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="322" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="322" t="s">
-        <v>62</v>
+        <v>142</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>84</v>
       </c>
       <c r="D27" s="79">
         <f>E27*(1+$T$1)</f>
-        <v>2.5099999999999998</v>
+        <v>3.8025000000000002</v>
       </c>
       <c r="E27" s="79">
         <f>AVERAGE(G27:Q27)</f>
-        <v>1.6733333333333331</v>
+        <v>2.5350000000000001</v>
       </c>
       <c r="F27" s="79">
         <f>STDEV(G27:Q27)</f>
-        <v>0.41064989143226871</v>
+        <v>0.6576093065034887</v>
       </c>
       <c r="G27" s="79">
-        <v>1.25</v>
-      </c>
-      <c r="H27" s="79">
-        <v>1.7</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H27" s="79"/>
       <c r="I27" s="79"/>
       <c r="J27" s="140"/>
       <c r="K27" s="141"/>
@@ -34899,31 +34968,33 @@
     </row>
     <row r="28" spans="1:20">
       <c r="A28" s="322" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>903</v>
-      </c>
-      <c r="D28" s="79" t="e">
-        <f>E28*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>92</v>
+      </c>
+      <c r="D28" s="79">
+        <f>E28*(1+$T$1)</f>
+        <v>1.875</v>
       </c>
       <c r="E28" s="79">
         <f>AVERAGE(G28:Q28)</f>
-        <v>1.75</v>
-      </c>
-      <c r="F28" s="79" t="e">
+        <v>1.25</v>
+      </c>
+      <c r="F28" s="79">
         <f>STDEV(G28:Q28)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="79">
-        <v>1.75</v>
-      </c>
+        <v>7.0710678118654821E-2</v>
+      </c>
+      <c r="G28" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="H28" s="79">
+        <v>1.2</v>
+      </c>
+      <c r="I28" s="79"/>
       <c r="J28" s="140"/>
       <c r="K28" s="141"/>
       <c r="S28" s="112"/>
@@ -34937,7 +35008,7 @@
         <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>904</v>
+        <v>936</v>
       </c>
       <c r="D29" s="79" t="e">
         <f>E29*(1+$O$1)</f>
@@ -34945,20 +35016,20 @@
       </c>
       <c r="E29" s="79">
         <f>AVERAGE(G29:Q29)</f>
-        <v>1.9750000000000001</v>
+        <v>1.8625</v>
       </c>
       <c r="F29" s="79">
         <f>STDEV(G29:Q29)</f>
-        <v>0.83416625041614656</v>
-      </c>
-      <c r="G29" s="79">
-        <v>1.4</v>
-      </c>
-      <c r="H29" s="79">
-        <v>1.8</v>
+        <v>0.89570735548317737</v>
+      </c>
+      <c r="G29" s="140"/>
+      <c r="H29" s="140">
+        <v>1.3</v>
       </c>
       <c r="I29" s="79"/>
-      <c r="J29" s="140"/>
+      <c r="J29" s="140">
+        <v>1.45</v>
+      </c>
       <c r="K29" s="141"/>
       <c r="L29" s="155">
         <v>3.2</v>
@@ -34974,31 +35045,27 @@
         <v>142</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>905</v>
+        <v>85</v>
       </c>
       <c r="D30" s="79">
         <f>E30*(1+$T$1)</f>
-        <v>2.3250000000000002</v>
+        <v>1.875</v>
       </c>
       <c r="E30" s="79">
         <f>AVERAGE(G30:Q30)</f>
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="F30" s="79">
         <f>STDEV(G30:Q30)</f>
-        <v>0.17320508075688779</v>
-      </c>
-      <c r="G30" s="79">
-        <v>1.4</v>
-      </c>
-      <c r="H30" s="79">
-        <v>1.8</v>
-      </c>
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
       <c r="I30" s="79">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J30" s="140"/>
       <c r="K30" s="141"/>
@@ -35010,28 +35077,30 @@
     </row>
     <row r="31" spans="1:20">
       <c r="A31" s="322" t="s">
-        <v>55</v>
+        <v>892</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>907</v>
-      </c>
-      <c r="D31" s="79" t="e">
-        <f>E31*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>917</v>
+      </c>
+      <c r="D31" s="79">
+        <f>E31*(1+$T$1)</f>
+        <v>2.7375000000000003</v>
       </c>
       <c r="E31" s="79">
         <f>AVERAGE(G31:Q31)</f>
-        <v>1.86</v>
-      </c>
-      <c r="F31" s="79" t="e">
+        <v>1.8250000000000002</v>
+      </c>
+      <c r="F31" s="79">
         <f>STDEV(G31:Q31)</f>
-        <v>#DIV/0!</v>
+        <v>4.9497474683058366E-2</v>
       </c>
       <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
+      <c r="H31" s="79">
+        <v>1.79</v>
+      </c>
       <c r="I31" s="79"/>
       <c r="J31" s="140"/>
       <c r="K31" s="141"/>
@@ -35043,29 +35112,29 @@
     </row>
     <row r="32" spans="1:20">
       <c r="A32" s="322" t="s">
-        <v>892</v>
+        <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>908</v>
-      </c>
-      <c r="D32" s="79" t="e">
-        <f>E32*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>67</v>
+      </c>
+      <c r="D32" s="79">
+        <f>E32*(1+$T$1)</f>
+        <v>3.7</v>
       </c>
       <c r="E32" s="79">
         <f>AVERAGE(G32:Q32)</f>
-        <v>2.6666666666666665</v>
+        <v>2.4666666666666668</v>
       </c>
       <c r="F32" s="79">
         <f>STDEV(G32:Q32)</f>
-        <v>1.3316656236958793</v>
+        <v>1.5143755588800729</v>
       </c>
       <c r="G32" s="79"/>
       <c r="H32" s="79">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="I32" s="79"/>
       <c r="J32" s="140"/>
@@ -35084,27 +35153,36 @@
         <v>142</v>
       </c>
       <c r="B33" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>906</v>
-      </c>
-      <c r="D33" s="79" t="e">
-        <f>E33*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>86</v>
+      </c>
+      <c r="D33" s="79">
+        <f>E33*(1+$T$1)</f>
+        <v>3.2062499999999998</v>
       </c>
       <c r="E33" s="79">
         <f>AVERAGE(G33:Q33)</f>
-        <v>1.65</v>
+        <v>2.1374999999999997</v>
       </c>
       <c r="F33" s="79">
         <f>STDEV(G33:Q33)</f>
-        <v>0.63639610306789296</v>
-      </c>
-      <c r="G33" s="79"/>
-      <c r="H33" s="79"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="140"/>
+        <v>0.58518159574614204</v>
+      </c>
+      <c r="G33" s="79">
+        <f>17.25/10</f>
+        <v>1.7250000000000001</v>
+      </c>
+      <c r="H33" s="79">
+        <v>2.7</v>
+      </c>
+      <c r="I33" s="79">
+        <v>2.5</v>
+      </c>
+      <c r="J33" s="140">
+        <v>2.6</v>
+      </c>
       <c r="K33" s="141"/>
       <c r="N33" s="155">
         <v>1.2</v>
@@ -35117,28 +35195,32 @@
     </row>
     <row r="34" spans="1:20">
       <c r="A34" s="322" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B34" t="s">
         <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>934</v>
-      </c>
-      <c r="D34" s="79" t="e">
-        <f>E34*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>118</v>
+      </c>
+      <c r="D34" s="79">
+        <f>E34*(1+$T$1)</f>
+        <v>2.4562500000000003</v>
       </c>
       <c r="E34" s="79">
         <f>AVERAGE(G34:Q34)</f>
-        <v>1.55</v>
+        <v>1.6375000000000002</v>
       </c>
       <c r="F34" s="79">
         <f>STDEV(G34:Q34)</f>
-        <v>0.77781745930520196</v>
-      </c>
-      <c r="G34" s="79"/>
-      <c r="H34" s="79"/>
+        <v>0.48196645803070737</v>
+      </c>
+      <c r="G34" s="79">
+        <v>1.55</v>
+      </c>
+      <c r="H34" s="79">
+        <v>1.9</v>
+      </c>
       <c r="I34" s="79"/>
       <c r="J34" s="140"/>
       <c r="K34" s="141"/>
@@ -35156,28 +35238,28 @@
         <v>142</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="D35" s="79">
         <f>E35*(1+$T$1)</f>
-        <v>2.4900000000000002</v>
+        <v>2.44</v>
       </c>
       <c r="E35" s="79">
         <f>AVERAGE(G35:Q35)</f>
-        <v>1.6600000000000001</v>
+        <v>1.6266666666666667</v>
       </c>
       <c r="F35" s="79">
         <f>STDEV(G35:Q35)</f>
-        <v>0.19697715603592203</v>
-      </c>
-      <c r="G35" s="79">
-        <v>1.6</v>
-      </c>
+        <v>0.21939310229205786</v>
+      </c>
+      <c r="G35" s="79"/>
       <c r="H35" s="79"/>
-      <c r="I35" s="79"/>
+      <c r="I35" s="79">
+        <v>1.5</v>
+      </c>
       <c r="J35" s="140"/>
       <c r="K35" s="141"/>
       <c r="L35" s="155">
@@ -35190,32 +35272,34 @@
       <c r="T35" s="159"/>
     </row>
     <row r="36" spans="1:20">
-      <c r="A36" t="s">
-        <v>892</v>
+      <c r="A36" s="322" t="s">
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="D36" s="79">
         <f>E36*(1+$T$1)</f>
-        <v>1.9500000000000002</v>
+        <v>1.75</v>
       </c>
       <c r="E36" s="79">
         <f>AVERAGE(G36:Q36)</f>
-        <v>1.3</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="F36" s="79">
         <f>STDEV(G36:Q36)</f>
-        <v>0.28284271247461834</v>
-      </c>
-      <c r="G36" s="140"/>
-      <c r="H36" s="140"/>
-      <c r="I36" s="79">
+        <v>0.30550504633038994</v>
+      </c>
+      <c r="G36" s="79">
         <v>1.1000000000000001</v>
       </c>
+      <c r="H36" s="79">
+        <v>0.9</v>
+      </c>
+      <c r="I36" s="79"/>
       <c r="J36" s="140"/>
       <c r="K36" s="141"/>
       <c r="O36" s="155">
@@ -35226,32 +35310,30 @@
     </row>
     <row r="37" spans="1:20">
       <c r="A37" s="322" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B37" t="s">
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>943</v>
       </c>
       <c r="D37" s="79">
         <f>E37*(1+$T$1)</f>
-        <v>2.37</v>
+        <v>2.5424999999999995</v>
       </c>
       <c r="E37" s="79">
         <f>AVERAGE(G37:Q37)</f>
-        <v>1.58</v>
+        <v>1.6949999999999998</v>
       </c>
       <c r="F37" s="79">
         <f>STDEV(G37:Q37)</f>
-        <v>0.3204684071792413</v>
+        <v>0.27577164466275589</v>
       </c>
       <c r="G37" s="79"/>
-      <c r="H37" s="79">
-        <v>1.6</v>
-      </c>
+      <c r="H37" s="79"/>
       <c r="I37" s="79">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="J37" s="140"/>
       <c r="K37" s="141"/>
@@ -35261,31 +35343,33 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38" s="322" t="s">
-        <v>21</v>
+        <v>892</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="D38" s="79">
         <f>E38*(1+$T$1)</f>
-        <v>2.3549999999999995</v>
+        <v>2.1949999999999998</v>
       </c>
       <c r="E38" s="79">
         <f>AVERAGE(G38:Q38)</f>
-        <v>1.5699999999999998</v>
+        <v>1.4633333333333332</v>
       </c>
       <c r="F38" s="79">
         <f>STDEV(G38:Q38)</f>
-        <v>0.45254833995939103</v>
-      </c>
-      <c r="G38" s="79"/>
-      <c r="H38" s="79"/>
-      <c r="I38" s="79">
-        <v>1.25</v>
-      </c>
+        <v>0.37287173844813359</v>
+      </c>
+      <c r="G38" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="H38" s="79">
+        <v>1.2</v>
+      </c>
+      <c r="I38" s="79"/>
       <c r="J38" s="140"/>
       <c r="K38" s="141"/>
       <c r="O38" s="155">
@@ -35294,62 +35378,68 @@
     </row>
     <row r="39" spans="1:20">
       <c r="A39" s="322" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s">
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>364</v>
-      </c>
-      <c r="D39" s="79" t="e">
-        <f>E39*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>914</v>
+      </c>
+      <c r="D39" s="79">
+        <f>E39*(1+$T$1)</f>
+        <v>2.9</v>
       </c>
       <c r="E39" s="79">
         <f>AVERAGE(G39:Q39)</f>
-        <v>1.5</v>
-      </c>
-      <c r="F39" s="79" t="e">
+        <v>1.9333333333333333</v>
+      </c>
+      <c r="F39" s="79">
         <f>STDEV(G39:Q39)</f>
-        <v>#DIV/0!</v>
+        <v>0.4509249752822892</v>
       </c>
       <c r="G39" s="79"/>
-      <c r="H39" s="79"/>
+      <c r="H39" s="79">
+        <v>1.9</v>
+      </c>
       <c r="I39" s="79"/>
-      <c r="J39" s="140"/>
+      <c r="J39" s="140">
+        <v>2.4</v>
+      </c>
       <c r="K39" s="141"/>
       <c r="O39" s="155">
         <v>1.5</v>
       </c>
     </row>
     <row r="40" spans="1:20">
-      <c r="A40" t="s">
-        <v>142</v>
+      <c r="A40" s="322" t="s">
+        <v>892</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D40" s="79">
         <f>E40*(1+$T$1)</f>
-        <v>6.15</v>
+        <v>4.0875000000000004</v>
       </c>
       <c r="E40" s="79">
         <f>AVERAGE(G40:Q40)</f>
-        <v>4.1000000000000005</v>
+        <v>2.7250000000000001</v>
       </c>
       <c r="F40" s="79">
         <f>STDEV(G40:Q40)</f>
-        <v>0.36055512754639901</v>
-      </c>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79">
-        <v>3.8</v>
-      </c>
-      <c r="I40" s="79"/>
+        <v>1.7802153427792569</v>
+      </c>
+      <c r="G40" s="79">
+        <v>1.4</v>
+      </c>
+      <c r="H40" s="79"/>
+      <c r="I40" s="79">
+        <v>1</v>
+      </c>
       <c r="J40" s="140"/>
       <c r="K40" s="141"/>
       <c r="L40" s="155">
@@ -35361,31 +35451,31 @@
     </row>
     <row r="41" spans="1:20">
       <c r="A41" s="322" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B41" t="s">
         <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D41" s="79">
         <f>E41*(1+$T$1)</f>
-        <v>4.51</v>
+        <v>3.71</v>
       </c>
       <c r="E41" s="79">
         <f>AVERAGE(G41:Q41)</f>
-        <v>3.0066666666666664</v>
+        <v>2.4733333333333332</v>
       </c>
       <c r="F41" s="79">
         <f>STDEV(G41:Q41)</f>
-        <v>0.59002824791134789</v>
-      </c>
-      <c r="G41" s="79">
-        <v>3</v>
-      </c>
+        <v>1.1009692699314253</v>
+      </c>
+      <c r="G41" s="79"/>
       <c r="H41" s="79"/>
-      <c r="I41" s="79"/>
+      <c r="I41" s="79">
+        <v>1.4</v>
+      </c>
       <c r="J41" s="140"/>
       <c r="K41" s="141"/>
       <c r="L41" s="155">
@@ -35397,31 +35487,31 @@
     </row>
     <row r="42" spans="1:20">
       <c r="A42" s="322" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B42" t="s">
         <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D42" s="79">
         <f>E42*(1+$T$1)</f>
-        <v>4.9499999999999993</v>
+        <v>3.8249999999999997</v>
       </c>
       <c r="E42" s="79">
         <f>AVERAGE(G42:Q42)</f>
-        <v>3.3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="F42" s="79">
         <f>STDEV(G42:Q42)</f>
-        <v>0.42426406871192857</v>
-      </c>
-      <c r="G42" s="79">
-        <v>3</v>
-      </c>
-      <c r="H42" s="79"/>
-      <c r="I42" s="79"/>
+        <v>1.4849242404917504</v>
+      </c>
+      <c r="G42" s="140"/>
+      <c r="H42" s="140"/>
+      <c r="I42" s="79">
+        <v>1.5</v>
+      </c>
       <c r="J42" s="140"/>
       <c r="K42" s="141"/>
       <c r="O42" s="155">
@@ -35436,25 +35526,23 @@
         <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>92</v>
+        <v>311</v>
       </c>
       <c r="D43" s="79">
         <f>E43*(1+$T$1)</f>
-        <v>2</v>
+        <v>2.625</v>
       </c>
       <c r="E43" s="79">
         <f>AVERAGE(G43:Q43)</f>
-        <v>1.3333333333333333</v>
+        <v>1.75</v>
       </c>
       <c r="F43" s="79">
         <f>STDEV(G43:Q43)</f>
-        <v>0.15275252316519469</v>
-      </c>
-      <c r="G43" s="79">
-        <v>1.3</v>
-      </c>
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="G43" s="79"/>
       <c r="H43" s="79">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="I43" s="79"/>
       <c r="J43" s="140"/>
@@ -35465,34 +35553,32 @@
     </row>
     <row r="44" spans="1:20">
       <c r="A44" s="322" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B44" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C44" t="s">
-        <v>92</v>
-      </c>
-      <c r="D44" s="79">
-        <f>E44*(1+$T$1)</f>
-        <v>2</v>
+        <v>919</v>
+      </c>
+      <c r="D44" s="79" t="e">
+        <f>E44*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E44" s="79">
         <f>AVERAGE(G44:Q44)</f>
-        <v>1.3333333333333333</v>
+        <v>1.25</v>
       </c>
       <c r="F44" s="79">
         <f>STDEV(G44:Q44)</f>
-        <v>0.15275252316519469</v>
-      </c>
-      <c r="G44" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="H44" s="79">
-        <v>1.2</v>
-      </c>
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="G44" s="79"/>
+      <c r="H44" s="79"/>
       <c r="I44" s="79"/>
-      <c r="J44" s="140"/>
+      <c r="J44" s="140">
+        <v>1</v>
+      </c>
       <c r="K44" s="141"/>
       <c r="N44" s="155">
         <v>1.5</v>
@@ -35500,64 +35586,64 @@
     </row>
     <row r="45" spans="1:20">
       <c r="A45" s="322" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="D45" s="79">
         <f>E45*(1+$T$1)</f>
-        <v>1.75</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="E45" s="79">
         <f>AVERAGE(G45:Q45)</f>
-        <v>1.1666666666666667</v>
-      </c>
-      <c r="F45" s="79">
+        <v>1.4</v>
+      </c>
+      <c r="F45" s="79" t="e">
         <f>STDEV(G45:Q45)</f>
-        <v>0.15275252316519497</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G45" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="H45" s="79">
-        <v>1.2</v>
-      </c>
-      <c r="I45" s="79">
-        <v>1</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="H45" s="79"/>
+      <c r="I45" s="79"/>
       <c r="J45" s="140"/>
       <c r="K45" s="141"/>
     </row>
     <row r="46" spans="1:20">
       <c r="A46" s="322" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C46" t="s">
-        <v>909</v>
-      </c>
-      <c r="D46" s="79" t="e">
-        <f>E46*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>89</v>
+      </c>
+      <c r="D46" s="79">
+        <f>E46*(1+$T$1)</f>
+        <v>1.9649999999999999</v>
       </c>
       <c r="E46" s="79">
         <f>AVERAGE(G46:Q46)</f>
-        <v>1.68</v>
-      </c>
-      <c r="F46" s="79" t="e">
+        <v>1.3099999999999998</v>
+      </c>
+      <c r="F46" s="79">
         <f>STDEV(G46:Q46)</f>
-        <v>#DIV/0!</v>
+        <v>0.34394767043839752</v>
       </c>
       <c r="G46" s="79"/>
-      <c r="H46" s="79"/>
+      <c r="H46" s="79">
+        <v>1</v>
+      </c>
       <c r="I46" s="79"/>
-      <c r="J46" s="140"/>
+      <c r="J46" s="140">
+        <v>1.25</v>
+      </c>
       <c r="K46" s="141"/>
       <c r="O46" s="155">
         <v>1.68</v>
@@ -35565,36 +35651,34 @@
     </row>
     <row r="47" spans="1:20">
       <c r="A47" s="322" t="s">
-        <v>892</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C47" t="s">
-        <v>120</v>
+        <v>922</v>
       </c>
       <c r="D47" s="79">
         <f>E47*(1+$T$1)</f>
-        <v>2.8875000000000002</v>
+        <v>2.7149999999999999</v>
       </c>
       <c r="E47" s="79">
         <f>AVERAGE(G47:Q47)</f>
-        <v>1.925</v>
+        <v>1.81</v>
       </c>
       <c r="F47" s="79">
         <f>STDEV(G47:Q47)</f>
-        <v>0.38568121551353746</v>
-      </c>
-      <c r="G47" s="79">
-        <v>1.4</v>
-      </c>
+        <v>0.49547956567349871</v>
+      </c>
+      <c r="G47" s="79"/>
       <c r="H47" s="79">
-        <v>1.95</v>
-      </c>
-      <c r="I47" s="79"/>
-      <c r="J47" s="140">
-        <v>2.25</v>
-      </c>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I47" s="79">
+        <v>2</v>
+      </c>
+      <c r="J47" s="140"/>
       <c r="K47" s="141"/>
       <c r="L47" s="155">
         <v>2.2000000000000002</v>
@@ -35608,96 +35692,98 @@
     </row>
     <row r="48" spans="1:20">
       <c r="A48" s="156" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="D48" s="79">
         <f>E48*(1+$T$1)</f>
-        <v>1.8000000000000003</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="E48" s="79">
         <f>AVERAGE(G48:Q48)</f>
-        <v>1.2000000000000002</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F48" s="79">
         <f>STDEV(G48:Q48)</f>
         <v>0.14142135623730948</v>
       </c>
       <c r="G48" s="79">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H48" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="I48" s="157"/>
+        <v>1.2</v>
+      </c>
+      <c r="H48" s="79"/>
+      <c r="I48" s="157">
+        <v>1</v>
+      </c>
       <c r="J48" s="140"/>
       <c r="K48" s="141"/>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="156" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="B49" t="s">
         <v>33</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="D49" s="79">
         <f>E49*(1+$T$1)</f>
-        <v>1.875</v>
+        <v>2.5</v>
       </c>
       <c r="E49" s="79">
         <f>AVERAGE(G49:Q49)</f>
-        <v>1.25</v>
-      </c>
-      <c r="F49" s="79" t="e">
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="F49" s="79">
         <f>STDEV(G49:Q49)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G49" s="140"/>
-      <c r="H49" s="140"/>
+        <v>0.23094010767585105</v>
+      </c>
+      <c r="G49" s="79">
+        <v>1.4</v>
+      </c>
+      <c r="H49" s="79">
+        <v>1.8</v>
+      </c>
       <c r="I49" s="157">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="J49" s="140"/>
       <c r="K49" s="141"/>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="156" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C50" t="s">
-        <v>936</v>
-      </c>
-      <c r="D50" s="79" t="e">
-        <f>E50*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>61</v>
+      </c>
+      <c r="D50" s="79">
+        <f>E50*(1+$T$1)</f>
+        <v>2.0550000000000002</v>
       </c>
       <c r="E50" s="79">
         <f>AVERAGE(G50:Q50)</f>
-        <v>1.4460000000000002</v>
+        <v>1.37</v>
       </c>
       <c r="F50" s="79">
         <f>STDEV(G50:Q50)</f>
-        <v>0.25510782034269269</v>
-      </c>
-      <c r="G50" s="140"/>
-      <c r="H50" s="140">
-        <v>1.3</v>
+        <v>0.37184226046358149</v>
+      </c>
+      <c r="G50" s="79"/>
+      <c r="H50" s="79">
+        <v>1</v>
       </c>
       <c r="I50" s="157"/>
-      <c r="J50" s="140">
-        <v>1.45</v>
-      </c>
+      <c r="J50" s="140"/>
       <c r="K50" s="141"/>
       <c r="N50" s="155">
         <v>1.7</v>
@@ -35714,18 +35800,18 @@
         <v>142</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C51" t="s">
-        <v>85</v>
-      </c>
-      <c r="D51" s="79">
-        <f>E51*(1+$T$1)</f>
-        <v>1.5</v>
+        <v>903</v>
+      </c>
+      <c r="D51" s="79" t="e">
+        <f>E51*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E51" s="79">
         <f>AVERAGE(G51:Q51)</f>
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="F51" s="79" t="e">
         <f>STDEV(G51:Q51)</f>
@@ -35734,36 +35820,42 @@
       <c r="G51" s="79"/>
       <c r="H51" s="79"/>
       <c r="I51" s="157">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="J51" s="140"/>
       <c r="K51" s="141"/>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="156" t="s">
-        <v>894</v>
+        <v>142</v>
       </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C52" t="s">
-        <v>901</v>
-      </c>
-      <c r="D52" s="79" t="e">
-        <f>E52*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>905</v>
+      </c>
+      <c r="D52" s="79">
+        <f>E52*(1+$T$1)</f>
+        <v>2.3250000000000002</v>
       </c>
       <c r="E52" s="79">
         <f>AVERAGE(G52:Q52)</f>
+        <v>1.55</v>
+      </c>
+      <c r="F52" s="79">
+        <f>STDEV(G52:Q52)</f>
+        <v>0.17320508075688779</v>
+      </c>
+      <c r="G52" s="79">
+        <v>1.4</v>
+      </c>
+      <c r="H52" s="79">
+        <v>1.8</v>
+      </c>
+      <c r="I52" s="157">
         <v>1.5</v>
       </c>
-      <c r="F52" s="79" t="e">
-        <f>STDEV(G52:Q52)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G52" s="79"/>
-      <c r="H52" s="79"/>
-      <c r="I52" s="157"/>
       <c r="J52" s="140"/>
       <c r="K52" s="141"/>
       <c r="O52" s="155">
@@ -35772,30 +35864,27 @@
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="156" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C53" t="s">
-        <v>136</v>
-      </c>
-      <c r="D53" s="79">
-        <f>E53*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>907</v>
+      </c>
+      <c r="D53" s="79" t="e">
+        <f>E53*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E53" s="79">
         <f>AVERAGE(G53:Q53)</f>
-        <v>1.5</v>
+        <v>1.5333333333333332</v>
       </c>
       <c r="F53" s="79">
         <f>STDEV(G53:Q53)</f>
-        <v>0.21602468994692911</v>
-      </c>
-      <c r="G53" s="79">
-        <f>14/10</f>
-        <v>1.4</v>
-      </c>
+        <v>0.25166114784236032</v>
+      </c>
+      <c r="G53" s="79"/>
       <c r="H53" s="79"/>
       <c r="I53" s="157"/>
       <c r="J53" s="140"/>
@@ -35812,31 +35901,31 @@
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="156" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B54" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C54" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D54" s="79">
         <f>E54*(1+$T$1)</f>
-        <v>2.2874999999999996</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="E54" s="79">
         <f>AVERAGE(G54:Q54)</f>
-        <v>1.5249999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="F54" s="79">
         <f>STDEV(G54:Q54)</f>
-        <v>0.60104076400856621</v>
-      </c>
-      <c r="G54" s="79">
-        <v>1.1000000000000001</v>
-      </c>
+        <v>0.49497474683058246</v>
+      </c>
+      <c r="G54" s="79"/>
       <c r="H54" s="79"/>
-      <c r="I54" s="157"/>
+      <c r="I54" s="157">
+        <v>1.25</v>
+      </c>
       <c r="J54" s="140"/>
       <c r="K54" s="141"/>
       <c r="O54" s="155">
@@ -35845,61 +35934,63 @@
     </row>
     <row r="55" spans="1:16">
       <c r="A55" s="156" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B55" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C55" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D55" s="79">
         <f>E55*(1+$T$1)</f>
-        <v>1.9500000000000002</v>
+        <v>1.875</v>
       </c>
       <c r="E55" s="79">
         <f>AVERAGE(G55:Q55)</f>
-        <v>1.3</v>
-      </c>
-      <c r="F55" s="79" t="e">
+        <v>1.25</v>
+      </c>
+      <c r="F55" s="79">
         <f>STDEV(G55:Q55)</f>
-        <v>#DIV/0!</v>
+        <v>7.0710678118654821E-2</v>
       </c>
       <c r="G55" s="79">
         <v>1.3</v>
       </c>
-      <c r="H55" s="79"/>
+      <c r="H55" s="79">
+        <v>1.2</v>
+      </c>
       <c r="I55" s="157"/>
       <c r="J55" s="140"/>
       <c r="K55" s="141"/>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="156" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B56" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C56" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D56" s="79">
         <f>E56*(1+$T$1)</f>
-        <v>2.0249999999999999</v>
+        <v>1.9000000000000004</v>
       </c>
       <c r="E56" s="79">
         <f>AVERAGE(G56:Q56)</f>
-        <v>1.3499999999999999</v>
+        <v>1.2666666666666668</v>
       </c>
       <c r="F56" s="79">
         <f>STDEV(G56:Q56)</f>
-        <v>0.68738635424337613</v>
-      </c>
-      <c r="G56" s="79">
-        <v>1.5</v>
-      </c>
-      <c r="H56" s="79"/>
-      <c r="I56" s="157"/>
+        <v>0.67515430335096993</v>
+      </c>
+      <c r="G56" s="140"/>
+      <c r="H56" s="140"/>
+      <c r="I56" s="157">
+        <v>1.25</v>
+      </c>
       <c r="J56" s="140"/>
       <c r="K56" s="141"/>
       <c r="O56" s="155">
@@ -35950,26 +36041,24 @@
         <v>142</v>
       </c>
       <c r="B58" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C58" t="s">
-        <v>127</v>
-      </c>
-      <c r="D58" s="79">
-        <f>E58*(1+$T$1)</f>
-        <v>2.0250000000000004</v>
+        <v>910</v>
+      </c>
+      <c r="D58" s="79" t="e">
+        <f>E58*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E58" s="79">
         <f>AVERAGE(G58:Q58)</f>
-        <v>1.35</v>
-      </c>
-      <c r="F58" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="F58" s="79" t="e">
         <f>STDEV(G58:Q58)</f>
-        <v>0.21213203435596303</v>
-      </c>
-      <c r="G58" s="79">
-        <v>1.2</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G58" s="79"/>
       <c r="H58" s="79"/>
       <c r="I58" s="157"/>
       <c r="J58" s="140"/>
@@ -35980,29 +36069,31 @@
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="156" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B59" t="s">
         <v>33</v>
       </c>
       <c r="C59" t="s">
-        <v>910</v>
-      </c>
-      <c r="D59" s="79" t="e">
-        <f>E59*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>66</v>
+      </c>
+      <c r="D59" s="79">
+        <f>E59*(1+$T$1)</f>
+        <v>2.5424999999999995</v>
       </c>
       <c r="E59" s="79">
         <f>AVERAGE(G59:Q59)</f>
-        <v>1.89</v>
-      </c>
-      <c r="F59" s="79" t="e">
+        <v>1.6949999999999998</v>
+      </c>
+      <c r="F59" s="79">
         <f>STDEV(G59:Q59)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G59" s="79"/>
-      <c r="H59" s="79"/>
-      <c r="I59" s="157"/>
+        <v>0.27577164466275589</v>
+      </c>
+      <c r="G59" s="140"/>
+      <c r="H59" s="140"/>
+      <c r="I59" s="157">
+        <v>1.5</v>
+      </c>
       <c r="J59" s="140"/>
       <c r="K59" s="141"/>
       <c r="O59" s="155">
@@ -36011,30 +36102,30 @@
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="156" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="B60" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C60" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="D60" s="79">
         <f>E60*(1+$T$1)</f>
-        <v>5.3625000000000007</v>
+        <v>4.3875000000000002</v>
       </c>
       <c r="E60" s="79">
         <f>AVERAGE(G60:Q60)</f>
-        <v>3.5750000000000002</v>
+        <v>2.9250000000000003</v>
       </c>
       <c r="F60" s="79">
         <f>STDEV(G60:Q60)</f>
-        <v>1.5202795795510775</v>
-      </c>
-      <c r="G60" s="140"/>
-      <c r="H60" s="140"/>
+        <v>2.4395183950935895</v>
+      </c>
+      <c r="G60" s="79"/>
+      <c r="H60" s="79"/>
       <c r="I60" s="157">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J60" s="140"/>
       <c r="K60" s="141"/>
@@ -36044,31 +36135,33 @@
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="156" t="s">
-        <v>892</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C61" t="s">
-        <v>916</v>
+        <v>35</v>
       </c>
       <c r="D61" s="79">
         <f>E61*(1+$T$1)</f>
-        <v>6.0950000000000006</v>
+        <v>6</v>
       </c>
       <c r="E61" s="79">
         <f>AVERAGE(G61:Q61)</f>
-        <v>4.0633333333333335</v>
+        <v>4</v>
       </c>
       <c r="F61" s="79">
         <f>STDEV(G61:Q61)</f>
-        <v>2.0895055236426936</v>
+        <v>1.6350331291240972</v>
       </c>
       <c r="G61" s="79"/>
       <c r="H61" s="79">
-        <v>1.79</v>
-      </c>
-      <c r="I61" s="157"/>
+        <v>3.6</v>
+      </c>
+      <c r="I61" s="157">
+        <v>2</v>
+      </c>
       <c r="J61" s="140"/>
       <c r="K61" s="141"/>
       <c r="O61" s="155">
@@ -36080,32 +36173,34 @@
     </row>
     <row r="62" spans="1:16">
       <c r="A62" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C62" t="s">
-        <v>917</v>
-      </c>
-      <c r="D62" s="79">
-        <f>E62*(1+$T$1)</f>
-        <v>2.6850000000000001</v>
+        <v>930</v>
+      </c>
+      <c r="D62" s="79" t="e">
+        <f>E62*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E62" s="79">
         <f>AVERAGE(G62:Q62)</f>
-        <v>1.79</v>
-      </c>
-      <c r="F62" s="79" t="e">
+        <v>1.45</v>
+      </c>
+      <c r="F62" s="79">
         <f>STDEV(G62:Q62)</f>
-        <v>#DIV/0!</v>
+        <v>7.0710678118654821E-2</v>
       </c>
       <c r="G62" s="79"/>
-      <c r="H62" s="79">
-        <v>1.79</v>
-      </c>
-      <c r="I62" s="157"/>
-      <c r="J62" s="140"/>
+      <c r="H62" s="79"/>
+      <c r="I62" s="157">
+        <v>1.5</v>
+      </c>
+      <c r="J62" s="140">
+        <v>1.4</v>
+      </c>
       <c r="K62" s="141"/>
     </row>
     <row r="63" spans="1:16">
@@ -36113,60 +36208,64 @@
         <v>142</v>
       </c>
       <c r="B63" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C63" t="s">
-        <v>941</v>
+        <v>100</v>
       </c>
       <c r="D63" s="79">
         <f>E63*(1+$T$1)</f>
-        <v>2.0999999999999996</v>
+        <v>4.125</v>
       </c>
       <c r="E63" s="79">
         <f>AVERAGE(G63:Q63)</f>
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
       <c r="F63" s="79">
         <f>STDEV(G63:Q63)</f>
-        <v>0.14142135623730948</v>
+        <v>0.5</v>
       </c>
       <c r="G63" s="79">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="H63" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="I63" s="157"/>
-      <c r="J63" s="140"/>
+        <v>3.5</v>
+      </c>
+      <c r="I63" s="157">
+        <v>2.5</v>
+      </c>
+      <c r="J63" s="140">
+        <v>2.5</v>
+      </c>
       <c r="K63" s="141"/>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="156" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B64" t="s">
-        <v>41</v>
-      </c>
-      <c r="C64" t="s">
-        <v>65</v>
+        <v>33</v>
+      </c>
+      <c r="C64" s="66" t="s">
+        <v>101</v>
       </c>
       <c r="D64" s="79">
         <f>E64*(1+$T$1)</f>
-        <v>2.0474999999999999</v>
+        <v>2.0250000000000004</v>
       </c>
       <c r="E64" s="79">
         <f>AVERAGE(G64:Q64)</f>
-        <v>1.365</v>
+        <v>1.35</v>
       </c>
       <c r="F64" s="79">
         <f>STDEV(G64:Q64)</f>
-        <v>0.3323401871576776</v>
-      </c>
-      <c r="G64" s="79">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="H64" s="79"/>
-      <c r="I64" s="157"/>
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="G64" s="140"/>
+      <c r="H64" s="140"/>
+      <c r="I64" s="157">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="J64" s="140"/>
       <c r="K64" s="141"/>
       <c r="O64" s="155">
@@ -36181,57 +36280,57 @@
         <v>33</v>
       </c>
       <c r="C65" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D65" s="79">
         <f>E65*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="E65" s="79">
         <f>AVERAGE(G65:Q65)</f>
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="F65" s="79" t="e">
         <f>STDEV(G65:Q65)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G65" s="140"/>
-      <c r="H65" s="140"/>
-      <c r="I65" s="157">
-        <v>1.5</v>
-      </c>
+      <c r="G65" s="79"/>
+      <c r="H65" s="79">
+        <v>4</v>
+      </c>
+      <c r="I65" s="157"/>
       <c r="J65" s="140"/>
       <c r="K65" s="141"/>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="156" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B66" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C66" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="D66" s="79">
         <f>E66*(1+$T$1)</f>
-        <v>1.7999999999999998</v>
+        <v>2.15</v>
       </c>
       <c r="E66" s="79">
         <f>AVERAGE(G66:Q66)</f>
-        <v>1.2</v>
+        <v>1.4333333333333333</v>
       </c>
       <c r="F66" s="79">
         <f>STDEV(G66:Q66)</f>
-        <v>0.36055512754639879</v>
+        <v>0.11547005383792512</v>
       </c>
       <c r="G66" s="79">
         <v>1.3</v>
       </c>
-      <c r="H66" s="79">
-        <v>0.8</v>
-      </c>
-      <c r="I66" s="157"/>
+      <c r="H66" s="79"/>
+      <c r="I66" s="157">
+        <v>1.5</v>
+      </c>
       <c r="J66" s="140"/>
       <c r="K66" s="141"/>
       <c r="L66" s="155">
@@ -36240,63 +36339,59 @@
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="156" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="B67" t="s">
         <v>33</v>
       </c>
       <c r="C67" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="D67" s="79">
         <f>E67*(1+$T$1)</f>
-        <v>1.7999999999999998</v>
+        <v>1.875</v>
       </c>
       <c r="E67" s="79">
         <f>AVERAGE(G67:Q67)</f>
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="F67" s="79" t="e">
         <f>STDEV(G67:Q67)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G67" s="79"/>
-      <c r="H67" s="79"/>
+      <c r="G67" s="140"/>
+      <c r="H67" s="140"/>
       <c r="I67" s="157">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="J67" s="140"/>
       <c r="K67" s="141"/>
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="156" t="s">
-        <v>21</v>
+        <v>892</v>
       </c>
       <c r="B68" t="s">
         <v>33</v>
       </c>
       <c r="C68" t="s">
-        <v>35</v>
-      </c>
-      <c r="D68" s="79">
-        <f>E68*(1+$T$1)</f>
-        <v>4.0537499999999991</v>
+        <v>913</v>
+      </c>
+      <c r="D68" s="79" t="e">
+        <f>E68*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E68" s="79">
         <f>AVERAGE(G68:Q68)</f>
-        <v>2.7024999999999997</v>
+        <v>2.605</v>
       </c>
       <c r="F68" s="79">
         <f>STDEV(G68:Q68)</f>
-        <v>0.8266549058303202</v>
-      </c>
-      <c r="G68" s="79"/>
-      <c r="H68" s="79">
-        <v>3.6</v>
-      </c>
-      <c r="I68" s="157">
-        <v>2</v>
-      </c>
+        <v>0.85559920523572308</v>
+      </c>
+      <c r="G68" s="140"/>
+      <c r="H68" s="140"/>
+      <c r="I68" s="157"/>
       <c r="J68" s="140"/>
       <c r="K68" s="141"/>
       <c r="L68" s="155">
@@ -36308,61 +36403,63 @@
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="156" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B69" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C69" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="D69" s="79">
         <f>E69*(1+$T$1)</f>
-        <v>1.9500000000000002</v>
+        <v>1.875</v>
       </c>
       <c r="E69" s="79">
         <f>AVERAGE(G69:Q69)</f>
-        <v>1.3</v>
-      </c>
-      <c r="F69" s="79" t="e">
+        <v>1.25</v>
+      </c>
+      <c r="F69" s="79">
         <f>STDEV(G69:Q69)</f>
-        <v>#DIV/0!</v>
+        <v>7.0710678118654821E-2</v>
       </c>
       <c r="G69" s="79">
         <v>1.3</v>
       </c>
-      <c r="H69" s="79"/>
+      <c r="H69" s="79">
+        <v>1.2</v>
+      </c>
       <c r="I69" s="157"/>
       <c r="J69" s="140"/>
       <c r="K69" s="141"/>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="156" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C70" t="s">
-        <v>912</v>
-      </c>
-      <c r="D70" s="79" t="e">
-        <f>E70*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>39</v>
+      </c>
+      <c r="D70" s="79">
+        <f>E70*(1+$T$1)</f>
+        <v>3.4312500000000004</v>
       </c>
       <c r="E70" s="79">
         <f>AVERAGE(G70:Q70)</f>
-        <v>2.7850000000000001</v>
+        <v>2.2875000000000001</v>
       </c>
       <c r="F70" s="79">
         <f>STDEV(G70:Q70)</f>
-        <v>2.0718510242453894</v>
+        <v>2.0850159871489398</v>
       </c>
       <c r="G70" s="79"/>
-      <c r="H70" s="79">
-        <v>3.49</v>
-      </c>
-      <c r="I70" s="157"/>
+      <c r="H70" s="79"/>
+      <c r="I70" s="157">
+        <v>1.5</v>
+      </c>
       <c r="J70" s="140"/>
       <c r="K70" s="141"/>
       <c r="L70" s="155">
@@ -36380,10 +36477,10 @@
         <v>142</v>
       </c>
       <c r="B71" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C71" t="s">
-        <v>911</v>
+        <v>651</v>
       </c>
       <c r="D71" s="79" t="e">
         <f>E71*(1+$O$1)</f>
@@ -36397,8 +36494,8 @@
         <f>STDEV(G71:Q71)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G71" s="79"/>
-      <c r="H71" s="79"/>
+      <c r="G71" s="140"/>
+      <c r="H71" s="140"/>
       <c r="I71" s="157"/>
       <c r="J71" s="140"/>
       <c r="K71" s="141"/>
@@ -36408,17 +36505,17 @@
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="156" t="s">
-        <v>142</v>
+        <v>893</v>
       </c>
       <c r="B72" t="s">
-        <v>51</v>
-      </c>
-      <c r="C72" t="s">
-        <v>924</v>
-      </c>
-      <c r="D72" s="79" t="e">
-        <f>E72*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>33</v>
+      </c>
+      <c r="C72" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="D72" s="79">
+        <f>E72*(1+$T$1)</f>
+        <v>2.6774999999999998</v>
       </c>
       <c r="E72" s="79">
         <f>AVERAGE(G72:Q72)</f>
@@ -36428,8 +36525,8 @@
         <f>STDEV(G72:Q72)</f>
         <v>0.40305086527633177</v>
       </c>
-      <c r="G72" s="79"/>
-      <c r="H72" s="79"/>
+      <c r="G72" s="140"/>
+      <c r="H72" s="140"/>
       <c r="I72" s="157">
         <v>1.5</v>
       </c>
@@ -36441,13 +36538,13 @@
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="156" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="B73" t="s">
         <v>33</v>
       </c>
       <c r="C73" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="D73" s="79" t="e">
         <f>E73*(1+$O$1)</f>
@@ -36455,20 +36552,18 @@
       </c>
       <c r="E73" s="79">
         <f>AVERAGE(G73:Q73)</f>
-        <v>1.2874999999999999</v>
+        <v>1.4166666666666667</v>
       </c>
       <c r="F73" s="79">
         <f>STDEV(G73:Q73)</f>
-        <v>0.20155644370746537</v>
+        <v>0.51071844820148538</v>
       </c>
       <c r="G73" s="79"/>
       <c r="H73" s="79"/>
       <c r="I73" s="157">
-        <v>1.5</v>
-      </c>
-      <c r="J73" s="140">
-        <v>1.4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J73" s="140"/>
       <c r="K73" s="141"/>
       <c r="N73" s="155">
         <v>1.2</v>
@@ -36479,13 +36574,13 @@
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="156" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B74" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C74" t="s">
-        <v>930</v>
+        <v>920</v>
       </c>
       <c r="D74" s="79" t="e">
         <f>E74*(1+$O$1)</f>
@@ -36493,20 +36588,16 @@
       </c>
       <c r="E74" s="79">
         <f>AVERAGE(G74:Q74)</f>
-        <v>1.2874999999999999</v>
+        <v>1.125</v>
       </c>
       <c r="F74" s="79">
         <f>STDEV(G74:Q74)</f>
-        <v>0.20155644370746537</v>
+        <v>0.10606601717798207</v>
       </c>
       <c r="G74" s="79"/>
       <c r="H74" s="79"/>
-      <c r="I74" s="157">
-        <v>1.5</v>
-      </c>
-      <c r="J74" s="140">
-        <v>1.4</v>
-      </c>
+      <c r="I74" s="157"/>
+      <c r="J74" s="140"/>
       <c r="K74" s="141"/>
       <c r="N74" s="155">
         <v>1.2</v>
@@ -36517,68 +36608,68 @@
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="156" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B75" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C75" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="D75" s="79">
         <f>E75*(1+$T$1)</f>
-        <v>1.875</v>
+        <v>1.7249999999999999</v>
       </c>
       <c r="E75" s="79">
         <f>AVERAGE(G75:Q75)</f>
-        <v>1.25</v>
-      </c>
-      <c r="F75" s="79" t="e">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="F75" s="79">
         <f>STDEV(G75:Q75)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G75" s="140"/>
-      <c r="H75" s="140"/>
-      <c r="I75" s="157">
-        <v>1.25</v>
-      </c>
+        <v>0.21213203435596617</v>
+      </c>
+      <c r="G75" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="H75" s="79">
+        <v>1</v>
+      </c>
+      <c r="I75" s="157"/>
       <c r="J75" s="140"/>
       <c r="K75" s="141"/>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="156" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="B76" t="s">
         <v>33</v>
       </c>
       <c r="C76" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D76" s="79">
         <f>E76*(1+$T$1)</f>
-        <v>4.0649999999999995</v>
+        <v>3.2421428571428574</v>
       </c>
       <c r="E76" s="79">
         <f>AVERAGE(G76:Q76)</f>
-        <v>2.71</v>
+        <v>2.1614285714285715</v>
       </c>
       <c r="F76" s="79">
         <f>STDEV(G76:Q76)</f>
-        <v>0.74542413621853099</v>
+        <v>0.97060854744894542</v>
       </c>
       <c r="G76" s="79">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="H76" s="79">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="I76" s="157">
-        <v>2.5</v>
-      </c>
-      <c r="J76" s="140">
-        <v>2.5</v>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="J76" s="140"/>
       <c r="K76" s="141"/>
       <c r="L76" s="155">
         <v>3</v>
@@ -36595,21 +36686,21 @@
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="156" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="B77" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C77" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="D77" s="79">
         <f>E77*(1+$T$1)</f>
-        <v>1.875</v>
+        <v>2.25</v>
       </c>
       <c r="E77" s="79">
         <f>AVERAGE(G77:Q77)</f>
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="F77" s="79" t="e">
         <f>STDEV(G77:Q77)</f>
@@ -36618,38 +36709,38 @@
       <c r="G77" s="79"/>
       <c r="H77" s="79"/>
       <c r="I77" s="157">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="J77" s="140"/>
       <c r="K77" s="141"/>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="156" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B78" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="66" t="s">
-        <v>101</v>
+      <c r="C78" t="s">
+        <v>96</v>
       </c>
       <c r="D78" s="79">
         <f>E78*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="E78" s="79">
         <f>AVERAGE(G78:Q78)</f>
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="F78" s="79" t="e">
         <f>STDEV(G78:Q78)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G78" s="140"/>
-      <c r="H78" s="140"/>
-      <c r="I78" s="157">
-        <v>1.1000000000000001</v>
-      </c>
+      <c r="G78" s="79"/>
+      <c r="H78" s="79">
+        <v>1</v>
+      </c>
+      <c r="I78" s="157"/>
       <c r="J78" s="140"/>
       <c r="K78" s="141"/>
     </row>
@@ -36658,27 +36749,27 @@
         <v>142</v>
       </c>
       <c r="B79" t="s">
-        <v>41</v>
-      </c>
-      <c r="C79" s="66" t="s">
-        <v>101</v>
+        <v>33</v>
+      </c>
+      <c r="C79" t="s">
+        <v>898</v>
       </c>
       <c r="D79" s="79">
         <f>E79*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>2.625</v>
       </c>
       <c r="E79" s="79">
         <f>AVERAGE(G79:Q79)</f>
-        <v>1.1000000000000001</v>
+        <v>1.75</v>
       </c>
       <c r="F79" s="79" t="e">
         <f>STDEV(G79:Q79)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G79" s="140"/>
-      <c r="H79" s="140"/>
+      <c r="G79" s="79"/>
+      <c r="H79" s="79"/>
       <c r="I79" s="157">
-        <v>1.1000000000000001</v>
+        <v>1.75</v>
       </c>
       <c r="J79" s="140"/>
       <c r="K79" s="141"/>
@@ -36688,28 +36779,28 @@
         <v>142</v>
       </c>
       <c r="B80" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C80" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="D80" s="79">
         <f>E80*(1+$T$1)</f>
-        <v>1.875</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="E80" s="79">
         <f>AVERAGE(G80:Q80)</f>
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="F80" s="79">
         <f>STDEV(G80:Q80)</f>
-        <v>0.35355339059327379</v>
-      </c>
-      <c r="G80" s="79"/>
+        <v>0.14142135623730948</v>
+      </c>
+      <c r="G80" s="79">
+        <v>1.3</v>
+      </c>
       <c r="H80" s="79"/>
-      <c r="I80" s="157">
-        <v>1</v>
-      </c>
+      <c r="I80" s="157"/>
       <c r="J80" s="140"/>
       <c r="K80" s="141"/>
       <c r="O80" s="155">
@@ -36718,31 +36809,31 @@
     </row>
     <row r="81" spans="1:16">
       <c r="A81" s="156" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B81" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C81" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="D81" s="79">
         <f>E81*(1+$T$1)</f>
-        <v>2.69</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="E81" s="79">
         <f>AVERAGE(G81:Q81)</f>
-        <v>1.7933333333333332</v>
+        <v>1.6600000000000001</v>
       </c>
       <c r="F81" s="79">
         <f>STDEV(G81:Q81)</f>
-        <v>0.35795716689756812</v>
+        <v>0.58206528843420913</v>
       </c>
       <c r="G81" s="79"/>
-      <c r="H81" s="79">
-        <v>1.4</v>
-      </c>
-      <c r="I81" s="157"/>
+      <c r="H81" s="79"/>
+      <c r="I81" s="157">
+        <v>1</v>
+      </c>
       <c r="J81" s="140"/>
       <c r="K81" s="141"/>
       <c r="O81" s="155">
@@ -36754,29 +36845,31 @@
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="156" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B82" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C82" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="D82" s="79">
         <f>E82*(1+$T$1)</f>
-        <v>5.3849999999999998</v>
+        <v>2.74</v>
       </c>
       <c r="E82" s="79">
         <f>AVERAGE(G82:Q82)</f>
-        <v>3.59</v>
+        <v>1.8266666666666669</v>
       </c>
       <c r="F82" s="79">
         <f>STDEV(G82:Q82)</f>
-        <v>0.57982756057297036</v>
-      </c>
-      <c r="G82" s="79"/>
+        <v>1.1730870953741388</v>
+      </c>
+      <c r="G82" s="79">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="H82" s="79">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="I82" s="157"/>
       <c r="J82" s="140"/>
@@ -36787,31 +36880,33 @@
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="156" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B83" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C83" t="s">
-        <v>68</v>
+        <v>935</v>
       </c>
       <c r="D83" s="79">
         <f>E83*(1+$T$1)</f>
-        <v>5.3849999999999998</v>
-      </c>
-      <c r="E83" s="79">
+        <v>4.09</v>
+      </c>
+      <c r="E83" s="140">
         <f>AVERAGE(G83:Q83)</f>
-        <v>3.59</v>
-      </c>
-      <c r="F83" s="79">
+        <v>2.7266666666666666</v>
+      </c>
+      <c r="F83" s="140">
         <f>STDEV(G83:Q83)</f>
-        <v>0.57982756057297036</v>
-      </c>
-      <c r="G83" s="79"/>
-      <c r="H83" s="79">
-        <v>4</v>
-      </c>
-      <c r="I83" s="157"/>
+        <v>0.63571482075954144</v>
+      </c>
+      <c r="G83" s="140"/>
+      <c r="H83" s="140">
+        <v>3</v>
+      </c>
+      <c r="I83" s="157">
+        <v>2</v>
+      </c>
       <c r="J83" s="140"/>
       <c r="K83" s="141"/>
       <c r="O83" s="155">
@@ -36820,39 +36915,30 @@
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="156" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="B84" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C84" t="s">
-        <v>86</v>
-      </c>
-      <c r="D84" s="79">
-        <f>E84*(1+$T$1)</f>
-        <v>3.7232142857142856</v>
-      </c>
-      <c r="E84" s="79">
+        <v>902</v>
+      </c>
+      <c r="D84" s="79" t="e">
+        <f>E84*(1+$O$1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E84" s="140">
         <f>AVERAGE(G84:Q84)</f>
-        <v>2.4821428571428572</v>
-      </c>
-      <c r="F84" s="79">
+        <v>2.6166666666666667</v>
+      </c>
+      <c r="F84" s="140">
         <f>STDEV(G84:Q84)</f>
-        <v>0.50347010125442637</v>
-      </c>
-      <c r="G84" s="79">
-        <f>17.25/10</f>
-        <v>1.7250000000000001</v>
-      </c>
-      <c r="H84" s="79">
-        <v>2.7</v>
-      </c>
-      <c r="I84" s="157">
-        <v>2.5</v>
-      </c>
-      <c r="J84" s="140">
-        <v>2.6</v>
-      </c>
+        <v>0.64485140407177022</v>
+      </c>
+      <c r="G84" s="140"/>
+      <c r="H84" s="140"/>
+      <c r="I84" s="157"/>
+      <c r="J84" s="140"/>
       <c r="K84" s="141"/>
       <c r="L84" s="155">
         <v>2.8</v>
@@ -36866,32 +36952,30 @@
     </row>
     <row r="85" spans="1:16">
       <c r="A85" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B85" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C85" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D85" s="79">
         <f>E85*(1+$T$1)</f>
-        <v>2.85</v>
+        <v>2.8875000000000002</v>
       </c>
       <c r="E85" s="79">
         <f>AVERAGE(G85:Q85)</f>
-        <v>1.9000000000000001</v>
+        <v>1.925</v>
       </c>
       <c r="F85" s="79">
         <f>STDEV(G85:Q85)</f>
-        <v>0.34999999999999942</v>
+        <v>0.45961940777125559</v>
       </c>
       <c r="G85" s="79">
-        <v>1.55</v>
-      </c>
-      <c r="H85" s="79">
-        <v>1.9</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="H85" s="79"/>
       <c r="I85" s="157"/>
       <c r="J85" s="140"/>
       <c r="K85" s="141"/>
@@ -36901,30 +36985,34 @@
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="156" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B86" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C86" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="D86" s="79">
         <f>E86*(1+$T$1)</f>
-        <v>2.4375</v>
+        <v>1.96875</v>
       </c>
       <c r="E86" s="79">
         <f>AVERAGE(G86:Q86)</f>
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="F86" s="79">
         <f>STDEV(G86:Q86)</f>
-        <v>0.17677669529663689</v>
-      </c>
-      <c r="G86" s="79"/>
-      <c r="H86" s="79"/>
+        <v>0.31721443851123793</v>
+      </c>
+      <c r="G86" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="H86" s="79">
+        <v>1.2</v>
+      </c>
       <c r="I86" s="157">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J86" s="140"/>
       <c r="K86" s="141"/>
@@ -36934,29 +37022,27 @@
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="156" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B87" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C87" t="s">
-        <v>115</v>
-      </c>
-      <c r="D87" s="79">
-        <f>E87*(1+$T$1)</f>
-        <v>2.0625</v>
+        <v>909</v>
+      </c>
+      <c r="D87" s="79" t="e">
+        <f>E87*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E87" s="79">
         <f>AVERAGE(G87:Q87)</f>
-        <v>1.375</v>
-      </c>
-      <c r="F87" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="F87" s="79" t="e">
         <f>STDEV(G87:Q87)</f>
-        <v>0.17677669529663689</v>
-      </c>
-      <c r="G87" s="79">
-        <v>1.25</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G87" s="79"/>
       <c r="H87" s="79"/>
       <c r="I87" s="157"/>
       <c r="J87" s="140"/>
@@ -36970,90 +37056,90 @@
         <v>142</v>
       </c>
       <c r="B88" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C88" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="D88" s="79">
         <f>E88*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>1.9500000000000002</v>
       </c>
       <c r="E88" s="79">
         <f>AVERAGE(G88:Q88)</f>
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="F88" s="79" t="e">
         <f>STDEV(G88:Q88)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G88" s="140"/>
-      <c r="H88" s="140"/>
-      <c r="I88" s="157">
-        <v>1.1000000000000001</v>
-      </c>
+      <c r="G88" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="H88" s="79"/>
+      <c r="I88" s="157"/>
       <c r="J88" s="140"/>
       <c r="K88" s="141"/>
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="156" t="s">
-        <v>894</v>
+        <v>55</v>
       </c>
       <c r="B89" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C89" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="D89" s="79">
         <f>E89*(1+$T$1)</f>
-        <v>1.5</v>
+        <v>1.6949999999999998</v>
       </c>
       <c r="E89" s="79">
         <f>AVERAGE(G89:Q89)</f>
-        <v>1</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F89" s="79" t="e">
         <f>STDEV(G89:Q89)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G89" s="140"/>
-      <c r="H89" s="140"/>
-      <c r="I89" s="157">
-        <v>1</v>
-      </c>
+      <c r="G89" s="79">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="H89" s="79"/>
+      <c r="I89" s="157"/>
       <c r="J89" s="140"/>
       <c r="K89" s="141"/>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="156" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B90" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C90" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="D90" s="79">
         <f>E90*(1+$T$1)</f>
-        <v>3.2749999999999995</v>
+        <v>2.9249999999999998</v>
       </c>
       <c r="E90" s="79">
         <f>AVERAGE(G90:Q90)</f>
-        <v>2.1833333333333331</v>
+        <v>1.95</v>
       </c>
       <c r="F90" s="79">
         <f>STDEV(G90:Q90)</f>
-        <v>1.3604533558095018</v>
+        <v>1.5787653403846944</v>
       </c>
       <c r="G90" s="79">
         <v>1.3</v>
       </c>
-      <c r="H90" s="79"/>
-      <c r="I90" s="157">
-        <v>1.5</v>
-      </c>
+      <c r="H90" s="79">
+        <v>0.8</v>
+      </c>
+      <c r="I90" s="157"/>
       <c r="J90" s="140"/>
       <c r="K90" s="141"/>
       <c r="O90" s="155">
@@ -37062,21 +37148,21 @@
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="156" t="s">
-        <v>892</v>
+        <v>30</v>
       </c>
       <c r="B91" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C91" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="D91" s="79">
         <f>E91*(1+$T$1)</f>
-        <v>3.75</v>
+        <v>1.875</v>
       </c>
       <c r="E91" s="79">
         <f>AVERAGE(G91:Q91)</f>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="F91" s="79" t="e">
         <f>STDEV(G91:Q91)</f>
@@ -37085,36 +37171,38 @@
       <c r="G91" s="79"/>
       <c r="H91" s="79"/>
       <c r="I91" s="157">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="J91" s="140"/>
       <c r="K91" s="141"/>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="156" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="B92" t="s">
-        <v>51</v>
-      </c>
-      <c r="C92" t="s">
-        <v>925</v>
-      </c>
-      <c r="D92" s="79" t="e">
-        <f>E92*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>41</v>
+      </c>
+      <c r="C92" s="66" t="s">
+        <v>101</v>
+      </c>
+      <c r="D92" s="79">
+        <f>E92*(1+$T$1)</f>
+        <v>2.2949999999999999</v>
       </c>
       <c r="E92" s="79">
         <f>AVERAGE(G92:Q92)</f>
-        <v>1.96</v>
-      </c>
-      <c r="F92" s="79" t="e">
+        <v>1.53</v>
+      </c>
+      <c r="F92" s="79">
         <f>STDEV(G92:Q92)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G92" s="79"/>
-      <c r="H92" s="79"/>
-      <c r="I92" s="157"/>
+        <v>0.6081118318204306</v>
+      </c>
+      <c r="G92" s="140"/>
+      <c r="H92" s="140"/>
+      <c r="I92" s="157">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="J92" s="140"/>
       <c r="K92" s="141"/>
       <c r="O92" s="155">
@@ -37123,31 +37211,31 @@
     </row>
     <row r="93" spans="1:16">
       <c r="A93" s="156" t="s">
-        <v>894</v>
+        <v>30</v>
       </c>
       <c r="B93" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C93" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="D93" s="79">
         <f>E93*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="E93" s="79">
         <f>AVERAGE(G93:Q93)</f>
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="F93" s="79" t="e">
         <f>STDEV(G93:Q93)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G93" s="140"/>
-      <c r="H93" s="140"/>
-      <c r="I93" s="157">
-        <v>1.5</v>
-      </c>
+      <c r="G93" s="79"/>
+      <c r="H93" s="79">
+        <v>1.8</v>
+      </c>
+      <c r="I93" s="157"/>
       <c r="J93" s="140"/>
       <c r="K93" s="141"/>
     </row>
@@ -37159,25 +37247,25 @@
         <v>41</v>
       </c>
       <c r="C94" t="s">
-        <v>45</v>
+        <v>942</v>
       </c>
       <c r="D94" s="79">
         <f>E94*(1+$T$1)</f>
-        <v>2.65</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="E94" s="79">
         <f>AVERAGE(G94:Q94)</f>
-        <v>1.7666666666666666</v>
+        <v>1.6333333333333335</v>
       </c>
       <c r="F94" s="79">
         <f>STDEV(G94:Q94)</f>
-        <v>0.2516611478423586</v>
+        <v>0.32145502536643072</v>
       </c>
       <c r="G94" s="79"/>
-      <c r="H94" s="79">
-        <v>1.8</v>
-      </c>
-      <c r="I94" s="157"/>
+      <c r="H94" s="79"/>
+      <c r="I94" s="157">
+        <v>1.4</v>
+      </c>
       <c r="J94" s="140"/>
       <c r="K94" s="141"/>
       <c r="L94" s="155">
@@ -37189,33 +37277,35 @@
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="156" t="s">
-        <v>21</v>
+        <v>892</v>
       </c>
       <c r="B95" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C95" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="D95" s="79">
         <f>E95*(1+$T$1)</f>
-        <v>1.855</v>
+        <v>1.9537499999999999</v>
       </c>
       <c r="E95" s="79">
         <f>AVERAGE(G95:Q95)</f>
-        <v>1.2366666666666666</v>
+        <v>1.3025</v>
       </c>
       <c r="F95" s="79">
         <f>STDEV(G95:Q95)</f>
-        <v>0.42193996413392026</v>
+        <v>0.29892864254422574</v>
       </c>
       <c r="G95" s="79">
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="H95" s="79">
-        <v>0.9</v>
-      </c>
-      <c r="I95" s="157"/>
+        <v>1.2</v>
+      </c>
+      <c r="I95" s="157">
+        <v>1</v>
+      </c>
       <c r="J95" s="140"/>
       <c r="K95" s="141"/>
       <c r="O95" s="155">
@@ -37224,63 +37314,61 @@
     </row>
     <row r="96" spans="1:16">
       <c r="A96" s="156" t="s">
-        <v>894</v>
+        <v>142</v>
       </c>
       <c r="B96" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C96" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D96" s="79">
         <f>E96*(1+$T$1)</f>
-        <v>1.6124999999999998</v>
+        <v>1.875</v>
       </c>
       <c r="E96" s="79">
         <f>AVERAGE(G96:Q96)</f>
-        <v>1.075</v>
-      </c>
-      <c r="F96" s="79">
+        <v>1.25</v>
+      </c>
+      <c r="F96" s="79" t="e">
         <f>STDEV(G96:Q96)</f>
-        <v>0.24748737341529214</v>
-      </c>
-      <c r="G96" s="79">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G96" s="79"/>
+      <c r="H96" s="79"/>
+      <c r="I96" s="157">
         <v>1.25</v>
       </c>
-      <c r="H96" s="79">
-        <v>0.9</v>
-      </c>
-      <c r="I96" s="157"/>
       <c r="J96" s="140"/>
       <c r="K96" s="141"/>
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="156" t="s">
-        <v>55</v>
+        <v>892</v>
       </c>
       <c r="B97" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C97" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="D97" s="79">
         <f>E97*(1+$T$1)</f>
-        <v>6.0187500000000007</v>
+        <v>4.1999999999999993</v>
       </c>
       <c r="E97" s="79">
         <f>AVERAGE(G97:Q97)</f>
-        <v>4.0125000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="F97" s="79">
         <f>STDEV(G97:Q97)</f>
-        <v>0.37052890125692844</v>
+        <v>1.4944341180973271</v>
       </c>
       <c r="G97" s="79">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="H97" s="79">
-        <v>3.95</v>
+        <v>1.7</v>
       </c>
       <c r="I97" s="157"/>
       <c r="J97" s="140"/>
@@ -37294,31 +37382,31 @@
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="156" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B98" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C98" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="D98" s="79">
         <f>E98*(1+$T$1)</f>
-        <v>6.3937500000000007</v>
+        <v>3.8625000000000003</v>
       </c>
       <c r="E98" s="79">
         <f>AVERAGE(G98:Q98)</f>
-        <v>4.2625000000000002</v>
+        <v>2.5750000000000002</v>
       </c>
       <c r="F98" s="79">
         <f>STDEV(G98:Q98)</f>
-        <v>0.58789880081524093</v>
+        <v>1.7423642940938995</v>
       </c>
       <c r="G98" s="79">
-        <v>4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H98" s="79">
-        <v>4.95</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I98" s="157"/>
       <c r="J98" s="140"/>
@@ -37332,31 +37420,29 @@
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="156" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B99" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C99" t="s">
-        <v>72</v>
-      </c>
-      <c r="D99" s="79">
-        <f>E99*(1+$T$1)</f>
-        <v>5.9287499999999991</v>
+        <v>655</v>
+      </c>
+      <c r="D99" s="79" t="e">
+        <f>E99*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E99" s="79">
         <f>AVERAGE(G99:Q99)</f>
-        <v>3.9524999999999997</v>
+        <v>3.3866666666666667</v>
       </c>
       <c r="F99" s="79">
         <f>STDEV(G99:Q99)</f>
-        <v>0.46657439563982656</v>
-      </c>
-      <c r="G99" s="79">
-        <v>4</v>
-      </c>
+        <v>1.1002423975348952</v>
+      </c>
+      <c r="G99" s="79"/>
       <c r="H99" s="79">
-        <v>3.95</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="I99" s="157"/>
       <c r="J99" s="140"/>
@@ -37370,32 +37456,30 @@
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="156" t="s">
-        <v>55</v>
+        <v>892</v>
       </c>
       <c r="B100" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C100" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="D100" s="79">
         <f>E100*(1+$T$1)</f>
-        <v>5.4224999999999994</v>
+        <v>4.53</v>
       </c>
       <c r="E100" s="79">
         <f>AVERAGE(G100:Q100)</f>
-        <v>3.6149999999999998</v>
+        <v>3.02</v>
       </c>
       <c r="F100" s="79">
         <f>STDEV(G100:Q100)</f>
-        <v>0.63945289114992876</v>
+        <v>1.6760668244434644</v>
       </c>
       <c r="G100" s="79">
-        <v>3</v>
-      </c>
-      <c r="H100" s="79">
-        <v>3.6</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="H100" s="79"/>
       <c r="I100" s="157"/>
       <c r="J100" s="140"/>
       <c r="K100" s="141"/>
@@ -37408,33 +37492,31 @@
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="156" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="B101" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C101" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="D101" s="79">
         <f>E101*(1+$T$1)</f>
-        <v>5.4412500000000001</v>
+        <v>4.3049999999999997</v>
       </c>
       <c r="E101" s="79">
         <f>AVERAGE(G101:Q101)</f>
-        <v>3.6274999999999999</v>
+        <v>2.8699999999999997</v>
       </c>
       <c r="F101" s="79">
         <f>STDEV(G101:Q101)</f>
-        <v>0.63955062348495895</v>
-      </c>
-      <c r="G101" s="79">
-        <v>3</v>
-      </c>
-      <c r="H101" s="79">
-        <v>3.65</v>
-      </c>
-      <c r="I101" s="157"/>
+        <v>1.9224203494553422</v>
+      </c>
+      <c r="G101" s="79"/>
+      <c r="H101" s="79"/>
+      <c r="I101" s="157">
+        <v>0.75</v>
+      </c>
       <c r="J101" s="140"/>
       <c r="K101" s="141"/>
       <c r="L101" s="155">
@@ -37446,58 +37528,64 @@
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="156" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B102" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C102" t="s">
-        <v>36</v>
+        <v>895</v>
       </c>
       <c r="D102" s="79">
         <f>E102*(1+$T$1)</f>
-        <v>1.875</v>
+        <v>2.4375</v>
       </c>
       <c r="E102" s="79">
         <f>AVERAGE(G102:Q102)</f>
-        <v>1.25</v>
-      </c>
-      <c r="F102" s="79" t="e">
+        <v>1.625</v>
+      </c>
+      <c r="F102" s="79">
         <f>STDEV(G102:Q102)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G102" s="140"/>
-      <c r="H102" s="140"/>
+        <v>0.17677669529663689</v>
+      </c>
+      <c r="G102" s="79"/>
+      <c r="H102" s="79">
+        <v>1.5</v>
+      </c>
       <c r="I102" s="157">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="J102" s="140"/>
       <c r="K102" s="141"/>
     </row>
     <row r="103" spans="1:16">
       <c r="A103" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B103" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C103" t="s">
-        <v>913</v>
-      </c>
-      <c r="D103" s="79" t="e">
-        <f>E103*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>125</v>
+      </c>
+      <c r="D103" s="79">
+        <f>E103*(1+$T$1)</f>
+        <v>2.36625</v>
       </c>
       <c r="E103" s="79">
         <f>AVERAGE(G103:Q103)</f>
-        <v>1.65</v>
+        <v>1.5774999999999999</v>
       </c>
       <c r="F103" s="79">
         <f>STDEV(G103:Q103)</f>
-        <v>0.21213203435596428</v>
-      </c>
-      <c r="G103" s="140"/>
-      <c r="H103" s="140"/>
+        <v>0.22366269246345122</v>
+      </c>
+      <c r="G103" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="H103" s="79">
+        <v>1.71</v>
+      </c>
       <c r="I103" s="157"/>
       <c r="J103" s="140"/>
       <c r="K103" s="141"/>
@@ -37510,61 +37598,65 @@
     </row>
     <row r="104" spans="1:16">
       <c r="A104" s="156" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B104" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C104" t="s">
-        <v>942</v>
+        <v>57</v>
       </c>
       <c r="D104" s="79">
-        <f t="shared" ref="D104:D105" si="0">E104*(1+$T$1)</f>
-        <v>2.0999999999999996</v>
+        <f>E104*(1+$T$1)</f>
+        <v>2.5499999999999998</v>
       </c>
       <c r="E104" s="79">
-        <f t="shared" ref="E104:E105" si="1">AVERAGE(G104:Q104)</f>
-        <v>1.4</v>
-      </c>
-      <c r="F104" s="79" t="e">
-        <f t="shared" ref="F104:F105" si="2">STDEV(G104:Q104)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G104" s="79"/>
-      <c r="H104" s="79"/>
-      <c r="I104" s="157">
-        <v>1.4</v>
-      </c>
+        <f>AVERAGE(G104:Q104)</f>
+        <v>1.7</v>
+      </c>
+      <c r="F104" s="79">
+        <f>STDEV(G104:Q104)</f>
+        <v>0.84852813742385691</v>
+      </c>
+      <c r="G104" s="79">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H104" s="79">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I104" s="157"/>
       <c r="J104" s="140"/>
       <c r="K104" s="141"/>
     </row>
     <row r="105" spans="1:16">
       <c r="A105" s="156" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B105" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C105" t="s">
-        <v>943</v>
+        <v>58</v>
       </c>
       <c r="D105" s="79">
-        <f t="shared" si="0"/>
-        <v>2.8125</v>
+        <f>E105*(1+$T$1)</f>
+        <v>2.7</v>
       </c>
       <c r="E105" s="79">
-        <f t="shared" si="1"/>
-        <v>1.875</v>
+        <f>AVERAGE(G105:Q105)</f>
+        <v>1.8</v>
       </c>
       <c r="F105" s="79">
-        <f t="shared" si="2"/>
-        <v>0.5303300858899106</v>
-      </c>
-      <c r="G105" s="79"/>
-      <c r="H105" s="79"/>
-      <c r="I105" s="157">
-        <v>1.5</v>
-      </c>
+        <f>STDEV(G105:Q105)</f>
+        <v>0.9124143795447327</v>
+      </c>
+      <c r="G105" s="79">
+        <v>0.75</v>
+      </c>
+      <c r="H105" s="79">
+        <v>2.4</v>
+      </c>
+      <c r="I105" s="157"/>
       <c r="J105" s="140"/>
       <c r="K105" s="141"/>
       <c r="O105" s="155">
@@ -37573,31 +37665,29 @@
     </row>
     <row r="106" spans="1:16">
       <c r="A106" s="156" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B106" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C106" t="s">
-        <v>944</v>
-      </c>
-      <c r="D106" s="79">
-        <f>E106*(1+$T$1)</f>
-        <v>2.8875000000000002</v>
+        <v>899</v>
+      </c>
+      <c r="D106" s="79" t="e">
+        <f>E106*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E106" s="79">
         <f>AVERAGE(G106:Q106)</f>
-        <v>1.925</v>
-      </c>
-      <c r="F106" s="79">
+        <v>2.25</v>
+      </c>
+      <c r="F106" s="79" t="e">
         <f>STDEV(G106:Q106)</f>
-        <v>0.45961940777125559</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G106" s="79"/>
       <c r="H106" s="79"/>
-      <c r="I106" s="157">
-        <v>1.6</v>
-      </c>
+      <c r="I106" s="157"/>
       <c r="J106" s="140"/>
       <c r="K106" s="141"/>
       <c r="O106" s="155">
@@ -37606,13 +37696,13 @@
     </row>
     <row r="107" spans="1:16">
       <c r="A107" s="156" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="B107" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C107" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="D107" s="79">
         <f>E107*(1+$T$1)</f>
@@ -37626,8 +37716,8 @@
         <f>STDEV(G107:Q107)</f>
         <v>0.60104076400856621</v>
       </c>
-      <c r="G107" s="79"/>
-      <c r="H107" s="79"/>
+      <c r="G107" s="140"/>
+      <c r="H107" s="140"/>
       <c r="I107" s="157">
         <v>1.1000000000000001</v>
       </c>
@@ -37639,31 +37729,29 @@
     </row>
     <row r="108" spans="1:16">
       <c r="A108" s="156" t="s">
-        <v>892</v>
+        <v>55</v>
       </c>
       <c r="B108" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C108" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D108" s="79">
         <f>E108*(1+$T$1)</f>
-        <v>2.1975000000000002</v>
+        <v>2.23</v>
       </c>
       <c r="E108" s="79">
         <f>AVERAGE(G108:Q108)</f>
-        <v>1.4650000000000001</v>
+        <v>1.4866666666666666</v>
       </c>
       <c r="F108" s="79">
         <f>STDEV(G108:Q108)</f>
-        <v>0.29137604568666914</v>
-      </c>
-      <c r="G108" s="79">
-        <v>1.3</v>
-      </c>
+        <v>0.38017539811688744</v>
+      </c>
+      <c r="G108" s="79"/>
       <c r="H108" s="79">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I108" s="157"/>
       <c r="J108" s="140"/>
@@ -37677,32 +37765,28 @@
     </row>
     <row r="109" spans="1:16">
       <c r="A109" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B109" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C109" t="s">
-        <v>80</v>
-      </c>
-      <c r="D109" s="79">
-        <f>E109*(1+$T$1)</f>
-        <v>2.1975000000000002</v>
+        <v>900</v>
+      </c>
+      <c r="D109" s="79" t="e">
+        <f>E109*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E109" s="79">
         <f>AVERAGE(G109:Q109)</f>
-        <v>1.4650000000000001</v>
+        <v>1.6800000000000002</v>
       </c>
       <c r="F109" s="79">
         <f>STDEV(G109:Q109)</f>
-        <v>0.29137604568666914</v>
-      </c>
-      <c r="G109" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="H109" s="79">
-        <v>1.2</v>
-      </c>
+        <v>0.25455844122715532</v>
+      </c>
+      <c r="G109" s="79"/>
+      <c r="H109" s="79"/>
       <c r="I109" s="157"/>
       <c r="J109" s="140"/>
       <c r="K109" s="141"/>
@@ -37715,68 +37799,64 @@
     </row>
     <row r="110" spans="1:16">
       <c r="A110" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B110" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C110" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D110" s="79">
         <f>E110*(1+$T$1)</f>
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E110" s="79">
         <f>AVERAGE(G110:Q110)</f>
-        <v>1.1666666666666667</v>
-      </c>
-      <c r="F110" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="F110" s="79" t="e">
         <f>STDEV(G110:Q110)</f>
-        <v>0.15275252316519497</v>
-      </c>
-      <c r="G110" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="H110" s="79">
-        <v>1.2</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G110" s="140"/>
+      <c r="H110" s="140"/>
       <c r="I110" s="157">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J110" s="140"/>
       <c r="K110" s="141"/>
     </row>
     <row r="111" spans="1:16">
       <c r="A111" s="156" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B111" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C111" t="s">
-        <v>915</v>
-      </c>
-      <c r="D111" s="79" t="e">
-        <f>E111*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>60</v>
+      </c>
+      <c r="D111" s="79">
+        <f>E111*(1+$T$1)</f>
+        <v>2.25</v>
       </c>
       <c r="E111" s="79">
         <f>AVERAGE(G111:Q111)</f>
-        <v>3.0333333333333332</v>
+        <v>1.5</v>
       </c>
       <c r="F111" s="79">
         <f>STDEV(G111:Q111)</f>
-        <v>0.83864970836061026</v>
-      </c>
-      <c r="G111" s="79"/>
-      <c r="H111" s="79">
-        <v>4</v>
-      </c>
-      <c r="I111" s="157"/>
-      <c r="J111" s="140">
-        <v>2.6</v>
-      </c>
+        <v>0.90138781886599728</v>
+      </c>
+      <c r="G111" s="79">
+        <v>0.75</v>
+      </c>
+      <c r="H111" s="79"/>
+      <c r="I111" s="157">
+        <v>1.25</v>
+      </c>
+      <c r="J111" s="140"/>
       <c r="K111" s="141"/>
       <c r="O111" s="155">
         <v>2.5</v>
@@ -37784,34 +37864,34 @@
     </row>
     <row r="112" spans="1:16">
       <c r="A112" s="156" t="s">
-        <v>30</v>
-      </c>
-      <c r="B112" t="s">
-        <v>26</v>
-      </c>
-      <c r="C112" t="s">
-        <v>914</v>
+        <v>55</v>
+      </c>
+      <c r="B112" s="322" t="s">
+        <v>49</v>
+      </c>
+      <c r="C112" s="322" t="s">
+        <v>62</v>
       </c>
       <c r="D112" s="79">
         <f>E112*(1+$T$1)</f>
-        <v>3.6574999999999998</v>
+        <v>3.3200000000000003</v>
       </c>
       <c r="E112" s="79">
         <f>AVERAGE(G112:Q112)</f>
-        <v>2.438333333333333</v>
+        <v>2.2133333333333334</v>
       </c>
       <c r="F112" s="79">
         <f>STDEV(G112:Q112)</f>
-        <v>0.46023544699063185</v>
-      </c>
-      <c r="G112" s="79"/>
+        <v>0.69589271203732628</v>
+      </c>
+      <c r="G112" s="79">
+        <v>1.25</v>
+      </c>
       <c r="H112" s="79">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="I112" s="157"/>
-      <c r="J112" s="140">
-        <v>2.4</v>
-      </c>
+      <c r="J112" s="140"/>
       <c r="K112" s="141"/>
       <c r="L112" s="155">
         <v>2.8</v>
@@ -37831,31 +37911,28 @@
         <v>892</v>
       </c>
       <c r="B113" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C113" t="s">
-        <v>945</v>
-      </c>
-      <c r="D113" s="79">
-        <f>E113*(1+$T$1)</f>
-        <v>2.8125</v>
+        <v>908</v>
+      </c>
+      <c r="D113" s="79" t="e">
+        <f>E113*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E113" s="79">
         <f>AVERAGE(G113:Q113)</f>
-        <v>1.875</v>
-      </c>
-      <c r="F113" s="79">
+        <v>2</v>
+      </c>
+      <c r="F113" s="79" t="e">
         <f>STDEV(G113:Q113)</f>
-        <v>0.5303300858899106</v>
-      </c>
-      <c r="G113" s="79">
-        <f>22.5/10</f>
-        <v>2.25</v>
-      </c>
-      <c r="H113" s="79"/>
-      <c r="I113" s="157">
-        <v>1.5</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G113" s="79"/>
+      <c r="H113" s="79">
+        <v>2</v>
+      </c>
+      <c r="I113" s="157"/>
       <c r="J113" s="140"/>
       <c r="K113" s="141"/>
     </row>
@@ -37864,29 +37941,27 @@
         <v>892</v>
       </c>
       <c r="B114" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C114" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="D114" s="79">
         <f>E114*(1+$T$1)</f>
-        <v>2.1</v>
+        <v>2.1750000000000003</v>
       </c>
       <c r="E114" s="79">
         <f>AVERAGE(G114:Q114)</f>
-        <v>1.4000000000000001</v>
+        <v>1.4500000000000002</v>
       </c>
       <c r="F114" s="79">
         <f>STDEV(G114:Q114)</f>
-        <v>0.40000000000000019</v>
-      </c>
-      <c r="G114" s="79">
-        <v>1.4</v>
-      </c>
-      <c r="H114" s="79"/>
+        <v>0.49497474683058246</v>
+      </c>
+      <c r="G114" s="140"/>
+      <c r="H114" s="140"/>
       <c r="I114" s="157">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J114" s="140"/>
       <c r="K114" s="141"/>
@@ -37896,92 +37971,96 @@
     </row>
     <row r="115" spans="1:16">
       <c r="A115" s="156" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B115" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C115" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D115" s="79">
         <f>E115*(1+$T$1)</f>
-        <v>1.875</v>
+        <v>2.8</v>
       </c>
       <c r="E115" s="79">
         <f>AVERAGE(G115:Q115)</f>
-        <v>1.25</v>
-      </c>
-      <c r="F115" s="79" t="e">
+        <v>1.8666666666666665</v>
+      </c>
+      <c r="F115" s="79">
         <f>STDEV(G115:Q115)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G115" s="79"/>
-      <c r="H115" s="79"/>
-      <c r="I115" s="157">
-        <v>1.25</v>
-      </c>
-      <c r="J115" s="140"/>
+        <v>0.43108390521258616</v>
+      </c>
+      <c r="G115" s="79">
+        <v>1.4</v>
+      </c>
+      <c r="H115" s="79">
+        <v>1.95</v>
+      </c>
+      <c r="I115" s="157"/>
+      <c r="J115" s="140">
+        <v>2.25</v>
+      </c>
       <c r="K115" s="141"/>
     </row>
     <row r="116" spans="1:16">
       <c r="A116" s="156" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B116" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C116" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="D116" s="79">
         <f>E116*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>1.8000000000000003</v>
       </c>
       <c r="E116" s="79">
         <f>AVERAGE(G116:Q116)</f>
-        <v>1.5</v>
-      </c>
-      <c r="F116" s="79" t="e">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="F116" s="79">
         <f>STDEV(G116:Q116)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G116" s="79"/>
-      <c r="H116" s="79"/>
-      <c r="I116" s="157">
-        <v>1.5</v>
-      </c>
+        <v>0.14142135623730948</v>
+      </c>
+      <c r="G116" s="79">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H116" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="I116" s="157"/>
       <c r="J116" s="140"/>
       <c r="K116" s="141"/>
     </row>
     <row r="117" spans="1:16">
       <c r="A117" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B117" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C117" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="D117" s="79">
         <f>E117*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>1.9499999999999997</v>
       </c>
       <c r="E117" s="79">
         <f>AVERAGE(G117:Q117)</f>
-        <v>1.5</v>
+        <v>1.2999999999999998</v>
       </c>
       <c r="F117" s="79">
         <f>STDEV(G117:Q117)</f>
-        <v>0.17320508075688776</v>
+        <v>0.14142135623730948</v>
       </c>
       <c r="G117" s="79">
-        <v>1.4</v>
-      </c>
-      <c r="H117" s="79">
-        <v>1.7</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="H117" s="79"/>
       <c r="I117" s="157"/>
       <c r="J117" s="140"/>
       <c r="K117" s="141"/>
@@ -37991,61 +38070,61 @@
     </row>
     <row r="118" spans="1:16">
       <c r="A118" s="156" t="s">
-        <v>892</v>
+        <v>21</v>
       </c>
       <c r="B118" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C118" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="D118" s="79">
         <f>E118*(1+$T$1)</f>
-        <v>2.0999999999999996</v>
+        <v>3.75</v>
       </c>
       <c r="E118" s="79">
         <f>AVERAGE(G118:Q118)</f>
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="F118" s="79" t="e">
         <f>STDEV(G118:Q118)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G118" s="79"/>
-      <c r="H118" s="79"/>
+      <c r="G118" s="140"/>
+      <c r="H118" s="140"/>
       <c r="I118" s="157">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J118" s="140"/>
       <c r="K118" s="141"/>
     </row>
     <row r="119" spans="1:16">
       <c r="A119" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B119" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C119" t="s">
-        <v>93</v>
-      </c>
-      <c r="D119" s="79">
-        <f>E119*(1+$T$1)</f>
-        <v>2.2949999999999999</v>
+        <v>912</v>
+      </c>
+      <c r="D119" s="79" t="e">
+        <f>E119*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E119" s="79">
         <f>AVERAGE(G119:Q119)</f>
-        <v>1.53</v>
+        <v>2.5250000000000004</v>
       </c>
       <c r="F119" s="79">
         <f>STDEV(G119:Q119)</f>
-        <v>4.2426406871192889E-2</v>
-      </c>
-      <c r="G119" s="140"/>
-      <c r="H119" s="140"/>
-      <c r="I119" s="157">
-        <v>1.5</v>
-      </c>
+        <v>1.3647160876900357</v>
+      </c>
+      <c r="G119" s="79"/>
+      <c r="H119" s="79">
+        <v>3.49</v>
+      </c>
+      <c r="I119" s="157"/>
       <c r="J119" s="140"/>
       <c r="K119" s="141"/>
       <c r="N119" s="155">
@@ -38057,10 +38136,10 @@
         <v>142</v>
       </c>
       <c r="B120" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C120" t="s">
-        <v>651</v>
+        <v>911</v>
       </c>
       <c r="D120" s="79" t="e">
         <f>E120*(1+$O$1)</f>
@@ -38074,8 +38153,8 @@
         <f>STDEV(G120:Q120)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G120" s="140"/>
-      <c r="H120" s="140"/>
+      <c r="G120" s="79"/>
+      <c r="H120" s="79"/>
       <c r="I120" s="157"/>
       <c r="J120" s="140"/>
       <c r="K120" s="141"/>
@@ -38088,31 +38167,31 @@
         <v>142</v>
       </c>
       <c r="B121" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C121" t="s">
-        <v>109</v>
-      </c>
-      <c r="D121" s="79">
-        <f>E121*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>930</v>
+      </c>
+      <c r="D121" s="79" t="e">
+        <f>E121*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E121" s="79">
         <f>AVERAGE(G121:Q121)</f>
-        <v>1.1000000000000001</v>
+        <v>1.45</v>
       </c>
       <c r="F121" s="79">
         <f>STDEV(G121:Q121)</f>
-        <v>0</v>
-      </c>
-      <c r="G121" s="79">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H121" s="79">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I121" s="157"/>
-      <c r="J121" s="140"/>
+        <v>7.0710678118654821E-2</v>
+      </c>
+      <c r="G121" s="79"/>
+      <c r="H121" s="79"/>
+      <c r="I121" s="157">
+        <v>1.5</v>
+      </c>
+      <c r="J121" s="140">
+        <v>1.4</v>
+      </c>
       <c r="K121" s="141"/>
     </row>
     <row r="122" spans="1:16">
@@ -38120,86 +38199,86 @@
         <v>142</v>
       </c>
       <c r="B122" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C122" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D122" s="79">
         <f>E122*(1+$T$1)</f>
-        <v>2.625</v>
+        <v>1.875</v>
       </c>
       <c r="E122" s="79">
         <f>AVERAGE(G122:Q122)</f>
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="F122" s="79" t="e">
         <f>STDEV(G122:Q122)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G122" s="79"/>
-      <c r="H122" s="79"/>
+      <c r="G122" s="140"/>
+      <c r="H122" s="140"/>
       <c r="I122" s="157">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="J122" s="140"/>
       <c r="K122" s="141"/>
     </row>
     <row r="123" spans="1:16">
       <c r="A123" s="156" t="s">
-        <v>893</v>
+        <v>142</v>
       </c>
       <c r="B123" t="s">
-        <v>33</v>
-      </c>
-      <c r="C123" s="66" t="s">
-        <v>94</v>
+        <v>49</v>
+      </c>
+      <c r="C123" t="s">
+        <v>129</v>
       </c>
       <c r="D123" s="79">
         <f>E123*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="E123" s="79">
         <f>AVERAGE(G123:Q123)</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F123" s="79" t="e">
         <f>STDEV(G123:Q123)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G123" s="140"/>
-      <c r="H123" s="140"/>
+      <c r="G123" s="79"/>
+      <c r="H123" s="79"/>
       <c r="I123" s="157">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J123" s="140"/>
       <c r="K123" s="141"/>
     </row>
     <row r="124" spans="1:16">
       <c r="A124" s="156" t="s">
-        <v>892</v>
+        <v>55</v>
       </c>
       <c r="B124" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C124" t="s">
-        <v>311</v>
+        <v>68</v>
       </c>
       <c r="D124" s="79">
         <f>E124*(1+$T$1)</f>
-        <v>2.4937500000000004</v>
+        <v>3.2437500000000004</v>
       </c>
       <c r="E124" s="79">
         <f>AVERAGE(G124:Q124)</f>
-        <v>1.6625000000000001</v>
+        <v>2.1625000000000001</v>
       </c>
       <c r="F124" s="79">
         <f>STDEV(G124:Q124)</f>
-        <v>0.28686524130097363</v>
+        <v>1.2378576924132543</v>
       </c>
       <c r="G124" s="79"/>
       <c r="H124" s="79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I124" s="157"/>
       <c r="J124" s="140"/>
@@ -38216,61 +38295,61 @@
     </row>
     <row r="125" spans="1:16">
       <c r="A125" s="156" t="s">
-        <v>21</v>
+        <v>894</v>
       </c>
       <c r="B125" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C125" t="s">
-        <v>937</v>
-      </c>
-      <c r="D125" s="79" t="e">
-        <f>E125*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>115</v>
+      </c>
+      <c r="D125" s="79">
+        <f>E125*(1+$T$1)</f>
+        <v>1.875</v>
       </c>
       <c r="E125" s="79">
         <f>AVERAGE(G125:Q125)</f>
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="F125" s="79" t="e">
         <f>STDEV(G125:Q125)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G125" s="79"/>
+      <c r="G125" s="79">
+        <v>1.25</v>
+      </c>
       <c r="H125" s="79"/>
-      <c r="I125" s="157">
-        <v>2</v>
-      </c>
+      <c r="I125" s="157"/>
       <c r="J125" s="140"/>
       <c r="K125" s="141"/>
     </row>
     <row r="126" spans="1:16">
       <c r="A126" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B126" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C126" t="s">
-        <v>938</v>
+        <v>130</v>
       </c>
       <c r="D126" s="79">
         <f>E126*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="E126" s="79">
         <f>AVERAGE(G126:Q126)</f>
-        <v>1.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F126" s="79" t="e">
         <f>STDEV(G126:Q126)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G126" s="79">
-        <v>1.5</v>
-      </c>
-      <c r="H126" s="79"/>
-      <c r="I126" s="157"/>
+      <c r="G126" s="140"/>
+      <c r="H126" s="140"/>
+      <c r="I126" s="157">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="J126" s="140"/>
       <c r="K126" s="141"/>
     </row>
@@ -38279,55 +38358,59 @@
         <v>892</v>
       </c>
       <c r="B127" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C127" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D127" s="79">
         <f>E127*(1+$T$1)</f>
-        <v>1.6500000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="E127" s="79">
         <f>AVERAGE(G127:Q127)</f>
-        <v>1.1000000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="F127" s="79" t="e">
         <f>STDEV(G127:Q127)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G127" s="79"/>
-      <c r="H127" s="79">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I127" s="157"/>
+      <c r="H127" s="79"/>
+      <c r="I127" s="157">
+        <v>2.5</v>
+      </c>
       <c r="J127" s="140"/>
       <c r="K127" s="141"/>
     </row>
     <row r="128" spans="1:16">
       <c r="A128" s="156" t="s">
-        <v>142</v>
+        <v>894</v>
       </c>
       <c r="B128" t="s">
         <v>49</v>
       </c>
       <c r="C128" t="s">
-        <v>918</v>
-      </c>
-      <c r="D128" s="79" t="e">
-        <f>E128*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>117</v>
+      </c>
+      <c r="D128" s="79">
+        <f>E128*(1+$T$1)</f>
+        <v>1.8249999999999997</v>
       </c>
       <c r="E128" s="79">
         <f>AVERAGE(G128:Q128)</f>
-        <v>1.5</v>
-      </c>
-      <c r="F128" s="79" t="e">
+        <v>1.2166666666666666</v>
+      </c>
+      <c r="F128" s="79">
         <f>STDEV(G128:Q128)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G128" s="79"/>
-      <c r="H128" s="79"/>
+        <v>0.30138568866708615</v>
+      </c>
+      <c r="G128" s="79">
+        <v>1.25</v>
+      </c>
+      <c r="H128" s="79">
+        <v>0.9</v>
+      </c>
       <c r="I128" s="157"/>
       <c r="J128" s="140"/>
       <c r="K128" s="141"/>
@@ -38340,10 +38423,10 @@
         <v>142</v>
       </c>
       <c r="B129" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C129" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D129" s="79" t="e">
         <f>E129*(1+$O$1)</f>
@@ -38351,18 +38434,16 @@
       </c>
       <c r="E129" s="79">
         <f>AVERAGE(G129:Q129)</f>
-        <v>1.2333333333333334</v>
+        <v>1.35</v>
       </c>
       <c r="F129" s="79">
         <f>STDEV(G129:Q129)</f>
-        <v>0.25166114784235771</v>
+        <v>0.21213203435596303</v>
       </c>
       <c r="G129" s="79"/>
       <c r="H129" s="79"/>
       <c r="I129" s="157"/>
-      <c r="J129" s="140">
-        <v>1</v>
-      </c>
+      <c r="J129" s="140"/>
       <c r="K129" s="141"/>
       <c r="N129" s="155">
         <v>1.2</v>
@@ -38405,17 +38486,17 @@
     </row>
     <row r="131" spans="1:16">
       <c r="A131" s="156" t="s">
-        <v>892</v>
+        <v>142</v>
       </c>
       <c r="B131" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C131" t="s">
-        <v>920</v>
-      </c>
-      <c r="D131" s="79" t="e">
-        <f>E131*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>897</v>
+      </c>
+      <c r="D131" s="79">
+        <f>E131*(1+$T$1)</f>
+        <v>2.25</v>
       </c>
       <c r="E131" s="79">
         <f>AVERAGE(G131:Q131)</f>
@@ -38436,32 +38517,28 @@
     </row>
     <row r="132" spans="1:16">
       <c r="A132" s="156" t="s">
-        <v>892</v>
+        <v>55</v>
       </c>
       <c r="B132" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C132" t="s">
-        <v>97</v>
-      </c>
-      <c r="D132" s="79">
-        <f>E132*(1+$T$1)</f>
-        <v>1.6949999999999998</v>
+        <v>923</v>
+      </c>
+      <c r="D132" s="79" t="e">
+        <f>E132*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E132" s="79">
         <f>AVERAGE(G132:Q132)</f>
-        <v>1.1299999999999999</v>
+        <v>1.1166666666666665</v>
       </c>
       <c r="F132" s="79">
         <f>STDEV(G132:Q132)</f>
-        <v>0.30331501776206288</v>
-      </c>
-      <c r="G132" s="79">
-        <v>1.3</v>
-      </c>
-      <c r="H132" s="79">
-        <v>1</v>
-      </c>
+        <v>0.40104031385053251</v>
+      </c>
+      <c r="G132" s="79"/>
+      <c r="H132" s="79"/>
       <c r="I132" s="157"/>
       <c r="J132" s="140"/>
       <c r="K132" s="141"/>
@@ -38477,34 +38554,30 @@
     </row>
     <row r="133" spans="1:16">
       <c r="A133" s="156" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="B133" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C133" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="D133" s="79">
         <f>E133*(1+$T$1)</f>
-        <v>2.3525</v>
+        <v>2.2725</v>
       </c>
       <c r="E133" s="79">
         <f>AVERAGE(G133:Q133)</f>
-        <v>1.5683333333333334</v>
+        <v>1.5150000000000001</v>
       </c>
       <c r="F133" s="79">
         <f>STDEV(G133:Q133)</f>
-        <v>0.27462095088806732</v>
-      </c>
-      <c r="G133" s="79">
-        <v>1.4</v>
-      </c>
-      <c r="H133" s="79">
-        <v>1.3</v>
-      </c>
+        <v>0.38802920852258826</v>
+      </c>
+      <c r="G133" s="140"/>
+      <c r="H133" s="140"/>
       <c r="I133" s="157">
-        <v>1.75</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J133" s="140"/>
       <c r="K133" s="141"/>
@@ -38520,30 +38593,30 @@
     </row>
     <row r="134" spans="1:16">
       <c r="A134" s="156" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B134" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C134" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="D134" s="79">
         <f>E134*(1+$T$1)</f>
-        <v>2.3774999999999999</v>
+        <v>2.1524999999999999</v>
       </c>
       <c r="E134" s="79">
         <f>AVERAGE(G134:Q134)</f>
-        <v>1.585</v>
+        <v>1.4350000000000001</v>
       </c>
       <c r="F134" s="79">
         <f>STDEV(G134:Q134)</f>
-        <v>0.26162950903902327</v>
-      </c>
-      <c r="G134" s="79">
-        <v>1.4</v>
-      </c>
-      <c r="H134" s="79"/>
+        <v>0.47376154339498688</v>
+      </c>
+      <c r="G134" s="79"/>
+      <c r="H134" s="79">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="I134" s="157"/>
       <c r="J134" s="140"/>
       <c r="K134" s="141"/>
@@ -38553,13 +38626,13 @@
     </row>
     <row r="135" spans="1:16">
       <c r="A135" s="156" t="s">
-        <v>142</v>
+        <v>894</v>
       </c>
       <c r="B135" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C135" t="s">
-        <v>655</v>
+        <v>901</v>
       </c>
       <c r="D135" s="79" t="e">
         <f>E135*(1+$O$1)</f>
@@ -38567,16 +38640,14 @@
       </c>
       <c r="E135" s="79">
         <f>AVERAGE(G135:Q135)</f>
-        <v>2.5333333333333332</v>
+        <v>2.65</v>
       </c>
       <c r="F135" s="79">
         <f>STDEV(G135:Q135)</f>
-        <v>0.25166114784235832</v>
+        <v>0.21213203435596414</v>
       </c>
       <c r="G135" s="79"/>
-      <c r="H135" s="79">
-        <v>2.2999999999999998</v>
-      </c>
+      <c r="H135" s="79"/>
       <c r="I135" s="157"/>
       <c r="J135" s="140"/>
       <c r="K135" s="141"/>
@@ -38592,31 +38663,30 @@
         <v>142</v>
       </c>
       <c r="B136" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C136" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="D136" s="79">
         <f>E136*(1+$T$1)</f>
-        <v>2.7349999999999999</v>
+        <v>2.5949999999999998</v>
       </c>
       <c r="E136" s="79">
         <f>AVERAGE(G136:Q136)</f>
-        <v>1.8233333333333333</v>
+        <v>1.73</v>
       </c>
       <c r="F136" s="79">
         <f>STDEV(G136:Q136)</f>
-        <v>0.5857189314566047</v>
-      </c>
-      <c r="G136" s="79"/>
-      <c r="H136" s="79">
-        <v>1.99</v>
-      </c>
+        <v>0.67230945255886443</v>
+      </c>
+      <c r="G136" s="79">
+        <f>14/10</f>
+        <v>1.4</v>
+      </c>
+      <c r="H136" s="79"/>
       <c r="I136" s="157"/>
-      <c r="J136" s="140">
-        <v>1.7</v>
-      </c>
+      <c r="J136" s="140"/>
       <c r="K136" s="141"/>
       <c r="L136" s="155">
         <v>1.5</v>
@@ -38633,34 +38703,32 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137" s="94" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="B137" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C137" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="D137" s="79">
         <f>E137*(1+$T$1)</f>
-        <v>1.78125</v>
+        <v>1.8000000000000003</v>
       </c>
       <c r="E137" s="79">
         <f>AVERAGE(G137:Q137)</f>
-        <v>1.1875</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="F137" s="79">
         <f>STDEV(G137:Q137)</f>
-        <v>0.13149778198382917</v>
-      </c>
-      <c r="G137" s="79"/>
-      <c r="H137" s="79">
-        <v>1</v>
-      </c>
+        <v>9.9999999999999978E-2</v>
+      </c>
+      <c r="G137" s="79">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H137" s="79"/>
       <c r="I137" s="105"/>
-      <c r="J137" s="140">
-        <v>1.25</v>
-      </c>
+      <c r="J137" s="140"/>
       <c r="K137" s="141"/>
       <c r="L137" s="155">
         <v>1.3</v>
@@ -38671,33 +38739,31 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138" s="322" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B138" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C138" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="D138" s="79">
         <f>E138*(1+$T$1)</f>
-        <v>3.7650000000000006</v>
+        <v>3.4725000000000001</v>
       </c>
       <c r="E138" s="79">
         <f>AVERAGE(G138:Q138)</f>
-        <v>2.5100000000000002</v>
+        <v>2.3149999999999999</v>
       </c>
       <c r="F138" s="79">
         <f>STDEV(G138:Q138)</f>
-        <v>0.61506097258727077</v>
-      </c>
-      <c r="G138" s="79"/>
-      <c r="H138" s="79">
-        <v>1.9</v>
-      </c>
-      <c r="I138" s="201">
-        <v>2.5</v>
-      </c>
+        <v>1.1525840533340725</v>
+      </c>
+      <c r="G138" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="H138" s="79"/>
+      <c r="I138" s="201"/>
       <c r="J138" s="140"/>
       <c r="K138" s="141"/>
       <c r="O138" s="155">
@@ -38705,30 +38771,32 @@
       </c>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" t="s">
-        <v>21</v>
+      <c r="A139" s="322" t="s">
+        <v>142</v>
       </c>
       <c r="B139" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C139" t="s">
-        <v>921</v>
-      </c>
-      <c r="D139" s="79" t="e">
-        <f>E139*(1+$O$1)</f>
-        <v>#VALUE!</v>
+        <v>941</v>
+      </c>
+      <c r="D139" s="79">
+        <f>E139*(1+$T$1)</f>
+        <v>2.7374999999999998</v>
       </c>
       <c r="E139" s="79">
         <f>AVERAGE(G139:Q139)</f>
-        <v>2.25</v>
+        <v>1.825</v>
       </c>
       <c r="F139" s="79">
         <f>STDEV(G139:Q139)</f>
-        <v>0.45000000000000062</v>
-      </c>
-      <c r="G139" s="79"/>
+        <v>0.6184658438426498</v>
+      </c>
+      <c r="G139" s="79">
+        <v>1.5</v>
+      </c>
       <c r="H139" s="79">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="I139" s="79"/>
       <c r="J139" s="140"/>
@@ -38742,33 +38810,31 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" s="322" t="s">
-        <v>21</v>
+        <v>894</v>
       </c>
       <c r="B140" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C140" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="D140" s="79">
         <f>E140*(1+$T$1)</f>
-        <v>4.1999999999999993</v>
+        <v>3</v>
       </c>
       <c r="E140" s="79">
         <f>AVERAGE(G140:Q140)</f>
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="F140" s="79">
         <f>STDEV(G140:Q140)</f>
-        <v>0.85244745683629541</v>
-      </c>
-      <c r="G140" s="79"/>
-      <c r="H140" s="79">
-        <v>4</v>
-      </c>
-      <c r="I140" s="79">
-        <v>2.5</v>
-      </c>
+        <v>0.70000000000000018</v>
+      </c>
+      <c r="G140" s="79">
+        <v>1.3</v>
+      </c>
+      <c r="H140" s="79"/>
+      <c r="I140" s="79"/>
       <c r="J140" s="140"/>
       <c r="K140" s="141"/>
       <c r="L140" s="155">
@@ -38780,32 +38846,30 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" s="322" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C141" t="s">
-        <v>922</v>
-      </c>
-      <c r="D141" s="79">
-        <f>E141*(1+$T$1)</f>
-        <v>2.3250000000000002</v>
+        <v>924</v>
+      </c>
+      <c r="D141" s="79" t="e">
+        <f>E141*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E141" s="79">
         <f>AVERAGE(G141:Q141)</f>
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="F141" s="79">
         <f>STDEV(G141:Q141)</f>
-        <v>0.47749345545253263</v>
+        <v>0.42924352062669513</v>
       </c>
       <c r="G141" s="79"/>
-      <c r="H141" s="79">
-        <v>1.1000000000000001</v>
-      </c>
+      <c r="H141" s="79"/>
       <c r="I141" s="79">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J141" s="140"/>
       <c r="K141" s="141"/>
@@ -38824,59 +38888,57 @@
     </row>
     <row r="142" spans="1:16">
       <c r="A142" s="156" t="s">
-        <v>142</v>
+        <v>894</v>
       </c>
       <c r="B142" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C142" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D142" s="79">
         <f>E142*(1+$T$1)</f>
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="E142" s="79">
         <f>AVERAGE(G142:Q142)</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F142" s="79" t="e">
         <f>STDEV(G142:Q142)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G142" s="79"/>
-      <c r="H142" s="79"/>
+      <c r="G142" s="140"/>
+      <c r="H142" s="140"/>
       <c r="I142" s="157">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J142" s="140"/>
       <c r="K142" s="141"/>
     </row>
     <row r="143" spans="1:16">
       <c r="A143" s="322" t="s">
-        <v>892</v>
+        <v>30</v>
       </c>
       <c r="B143" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C143" t="s">
-        <v>103</v>
-      </c>
-      <c r="D143" s="79">
-        <f>E143*(1+$T$1)</f>
-        <v>2.0250000000000004</v>
+        <v>925</v>
+      </c>
+      <c r="D143" s="79" t="e">
+        <f>E143*(1+$O$1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E143" s="79">
         <f>AVERAGE(G143:Q143)</f>
-        <v>1.35</v>
-      </c>
-      <c r="F143" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="F143" s="79" t="e">
         <f>STDEV(G143:Q143)</f>
-        <v>0.21213203435596303</v>
-      </c>
-      <c r="G143" s="79">
-        <v>1.2</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G143" s="79"/>
       <c r="H143" s="79"/>
       <c r="I143" s="79"/>
       <c r="J143" s="140"/>
@@ -38887,61 +38949,61 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" s="322" t="s">
-        <v>142</v>
+        <v>894</v>
       </c>
       <c r="B144" t="s">
         <v>51</v>
       </c>
       <c r="C144" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D144" s="79">
         <f>E144*(1+$T$1)</f>
-        <v>2.0999999999999996</v>
+        <v>2.25</v>
       </c>
       <c r="E144" s="79">
         <f>AVERAGE(G144:Q144)</f>
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F144" s="79" t="e">
         <f>STDEV(G144:Q144)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G144" s="79"/>
-      <c r="H144" s="79"/>
+      <c r="G144" s="140"/>
+      <c r="H144" s="140"/>
       <c r="I144" s="79">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J144" s="140"/>
       <c r="K144" s="141"/>
     </row>
     <row r="145" spans="1:15">
       <c r="A145" s="322" t="s">
-        <v>892</v>
+        <v>21</v>
       </c>
       <c r="B145" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C145" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="D145" s="79">
         <f>E145*(1+$T$1)</f>
-        <v>2.1949999999999998</v>
+        <v>2.2450000000000001</v>
       </c>
       <c r="E145" s="79">
         <f>AVERAGE(G145:Q145)</f>
-        <v>1.4633333333333332</v>
+        <v>1.4966666666666668</v>
       </c>
       <c r="F145" s="79">
         <f>STDEV(G145:Q145)</f>
-        <v>0.44613152021946778</v>
+        <v>0.39501054838236005</v>
       </c>
       <c r="G145" s="79"/>
-      <c r="H145" s="79">
-        <v>1</v>
-      </c>
-      <c r="I145" s="79"/>
+      <c r="H145" s="79"/>
+      <c r="I145" s="79">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="J145" s="140"/>
       <c r="K145" s="141"/>
       <c r="N145" s="155">
@@ -38953,32 +39015,33 @@
     </row>
     <row r="146" spans="1:15">
       <c r="A146" s="322" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B146" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C146" t="s">
-        <v>91</v>
+        <v>945</v>
       </c>
       <c r="D146" s="79">
         <f>E146*(1+$T$1)</f>
-        <v>1.9000000000000004</v>
+        <v>2.6749999999999998</v>
       </c>
       <c r="E146" s="79">
         <f>AVERAGE(G146:Q146)</f>
-        <v>1.2666666666666668</v>
+        <v>1.7833333333333332</v>
       </c>
       <c r="F146" s="79">
         <f>STDEV(G146:Q146)</f>
-        <v>0.30550504633038922</v>
+        <v>0.40722639076235517</v>
       </c>
       <c r="G146" s="79">
-        <v>1.2</v>
+        <f>22.5/10</f>
+        <v>2.25</v>
       </c>
       <c r="H146" s="79"/>
       <c r="I146" s="79">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J146" s="140"/>
       <c r="K146" s="141"/>
@@ -38991,27 +39054,27 @@
         <v>142</v>
       </c>
       <c r="B147" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C147" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="D147" s="79">
         <f>E147*(1+$T$1)</f>
-        <v>2.3849999999999998</v>
+        <v>2.46</v>
       </c>
       <c r="E147" s="79">
         <f>AVERAGE(G147:Q147)</f>
-        <v>1.5899999999999999</v>
+        <v>1.6400000000000001</v>
       </c>
       <c r="F147" s="79">
         <f>STDEV(G147:Q147)</f>
-        <v>8.4852813742385624E-2</v>
+        <v>0.15556349186104043</v>
       </c>
       <c r="G147" s="79"/>
       <c r="H147" s="79"/>
       <c r="I147" s="79">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="J147" s="140"/>
       <c r="K147" s="141"/>
@@ -39021,58 +39084,60 @@
     </row>
     <row r="148" spans="1:15">
       <c r="A148" s="322" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B148" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C148" t="s">
-        <v>110</v>
+        <v>938</v>
       </c>
       <c r="D148" s="79">
         <f>E148*(1+$T$1)</f>
-        <v>1.125</v>
+        <v>2.25</v>
       </c>
       <c r="E148" s="79">
         <f>AVERAGE(G148:Q148)</f>
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="F148" s="79" t="e">
         <f>STDEV(G148:Q148)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G148" s="79"/>
+      <c r="G148" s="79">
+        <v>1.5</v>
+      </c>
       <c r="H148" s="79"/>
-      <c r="I148" s="79">
-        <v>0.75</v>
-      </c>
+      <c r="I148" s="79"/>
       <c r="J148" s="140"/>
       <c r="K148" s="141"/>
     </row>
     <row r="149" spans="1:15">
       <c r="A149" s="322" t="s">
-        <v>142</v>
+        <v>892</v>
       </c>
       <c r="B149" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C149" t="s">
-        <v>897</v>
+        <v>134</v>
       </c>
       <c r="D149" s="79">
         <f>E149*(1+$T$1)</f>
-        <v>2.9249999999999998</v>
+        <v>2.2874999999999996</v>
       </c>
       <c r="E149" s="79">
         <f>AVERAGE(G149:Q149)</f>
-        <v>1.95</v>
-      </c>
-      <c r="F149" s="79" t="e">
+        <v>1.5249999999999999</v>
+      </c>
+      <c r="F149" s="79">
         <f>STDEV(G149:Q149)</f>
-        <v>#DIV/0!</v>
+        <v>0.60104076400856621</v>
       </c>
       <c r="G149" s="79"/>
-      <c r="H149" s="79"/>
+      <c r="H149" s="79">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="I149" s="79"/>
       <c r="J149" s="140"/>
       <c r="K149" s="141"/>
@@ -39085,26 +39150,28 @@
         <v>142</v>
       </c>
       <c r="B150" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C150" t="s">
-        <v>898</v>
+        <v>140</v>
       </c>
       <c r="D150" s="79">
         <f>E150*(1+$T$1)</f>
-        <v>3.6524999999999999</v>
+        <v>3.1349999999999998</v>
       </c>
       <c r="E150" s="79">
         <f>AVERAGE(G150:Q150)</f>
-        <v>2.4350000000000001</v>
+        <v>2.09</v>
       </c>
       <c r="F150" s="79">
         <f>STDEV(G150:Q150)</f>
-        <v>9.1923881554251102E-2</v>
+        <v>0.60108235708594948</v>
       </c>
       <c r="G150" s="79"/>
       <c r="H150" s="79"/>
-      <c r="I150" s="79"/>
+      <c r="I150" s="79">
+        <v>1.4</v>
+      </c>
       <c r="J150" s="140"/>
       <c r="K150" s="141"/>
       <c r="N150" s="155">
@@ -60395,7 +60462,7 @@
       </c>
       <c r="D4" s="248">
         <f>SUMPRODUCT(I4:I9, E4:E9)</f>
-        <v>22.89473511904762</v>
+        <v>22.607010912698417</v>
       </c>
       <c r="E4" s="212">
         <v>3</v>
@@ -60409,7 +60476,7 @@
       </c>
       <c r="I4" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Early Spring*", 'Master Variety List'!B:B, "*Focal*")</f>
-        <v>2.5036666666666667</v>
+        <v>2.4263333333333335</v>
       </c>
       <c r="J4" s="179">
         <v>500</v>
@@ -60447,7 +60514,7 @@
       </c>
       <c r="I5" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Early Spring*", 'Master Variety List'!B:B, "*Foundation*")</f>
-        <v>1.8387500000000001</v>
+        <v>1.6369444444444445</v>
       </c>
       <c r="J5" s="179">
         <v>700</v>
@@ -60485,7 +60552,7 @@
       </c>
       <c r="I6" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Early Spring*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>1.6676041666666666</v>
+        <v>1.970907738095238</v>
       </c>
       <c r="J6" s="179">
         <v>100</v>
@@ -60516,7 +60583,7 @@
       </c>
       <c r="I7" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Early Spring*", 'Master Variety List'!B:B, "*Float*")</f>
-        <v>1.5766666666666667</v>
+        <v>1.9304761904761905</v>
       </c>
       <c r="J7" s="179">
         <v>400</v>
@@ -60551,7 +60618,7 @@
       </c>
       <c r="I8" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Early Spring*", 'Master Variety List'!B:B, "*Finisher*")</f>
-        <v>2.0083333333333333</v>
+        <v>1.6555555555555557</v>
       </c>
       <c r="J8" s="179">
         <v>25</v>
@@ -60587,7 +60654,7 @@
       </c>
       <c r="I9" s="170">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Early Spring*", 'Master Variety List'!B:B, "*Foliage*")</f>
-        <v>1.4728571428571429</v>
+        <v>1.6209523809523809</v>
       </c>
       <c r="J9" s="180">
         <v>150</v>
@@ -63086,7 +63153,7 @@
       </c>
       <c r="E4" s="248">
         <f>SUMPRODUCT(F4:F9, J4:J9)</f>
-        <v>58.764747231627346</v>
+        <v>58.539058448211222</v>
       </c>
       <c r="F4" s="212">
         <v>6</v>
@@ -63100,7 +63167,7 @@
       </c>
       <c r="J4" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Late Spring*", 'Master Variety List'!B:B, "*Focal*")</f>
-        <v>3.5614583333333334</v>
+        <v>2.6154583333333332</v>
       </c>
       <c r="K4" s="181">
         <v>500</v>
@@ -63129,7 +63196,7 @@
       </c>
       <c r="J5" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Late Spring*", 'Master Variety List'!B:B, "*Foundation*")</f>
-        <v>1.6612666666666667</v>
+        <v>1.8936111111111116</v>
       </c>
       <c r="K5" s="181">
         <v>1711</v>
@@ -63158,7 +63225,7 @@
       </c>
       <c r="J6" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Late Spring*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>1.6491111111111112</v>
+        <v>1.6969285714285716</v>
       </c>
       <c r="K6" s="181">
         <v>264</v>
@@ -63187,7 +63254,7 @@
       </c>
       <c r="J7" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Late Spring*", 'Master Variety List'!B:B, "*Float*")</f>
-        <v>1.4819230769230769</v>
+        <v>1.8906410256410255</v>
       </c>
       <c r="K7" s="181">
         <v>83</v>
@@ -63216,7 +63283,7 @@
       </c>
       <c r="J8" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Late Spring*", 'Master Variety List'!B:B, "*Finisher*")</f>
-        <v>1.7894791666666667</v>
+        <v>1.7044270833333333</v>
       </c>
       <c r="K8" s="181">
         <v>30</v>
@@ -63246,7 +63313,7 @@
       </c>
       <c r="J9" s="170">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Late Spring*", 'Master Variety List'!B:B, "*Foliage*")</f>
-        <v>1.4383333333333335</v>
+        <v>1.6270833333333332</v>
       </c>
       <c r="K9" s="182">
         <v>1000</v>
@@ -64172,7 +64239,7 @@
       </c>
       <c r="E4" s="248">
         <f>SUMPRODUCT(J4:J9, F4:F9)</f>
-        <v>39.527724547382448</v>
+        <v>41.120190739085473</v>
       </c>
       <c r="F4" s="212">
         <v>3</v>
@@ -64186,7 +64253,7 @@
       </c>
       <c r="J4" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Summer*", 'Master Variety List'!B:B, "*Focal*")</f>
-        <v>2.6453333333333333</v>
+        <v>2.0804999999999998</v>
       </c>
       <c r="K4" s="184">
         <v>500</v>
@@ -64217,7 +64284,7 @@
       </c>
       <c r="J5" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Summer*", 'Master Variety List'!B:B, "*Foundation*")</f>
-        <v>1.6591883116883117</v>
+        <v>1.7135227272727276</v>
       </c>
       <c r="K5" s="184">
         <v>2000</v>
@@ -64248,7 +64315,7 @@
       </c>
       <c r="J6" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Summer*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>1.6082894736842104</v>
+        <v>1.6617543859649124</v>
       </c>
       <c r="K6" s="184">
         <v>500</v>
@@ -64279,7 +64346,7 @@
       </c>
       <c r="J7" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Summer*", 'Master Variety List'!B:B, "*Float*")</f>
-        <v>1.3608333333333333</v>
+        <v>2.008690476190476</v>
       </c>
       <c r="K7" s="184">
         <v>500</v>
@@ -64310,7 +64377,7 @@
       </c>
       <c r="J8" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Summer*", 'Master Variety List'!B:B, "*Finisher*")</f>
-        <v>1.7747807017543862</v>
+        <v>1.5863596491228071</v>
       </c>
       <c r="K8" s="184">
         <v>50</v>
@@ -64342,7 +64409,7 @@
       </c>
       <c r="J9" s="170">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Summer*", 'Master Variety List'!B:B, "*Foliage*")</f>
-        <v>1.4392307692307693</v>
+        <v>1.7152564102564098</v>
       </c>
       <c r="K9" s="185">
         <v>150</v>
@@ -67267,7 +67334,7 @@
       <c r="L2" s="80"/>
       <c r="O2" s="163">
         <f>MIN($D$24)</f>
-        <v>55.962819066898014</v>
+        <v>57.486429776363991</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="21" customHeight="1">
@@ -67462,7 +67529,7 @@
       </c>
       <c r="D13" s="248">
         <f>SUMPRODUCT(E13:E18, I13:I18)</f>
-        <v>34.883142068457857</v>
+        <v>35.828833083583078</v>
       </c>
       <c r="E13" s="212">
         <v>3</v>
@@ -67476,7 +67543,7 @@
       </c>
       <c r="I13" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Focal*")</f>
-        <v>2.6453333333333333</v>
+        <v>2.0804999999999998</v>
       </c>
       <c r="J13" s="188">
         <v>400</v>
@@ -67510,7 +67577,7 @@
       </c>
       <c r="I14" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foundation*")</f>
-        <v>1.6591883116883117</v>
+        <v>1.7135227272727276</v>
       </c>
       <c r="J14" s="188">
         <v>400</v>
@@ -67544,7 +67611,7 @@
       </c>
       <c r="I15" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>1.6082894736842104</v>
+        <v>1.6617543859649124</v>
       </c>
       <c r="J15" s="188">
         <v>120</v>
@@ -67578,7 +67645,7 @@
       </c>
       <c r="I16" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Float*")</f>
-        <v>1.3608333333333333</v>
+        <v>2.008690476190476</v>
       </c>
       <c r="J16" s="188">
         <v>200</v>
@@ -67612,7 +67679,7 @@
       </c>
       <c r="I17" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Finisher*")</f>
-        <v>1.7747807017543862</v>
+        <v>1.5863596491228071</v>
       </c>
       <c r="J17" s="188">
         <v>250</v>
@@ -67647,7 +67714,7 @@
       </c>
       <c r="I18" s="170">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foliage*")</f>
-        <v>1.4392307692307693</v>
+        <v>1.7152564102564098</v>
       </c>
       <c r="J18" s="189">
         <v>300</v>
@@ -67760,7 +67827,7 @@
       </c>
       <c r="D24" s="248">
         <f>SUMPRODUCT(I24:I29, E24:E29)</f>
-        <v>55.962819066898014</v>
+        <v>57.486429776363991</v>
       </c>
       <c r="E24" s="212">
         <v>5</v>
@@ -67774,7 +67841,7 @@
       </c>
       <c r="I24" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Focal*")</f>
-        <v>2.6453333333333333</v>
+        <v>2.0804999999999998</v>
       </c>
       <c r="J24" s="192">
         <f t="shared" ref="J24:J29" si="2">L13</f>
@@ -67805,7 +67872,7 @@
       </c>
       <c r="I25" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foundation*")</f>
-        <v>1.6591883116883117</v>
+        <v>1.7135227272727276</v>
       </c>
       <c r="J25" s="192">
         <f t="shared" si="2"/>
@@ -67836,7 +67903,7 @@
       </c>
       <c r="I26" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>1.6082894736842104</v>
+        <v>1.6617543859649124</v>
       </c>
       <c r="J26" s="192">
         <f t="shared" si="2"/>
@@ -67867,7 +67934,7 @@
       </c>
       <c r="I27" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Float*")</f>
-        <v>1.3608333333333333</v>
+        <v>2.008690476190476</v>
       </c>
       <c r="J27" s="192">
         <f t="shared" si="2"/>
@@ -67898,7 +67965,7 @@
       </c>
       <c r="I28" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Finisher*")</f>
-        <v>1.7747807017543862</v>
+        <v>1.5863596491228071</v>
       </c>
       <c r="J28" s="192">
         <f t="shared" si="2"/>
@@ -67930,7 +67997,7 @@
       </c>
       <c r="I29" s="170">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foliage*")</f>
-        <v>1.4392307692307693</v>
+        <v>1.7152564102564098</v>
       </c>
       <c r="J29" s="193">
         <f t="shared" si="2"/>
@@ -68013,7 +68080,7 @@
       </c>
       <c r="D34" s="248">
         <f>SUMPRODUCT(E34:E39, I34:I39)</f>
-        <v>21.882016562384987</v>
+        <v>22.762476422700111</v>
       </c>
       <c r="E34" s="212">
         <v>1</v>
@@ -68027,7 +68094,7 @@
       </c>
       <c r="I34" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Focal*")</f>
-        <v>2.6453333333333333</v>
+        <v>2.0804999999999998</v>
       </c>
       <c r="J34" s="192">
         <f t="shared" ref="J34:J39" si="5">L24</f>
@@ -68058,7 +68125,7 @@
       </c>
       <c r="I35" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foundation*")</f>
-        <v>1.6591883116883117</v>
+        <v>1.7135227272727276</v>
       </c>
       <c r="J35" s="192">
         <f t="shared" si="5"/>
@@ -68089,7 +68156,7 @@
       </c>
       <c r="I36" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>1.6082894736842104</v>
+        <v>1.6617543859649124</v>
       </c>
       <c r="J36" s="192">
         <f t="shared" si="5"/>
@@ -68120,7 +68187,7 @@
       </c>
       <c r="I37" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Float*")</f>
-        <v>1.3608333333333333</v>
+        <v>2.008690476190476</v>
       </c>
       <c r="J37" s="192">
         <f t="shared" si="5"/>
@@ -68151,7 +68218,7 @@
       </c>
       <c r="I38" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Finisher*")</f>
-        <v>1.7747807017543862</v>
+        <v>1.5863596491228071</v>
       </c>
       <c r="J38" s="192">
         <f t="shared" si="5"/>
@@ -68183,7 +68250,7 @@
       </c>
       <c r="I39" s="170">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foliage*")</f>
-        <v>1.4392307692307693</v>
+        <v>1.7152564102564098</v>
       </c>
       <c r="J39" s="192">
         <f t="shared" si="5"/>
@@ -68243,7 +68310,7 @@
       </c>
       <c r="D43" s="248">
         <f>SUMPRODUCT(E43:E48, I43:I48)</f>
-        <v>23.506125506072873</v>
+        <v>19.45147570850202</v>
       </c>
       <c r="E43" s="212">
         <v>7</v>
@@ -68257,7 +68324,7 @@
       </c>
       <c r="I43" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Focal*")</f>
-        <v>2.6453333333333333</v>
+        <v>2.0804999999999998</v>
       </c>
       <c r="J43" s="192">
         <f t="shared" ref="J43:J48" si="9">L34</f>
@@ -68288,7 +68355,7 @@
       </c>
       <c r="I44" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foundation*")</f>
-        <v>1.6591883116883117</v>
+        <v>1.7135227272727276</v>
       </c>
       <c r="J44" s="192">
         <f t="shared" si="9"/>
@@ -68319,7 +68386,7 @@
       </c>
       <c r="I45" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Filler*")</f>
-        <v>1.6082894736842104</v>
+        <v>1.6617543859649124</v>
       </c>
       <c r="J45" s="192">
         <f t="shared" si="9"/>
@@ -68350,7 +68417,7 @@
       </c>
       <c r="I46" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Float*")</f>
-        <v>1.3608333333333333</v>
+        <v>2.008690476190476</v>
       </c>
       <c r="J46" s="192">
         <f t="shared" si="9"/>
@@ -68381,7 +68448,7 @@
       </c>
       <c r="I47" s="80">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Finisher*")</f>
-        <v>1.7747807017543862</v>
+        <v>1.5863596491228071</v>
       </c>
       <c r="J47" s="192">
         <f t="shared" si="9"/>
@@ -68413,7 +68480,7 @@
       </c>
       <c r="I48" s="170">
         <f>AVERAGEIFS('Master Variety List'!E:E, 'Master Variety List'!A:A, "*Fall*", 'Master Variety List'!B:B, "*Foliage*")</f>
-        <v>1.4392307692307693</v>
+        <v>1.7152564102564098</v>
       </c>
       <c r="J48" s="192">
         <f t="shared" si="9"/>
